--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-10</t>
+          <t>2025-08-01 〜 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2127</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3375</v>
+        <v>0.3395</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1946</v>
+        <v>0.1933</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>20</v>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>41</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.277</v>
+        <v>0.2752</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3261</v>
+        <v>0.3237</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -846,101 +846,101 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.4297</v>
+        <v>0.1085</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>128</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0.1094</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="F12" s="5" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.32</v>
+        <v>0.5794</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>125</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.584</v>
+        <v>0.32</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.1707</v>
+        <v>0.1774</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>32</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5462</v>
+        <v>0.5417</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5133</v>
+        <v>0.5088</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>8</v>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5893</v>
+        <v>0.5929</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4953</v>
+        <v>0.4907</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>11</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>52</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4906</v>
+        <v>0.486</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>9</v>
@@ -1221,51 +1221,51 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.4078</v>
+        <v>0.625</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
         <v>103</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.6311</v>
+        <v>0.4078</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1346,23 +1346,23 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
         <v>96</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.125</v>
+        <v>0.2708</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1371,23 +1371,23 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.2737</v>
+        <v>0.125</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6988</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>9</v>
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.2785</v>
+        <v>0.275</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>1</v>
@@ -1575,19 +1575,19 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.4459</v>
+        <v>0.4533</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.1408</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>24</v>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1562</v>
+        <v>0.1538</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>5</v>
@@ -1821,73 +1821,73 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
         <v>56</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.5714</v>
+        <v>0.2143</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
         <v>56</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.3036</v>
+        <v>0.5714</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3036</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0</v>
@@ -2371,51 +2371,51 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>放置無言出入自由</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>0</v>
+        <v>0.1071</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>放置無言出入自由</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
         <v>27</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2571,73 +2571,73 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
         <v>21</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>0.05</v>
+        <v>0.1429</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G82" s="5" t="n">
         <v>0</v>
@@ -2750,19 +2750,19 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>2</v>
@@ -3321,23 +3321,23 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,23 +3346,23 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>0</v>
@@ -3371,20 +3371,20 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.1429</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>13</v>
@@ -3396,7 +3396,7 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -3412,57 +3412,57 @@
         <v>3</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.1429</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -3471,23 +3471,23 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3496,23 +3496,23 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.5</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
@@ -3521,23 +3521,23 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
@@ -3546,23 +3546,23 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -3584,10 +3584,10 @@
         <v>0.1667</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3646,23 +3646,23 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>0</v>
@@ -3671,23 +3671,23 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G124" s="5" t="n">
         <v>0</v>
@@ -3696,23 +3696,23 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>0</v>
@@ -3721,23 +3721,23 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G126" s="5" t="n">
         <v>0</v>
@@ -3746,23 +3746,23 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E127" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C127" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D127" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F127" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -3771,23 +3771,23 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>47</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>44</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3</v>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>9</v>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>15</v>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>18</v>
@@ -5505,43 +5505,43 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>27</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -5867,80 +5867,80 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -6114,40 +6114,40 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>7</v>
@@ -6156,61 +6156,61 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>MÏRÃGË</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
           <t>Revenant</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>7</v>
@@ -6219,112 +6219,112 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -6336,10 +6336,10 @@
         <v>19</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -6681,117 +6681,117 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -6801,112 +6801,112 @@
         <v>3</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -7269,12 +7269,12 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
@@ -7284,46 +7284,46 @@
         <v>0</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>6</v>
@@ -7332,40 +7332,40 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0</v>
@@ -7374,103 +7374,103 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>3</v>
@@ -7479,33 +7479,33 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
@@ -7515,18 +7515,18 @@
         <v>3</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
@@ -7536,112 +7536,112 @@
         <v>4</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
+          <t>xAEGISx</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
           <t>オアシステップ</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>一Arch</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120">
@@ -7689,33 +7689,33 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
@@ -7725,60 +7725,60 @@
         <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
@@ -7788,13 +7788,13 @@
         <v>0</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -7809,97 +7809,97 @@
         <v>0</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -7911,49 +7911,49 @@
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" s="5" t="n">
         <v>4</v>
@@ -7962,96 +7962,96 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
@@ -8067,12 +8067,12 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
@@ -8082,34 +8082,34 @@
         <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -8121,31 +8121,31 @@
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
           <t>義勇</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -8571,61 +8571,61 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5" t="n">
         <v>3</v>
@@ -8634,40 +8634,40 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5" t="n">
         <v>4</v>
@@ -8676,12 +8676,12 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
@@ -8691,25 +8691,25 @@
         <v>1</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
@@ -8730,7 +8730,7 @@
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>1</v>
@@ -8739,28 +8739,28 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -8772,10 +8772,10 @@
         <v>10</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
@@ -8796,13 +8796,13 @@
         <v>3</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -8814,7 +8814,7 @@
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E175" s="5" t="n">
         <v>0</v>
@@ -8823,75 +8823,75 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
@@ -8901,67 +8901,67 @@
         <v>2</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E182" s="5" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -8991,19 +8991,19 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E184" s="5" t="n">
         <v>0</v>
@@ -9012,49 +9012,49 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D186" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E186" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E187" s="5" t="n">
         <v>3</v>
@@ -9075,12 +9075,12 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
@@ -9159,7 +9159,7 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -9171,21 +9171,21 @@
         <v>9</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
@@ -9195,25 +9195,25 @@
         <v>1</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
         <v>1</v>
@@ -9222,19 +9222,19 @@
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
+          <t>ひよこりあ</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
           <t>月下の集い</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" s="5" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
@@ -9255,84 +9255,84 @@
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
           <t>TRAITORs</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="inlineStr">
-        <is>
-          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
@@ -9342,28 +9342,28 @@
         <v>0</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9435,7 +9435,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -9464,12 +9464,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
@@ -9493,26 +9493,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
@@ -9551,12 +9551,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
@@ -9580,26 +9580,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -9957,26 +9957,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -10015,12 +10015,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
@@ -10044,12 +10044,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G23" s="6" t="n">
@@ -10073,26 +10073,26 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G24" s="6" t="n">
@@ -10102,26 +10102,26 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G25" s="6" t="n">
@@ -10131,26 +10131,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
@@ -10160,26 +10160,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
@@ -10189,12 +10189,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
@@ -10218,26 +10218,26 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
@@ -10247,26 +10247,26 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -10334,12 +10334,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
@@ -10363,26 +10363,26 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
@@ -10392,12 +10392,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Outlawss</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
@@ -10421,12 +10421,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Outlawss</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
@@ -10450,7 +10450,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -10479,26 +10479,26 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
@@ -10508,12 +10508,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
@@ -10537,12 +10537,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
@@ -10566,12 +10566,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
@@ -10595,12 +10595,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -10653,26 +10653,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
@@ -10682,7 +10682,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -10711,7 +10711,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -10740,26 +10740,26 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
@@ -11262,26 +11262,26 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11291,26 +11291,26 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G66" s="6" t="n">
@@ -11320,7 +11320,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -11349,12 +11349,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
@@ -11378,7 +11378,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -11407,12 +11407,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11436,26 +11436,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
@@ -11465,30 +11465,30 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="73">
@@ -12103,7 +12103,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0827</v>
+        <v>0.0824</v>
       </c>
     </row>
     <row r="3">
@@ -12116,10 +12116,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2045</v>
+        <v>0.2042</v>
       </c>
     </row>
     <row r="4">
@@ -12132,10 +12132,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.417</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="5">
@@ -12151,7 +12151,7 @@
         <v>169</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0795</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -12164,10 +12164,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2163</v>
+        <v>0.2164</v>
       </c>
     </row>
   </sheetData>
@@ -12181,7 +12181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14006,15 +14006,15 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝, VainqueurJP:2勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15670,30 +15670,30 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15708,15 +15708,15 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15754,15 +15754,15 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15961,7 +15961,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -15969,30 +15969,30 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:4勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16007,15 +16007,15 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:5勝</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16191,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -16237,13 +16237,36 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D176" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
+      <c r="D177" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16461,10 +16484,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
@@ -16565,10 +16588,10 @@
         <v>16</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
@@ -16617,10 +16640,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -16669,10 +16692,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
@@ -16834,102 +16857,102 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="G11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="5" t="n">
+      <c r="K11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="J12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="O12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>128</v>
@@ -16938,102 +16961,102 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="M13" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="H14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>125</v>
@@ -17085,10 +17108,10 @@
         <v>12</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -17189,10 +17212,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
@@ -17293,10 +17316,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -17345,10 +17368,10 @@
         <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
@@ -17449,10 +17472,10 @@
         <v>10</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
@@ -17501,10 +17524,10 @@
         <v>9</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -17614,102 +17637,102 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>8</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>103</v>
@@ -17874,50 +17897,50 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="G31" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>96</v>
@@ -17926,53 +17949,53 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F32" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33">
@@ -18125,10 +18148,10 @@
         <v>5</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -18229,10 +18252,10 @@
         <v>12</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -18385,10 +18408,10 @@
         <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
@@ -18489,10 +18512,10 @@
         <v>9</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -18749,10 +18772,10 @@
         <v>10</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -18862,7 +18885,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -18881,7 +18904,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>8</v>
@@ -18890,22 +18913,22 @@
         <v>7</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M50" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="O50" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="P50" s="5" t="n">
         <v>56</v>
@@ -18914,50 +18937,50 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="I51" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51" s="5" t="n">
         <v>56</v>
@@ -18966,53 +18989,53 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53">
@@ -20006,7 +20029,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>放置無言出入自由</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -20016,13 +20039,13 @@
         <v>1</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>3</v>
@@ -20031,34 +20054,34 @@
         <v>1</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>放置無言出入自由</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -20068,13 +20091,13 @@
         <v>1</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="n">
         <v>3</v>
@@ -20083,22 +20106,22 @@
         <v>1</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M73" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="N73" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O73" s="5" t="n">
         <v>0</v>
@@ -20422,50 +20445,50 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D80" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" s="5" t="n">
         <v>21</v>
@@ -20474,23 +20497,23 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>0</v>
@@ -20520,13 +20543,13 @@
         <v>0</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -20536,16 +20559,16 @@
         <v>1</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>0</v>
@@ -20554,16 +20577,16 @@
         <v>0</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N82" s="5" t="n">
         <v>0</v>
@@ -20829,10 +20852,10 @@
         <v>0</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
@@ -21982,7 +22005,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -22007,16 +22030,16 @@
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0</v>
@@ -22025,7 +22048,7 @@
         <v>1</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P110" s="5" t="n">
         <v>7</v>
@@ -22034,11 +22057,11 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C111" s="5" t="n">
         <v>0</v>
@@ -22059,22 +22082,22 @@
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="5" t="n">
         <v>0</v>
@@ -22086,11 +22109,11 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>0</v>
@@ -22117,10 +22140,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0</v>
@@ -22138,41 +22161,41 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0</v>
@@ -22190,17 +22213,17 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>0</v>
@@ -22242,17 +22265,17 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>0</v>
@@ -22261,7 +22284,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
@@ -22288,17 +22311,17 @@
         <v>0</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C116" s="5" t="n">
         <v>0</v>
@@ -22313,7 +22336,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>0</v>
@@ -22346,11 +22369,11 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C117" s="5" t="n">
         <v>0</v>
@@ -22386,10 +22409,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P117" s="5" t="n">
         <v>6</v>
@@ -22398,7 +22421,7 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -22423,25 +22446,25 @@
         <v>0</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M118" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P118" s="5" t="n">
         <v>6</v>
@@ -22450,17 +22473,17 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E119" s="5" t="n">
         <v>0</v>
@@ -22475,16 +22498,16 @@
         <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M119" s="5" t="n">
         <v>0</v>
@@ -22493,7 +22516,7 @@
         <v>0</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" s="5" t="n">
         <v>6</v>
@@ -22502,17 +22525,17 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>0</v>
@@ -22542,10 +22565,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P120" s="5" t="n">
         <v>6</v>
@@ -22658,11 +22681,11 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C123" s="5" t="n">
         <v>0</v>
@@ -22698,10 +22721,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P123" s="5" t="n">
         <v>5</v>
@@ -22710,17 +22733,17 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>0</v>
@@ -22735,10 +22758,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K124" s="5" t="n">
         <v>0</v>
@@ -22750,10 +22773,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P124" s="5" t="n">
         <v>5</v>
@@ -22762,14 +22785,14 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>0</v>
@@ -22814,11 +22837,11 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C126" s="5" t="n">
         <v>0</v>
@@ -22839,10 +22862,10 @@
         <v>0</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K126" s="5" t="n">
         <v>0</v>
@@ -22866,14 +22889,14 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>0</v>
@@ -22906,29 +22929,29 @@
         <v>0</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P127" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>0</v>
@@ -22958,13 +22981,13 @@
         <v>0</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
@@ -25734,7 +25757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25804,7 +25827,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -25822,7 +25845,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -25840,7 +25863,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25852,13 +25875,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25876,7 +25899,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -25894,7 +25917,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -25912,25 +25935,25 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>離脱(前半のみ)</t>
+          <t>新規参入(後半のみ)</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -25939,7 +25962,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0</v>
@@ -25948,7 +25971,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -25957,7 +25980,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
@@ -25966,7 +25989,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -25975,7 +25998,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -25984,7 +26007,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -25993,7 +26016,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -26002,7 +26025,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -26011,7 +26034,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -26020,7 +26043,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>DoraemonSA</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -26029,7 +26052,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -26038,7 +26061,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>DoraemonSA</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -26047,7 +26070,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -26056,7 +26079,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -26065,7 +26088,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
@@ -26074,7 +26097,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>愛Eиdorphiиe</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -26083,7 +26106,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -26092,7 +26115,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>愛Eиdorphiиe</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -26101,7 +26124,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -26110,7 +26133,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -26119,7 +26142,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -26128,7 +26151,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -26146,7 +26169,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -26155,7 +26178,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -26164,7 +26187,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -26173,7 +26196,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>0</v>
@@ -26182,7 +26205,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -26191,7 +26214,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -26200,7 +26223,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -26218,7 +26241,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -26227,7 +26250,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
@@ -26236,7 +26259,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -26245,7 +26268,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>0</v>
@@ -26254,7 +26277,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -26272,7 +26295,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -26281,7 +26304,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>0</v>
@@ -26290,7 +26313,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -26308,7 +26331,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -26326,7 +26349,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -26335,7 +26358,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>0</v>
@@ -26344,7 +26367,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -26362,7 +26385,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -26380,7 +26403,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -26398,7 +26421,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -26407,7 +26430,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>0</v>
@@ -26416,7 +26439,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -26434,7 +26457,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -26446,6 +26469,24 @@
         <v>5</v>
       </c>
       <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Ancîеnts</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>離脱(前半のみ)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26530,16 +26571,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(44), 雪狼族(41), 沙漠黑鷹(40), 雲淡風輕o(16), 當惡魔遇到殺手貓(15), LeLien(13), ーリベリオンー(11), Unity(9)</t>
+          <t>・殺戮・(45), 雪狼族(42), 沙漠黑鷹(41), 雲淡風輕o(17), 當惡魔遇到殺手貓(16), LeLien(13), ーリベリオンー(11), Unity(9)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(40勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
+          <t>・殺戮・(41勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
         </is>
       </c>
     </row>
@@ -26714,16 +26755,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(39), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(18), TRAITORs(11), Phoenix(8), ・殺戮・(6)</t>
+          <t>AlmaVivaJP(40), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(18), TRAITORs(12), Phoenix(8), ・殺戮・(7)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(28勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
+          <t>AlmaVivaJP(29勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -26875,16 +26916,16 @@
         <v>38</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(11), 黒の太陽(11), ーEspoirー(10), xAEGISx(6), ーリベリオンー(5)</t>
+          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(12), 黒の太陽(11), ーEspoirー(10), Restart(6), xAEGISx(6)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(16勝), シェイド(11勝), 一Arch(6勝), FLORISTS(5勝), 黒の太陽(3勝)</t>
+          <t>オアシステップ(16勝), シェイド(11勝), 一Arch(6勝), FLORISTS(5勝), オアシスステップ(3勝)</t>
         </is>
       </c>
     </row>
@@ -26898,16 +26939,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(38), RaиkSS(26), VainqueurJP(26), PONYTAIL(22), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
+          <t>TRAITORs(38), RaиkSS(27), VainqueurJP(27), PONYTAIL(23), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(22勝), RaиkSS(9勝), VainqueurJP(8勝), PONYTAIL(7勝), AlmaVivaJP(5勝)</t>
+          <t>TRAITORs(22勝), RaиkSS(9勝), PONYTAIL(8勝), VainqueurJP(8勝), AlmaVivaJP(5勝)</t>
         </is>
       </c>
     </row>
@@ -26918,14 +26959,14 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(22), Kopitiam(11), ーリベリオンー(9), ZirconiA(7), Иouver(7), 柿一門(5), 亗Luxúria亗(5), MelonEmpire(5)</t>
+          <t>一惡人谷一(22), Kopitiam(11), ーリベリオンー(10), ZirconiA(7), Иouver(7), 柿一門(5), 亗Luxúria亗(5), MelonEmpire(5)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -27036,7 +27077,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -27125,19 +27166,19 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ひよこりあ(28), ーEspoirー(20), 義勇(19), 桜吹雪(19), 月下の集い(18), TheEnd(17), のら猫(15), ZirconiA(14)</t>
+          <t>ひよこりあ(28), ーEspoirー(21), 義勇(20), 月下の集い(19), 桜吹雪(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>義勇(10勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝), ーEspoirー(4勝)</t>
+          <t>義勇(11勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝), ーEspoirー(4勝)</t>
         </is>
       </c>
     </row>
@@ -27174,16 +27215,16 @@
         <v>46</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 桜吹雪(8), 柿一門(7), ーEspoirー(7), 微笑Party(6), EIemento(5)</t>
+          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 柿一門(8), 桜吹雪(8), 微笑Party(7), ーEspoirー(7), EIemento(5)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(10勝), Restart(9勝), 柿一門(4勝), 一DEFIANCE(3勝), REGENCY彡(2勝)</t>
+          <t>亗Luxúria亗(10勝), Restart(9勝), 柿一門(4勝), 微笑Party(3勝), 一DEFIANCE(3勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-12</t>
+          <t>2025-08-01 〜 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2135</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3374</v>
+        <v>0.3354</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3395</v>
+        <v>0.3374</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.3667</v>
+        <v>0.3642</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>31</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1933</v>
+        <v>0.1921</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>20</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3237</v>
+        <v>0.3214</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3435</v>
+        <v>0.3409</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.5794</v>
+        <v>0.5827</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>17</v>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4649</v>
+        <v>0.4609</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>1</v>
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5088</v>
+        <v>0.513</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>8</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.486</v>
+        <v>0.4907</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>9</v>
@@ -1196,51 +1196,51 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.4381</v>
+        <v>0.619</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.625</v>
+        <v>0.4381</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3407</v>
+        <v>0.337</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
@@ -1575,19 +1575,19 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C40" s="5" t="n">
         <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.4533</v>
+        <v>0.4474</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1408</v>
+        <v>0.1389</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>24</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>1</v>
@@ -1646,51 +1646,51 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.7206</v>
+        <v>0.1449</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
         <v>68</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.7206</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
@@ -1725,19 +1725,19 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.1692</v>
+        <v>0.1667</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>1</v>
@@ -1825,19 +1825,19 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.2143</v>
+        <v>0.2105</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.5714</v>
+        <v>0.5789</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>14</v>
@@ -1921,23 +1921,23 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.2963</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -1946,23 +1946,23 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.3019</v>
+        <v>0.1111</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0.2571</v>
+        <v>0.2778</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>12</v>
@@ -2696,48 +2696,48 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
         <v>17</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>0.1765</v>
+        <v>0.3529</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
         <v>17</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>0</v>
+        <v>0.1765</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>0</v>
@@ -2746,26 +2746,26 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3196,23 +3196,23 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -3237,7 +3237,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0</v>
@@ -3246,23 +3246,23 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -3309,35 +3309,35 @@
         <v>0.125</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,26 +3346,26 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3396,20 +3396,20 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.4286</v>
+        <v>0.7143</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>13</v>
@@ -3421,7 +3421,7 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -3437,57 +3437,57 @@
         <v>3</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.1429</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3496,23 +3496,23 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
@@ -3521,23 +3521,23 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.8333</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
@@ -3546,23 +3546,23 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E119" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0</v>
@@ -3571,23 +3571,23 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -3609,7 +3609,7 @@
         <v>0.1667</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F121" s="5" t="n">
         <v>16</v>
@@ -3621,23 +3621,23 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G122" s="5" t="n">
         <v>0</v>
@@ -3646,23 +3646,23 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C123" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F123" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>23</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>5</v>
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -5589,61 +5589,61 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>2</v>
@@ -5652,40 +5652,40 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>6</v>
@@ -5694,70 +5694,70 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -5766,76 +5766,76 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D31" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -5946,91 +5946,91 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -6042,37 +6042,37 @@
         <v>20</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -6084,21 +6084,21 @@
         <v>20</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -6108,18 +6108,18 @@
         <v>4</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
@@ -6129,46 +6129,46 @@
         <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>7</v>
@@ -6387,19 +6387,19 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>5</v>
@@ -6408,61 +6408,61 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>4</v>
@@ -6471,106 +6471,106 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -6597,28 +6597,28 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6630,79 +6630,79 @@
         <v>17</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -6714,7 +6714,7 @@
         <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
@@ -6723,33 +6723,33 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
@@ -6759,55 +6759,55 @@
         <v>5</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -6819,28 +6819,28 @@
         <v>16</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>7</v>
@@ -7710,33 +7710,33 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
@@ -7746,60 +7746,60 @@
         <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
@@ -7809,13 +7809,13 @@
         <v>0</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -7830,97 +7830,97 @@
         <v>0</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -7932,49 +7932,49 @@
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>4</v>
@@ -7983,96 +7983,96 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
@@ -8088,12 +8088,12 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
@@ -8103,28 +8103,28 @@
         <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -8445,7 +8445,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -8457,196 +8457,196 @@
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" s="5" t="n">
         <v>3</v>
@@ -8655,40 +8655,40 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="5" t="n">
         <v>4</v>
@@ -8697,12 +8697,12 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
@@ -8712,25 +8712,25 @@
         <v>1</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>1</v>
@@ -8739,7 +8739,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -8751,7 +8751,7 @@
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>1</v>
@@ -8760,28 +8760,28 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -8793,10 +8793,10 @@
         <v>10</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
@@ -8817,13 +8817,13 @@
         <v>3</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -8835,7 +8835,7 @@
         <v>10</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E176" s="5" t="n">
         <v>0</v>
@@ -8844,75 +8844,75 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
@@ -8922,67 +8922,67 @@
         <v>2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E182" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E183" s="5" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -9012,19 +9012,19 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E185" s="5" t="n">
         <v>0</v>
@@ -9033,22 +9033,22 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="49">
@@ -12103,7 +12103,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0824</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -12116,10 +12116,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2042</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="4">
@@ -12132,10 +12132,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4178</v>
+        <v>0.4176</v>
       </c>
     </row>
     <row r="5">
@@ -12151,7 +12151,7 @@
         <v>169</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="6">
@@ -12164,10 +12164,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2164</v>
+        <v>0.2165</v>
       </c>
     </row>
   </sheetData>
@@ -13895,11 +13895,11 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:4勝</t>
+          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:5勝</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>沙漠黑鷹:6勝</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14029,15 +14029,15 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -16432,10 +16432,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -16484,10 +16484,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
@@ -16536,10 +16536,10 @@
         <v>13</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
@@ -16588,10 +16588,10 @@
         <v>16</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -16692,10 +16692,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
@@ -16848,10 +16848,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -17004,10 +17004,10 @@
         <v>14</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -17264,10 +17264,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
@@ -17316,10 +17316,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -17524,10 +17524,10 @@
         <v>9</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
@@ -17585,50 +17585,50 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="G25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="N25" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="O25" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>105</v>
@@ -17637,53 +17637,53 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I26" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="J26" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
@@ -18044,10 +18044,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
@@ -18408,10 +18408,10 @@
         <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
@@ -18512,111 +18512,111 @@
         <v>9</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="H43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="K43" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" s="5" t="n">
         <v>68</v>
@@ -18720,10 +18720,10 @@
         <v>3</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47">
@@ -18928,10 +18928,10 @@
         <v>10</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
@@ -18980,10 +18980,10 @@
         <v>5</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
@@ -19093,50 +19093,50 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="M54" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P54" s="5" t="n">
         <v>54</v>
@@ -19145,53 +19145,53 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D55" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="G55" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M55" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56">
@@ -19552,10 +19552,10 @@
         <v>13</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -20705,35 +20705,35 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>0</v>
@@ -20742,13 +20742,13 @@
         <v>0</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P85" s="5" t="n">
         <v>17</v>
@@ -20757,50 +20757,50 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" s="5" t="n">
         <v>17</v>
@@ -20809,53 +20809,53 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" s="5" t="n">
         <v>2</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" s="5" t="n">
         <v>1</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88">
@@ -21745,17 +21745,17 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -21776,19 +21776,19 @@
         <v>0</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P105" s="5" t="n">
         <v>8</v>
@@ -21797,7 +21797,7 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -21819,28 +21819,28 @@
         <v>0</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I106" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="5" t="n">
         <v>8</v>
@@ -21849,14 +21849,14 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>1</v>
@@ -21880,19 +21880,19 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P107" s="5" t="n">
         <v>8</v>
@@ -21901,35 +21901,35 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K108" s="5" t="n">
         <v>0</v>
@@ -21953,17 +21953,17 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
@@ -21972,13 +21972,13 @@
         <v>0</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
         <v>0</v>
@@ -21987,16 +21987,16 @@
         <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" s="5" t="n">
         <v>8</v>
@@ -22005,32 +22005,32 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="5" t="n">
         <v>0</v>
@@ -22045,23 +22045,23 @@
         <v>0</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" s="5" t="n">
         <v>0</v>
@@ -22076,22 +22076,22 @@
         <v>0</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0</v>
@@ -22100,10 +22100,10 @@
         <v>1</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -22161,7 +22161,7 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -22192,19 +22192,19 @@
         <v>0</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P113" s="5" t="n">
         <v>7</v>
@@ -22213,41 +22213,41 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L114" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="C114" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>0</v>
@@ -22265,17 +22265,17 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>0</v>
@@ -22317,17 +22317,17 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>0</v>
@@ -22336,7 +22336,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>0</v>
@@ -22363,17 +22363,17 @@
         <v>0</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C117" s="5" t="n">
         <v>0</v>
@@ -22409,10 +22409,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P117" s="5" t="n">
         <v>6</v>
@@ -22421,11 +22421,11 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C118" s="5" t="n">
         <v>0</v>
@@ -22440,7 +22440,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H118" s="5" t="n">
         <v>0</v>
@@ -22461,10 +22461,10 @@
         <v>0</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P118" s="5" t="n">
         <v>6</v>
@@ -22473,11 +22473,11 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C119" s="5" t="n">
         <v>0</v>
@@ -22498,16 +22498,16 @@
         <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" s="5" t="n">
         <v>0</v>
@@ -22516,7 +22516,7 @@
         <v>0</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" s="5" t="n">
         <v>6</v>
@@ -22525,17 +22525,17 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>0</v>
@@ -22550,16 +22550,16 @@
         <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>0</v>
@@ -22568,7 +22568,7 @@
         <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" s="5" t="n">
         <v>6</v>
@@ -22577,17 +22577,17 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
         <v>0</v>
@@ -22629,35 +22629,35 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" s="5" t="n">
         <v>0</v>
@@ -22681,7 +22681,7 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -22691,25 +22691,25 @@
         <v>0</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" s="5" t="n">
         <v>0</v>
@@ -22721,13 +22721,13 @@
         <v>0</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
@@ -25839,7 +25839,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -25857,13 +25857,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25881,7 +25881,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25893,13 +25893,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -25917,7 +25917,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -25929,7 +25929,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -26617,11 +26617,11 @@
         <v>69</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Revenant(42), ZirconiA(17), MÏRÃGË(17), 黄昏のえりしおん(12), 柿一門(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
+          <t>Revenant(43), MÏRÃGË(18), ZirconiA(17), 黄昏のえりしおん(12), 柿一門(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -26824,16 +26824,16 @@
         <v>38</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(52), ・殺戮・(50), 毛家村(41), 雲淡風輕o(18), 廣寒宮(9), 微笑Party(8), Oops(6), TheUniverse(6)</t>
+          <t>沙漠黑鷹(53), ・殺戮・(51), 毛家村(42), 雲淡風輕o(18), 廣寒宮(9), 微笑Party(8), Oops(6), TheUniverse(6)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(47勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
+          <t>沙漠黑鷹(48勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
         </is>
       </c>
     </row>
@@ -26893,16 +26893,16 @@
         <v>22</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(34), ßบรнíïdо丶ๅ家族(25), Kopitiam(19), SkyCastIe(17), 彡MukBANG彡(9), MelonEmpire(8), 微笑Party(6), Ancîеnts(5)</t>
+          <t>亗Luxúria亗(35), ßบรнíïdо丶ๅ家族(25), Kopitiam(20), SkyCastIe(17), MelonEmpire(9), 彡MukBANG彡(9), 微笑Party(6), Ancîеnts(5)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(16勝), SkyCastIe(13勝), ßบรнíïdо丶ๅ家族(11勝), MelonEmpire(5勝), ーリベリオンー(3勝)</t>
+          <t>亗Luxúria亗(16勝), SkyCastIe(13勝), ßบรнíïdо丶ๅ家族(11勝), MelonEmpire(6勝), ーリベリオンー(3勝)</t>
         </is>
       </c>
     </row>
@@ -27008,11 +27008,11 @@
         <v>62</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>義勇(28), ーEspoirー(19), オアシステップ(18), 桜吹雪(17), ー麒麟ー(16), 黄昏のえりしおん(14), Restart(13), 黒の太陽(11)</t>
+          <t>義勇(29), ーEspoirー(19), オアシステップ(18), ー麒麟ー(17), 桜吹雪(17), Restart(14), 黄昏のえりしおん(14), 柿一門(11)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -27238,16 +27238,16 @@
         <v>41</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(23), PokemonGo(10), xAEGISx(9), VainqueurJP(8), TheUniverse(7), PONYTAIL(7), Maverickz(6), Revenant(5)</t>
+          <t>TRAITORs(24), PokemonGo(10), xAEGISx(9), VainqueurJP(8), TheUniverse(7), PONYTAIL(7), RaиkSS(6), Maverickz(6)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(21勝), VainqueurJP(6勝), PONYTAIL(5勝), RaиkSS(4勝), PokemonGo(3勝)</t>
+          <t>TRAITORs(21勝), VainqueurJP(6勝), RaиkSS(5勝), PONYTAIL(5勝), PokemonGo(3勝)</t>
         </is>
       </c>
     </row>
@@ -27261,16 +27261,16 @@
         <v>49</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(28), ーリベリオンー(10), Restart(10), EIemento(8), 一惡人谷一(8), ーEspoirー(7), 一Arch(6), Anino(6)</t>
+          <t>オアシステップ(28), ーリベリオンー(11), Restart(10), EIemento(8), 一惡人谷一(8), ーEspoirー(7), 一Arch(6), Anino(6)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(15勝), ーリベリオンー(6勝), 一惡人谷一(6勝), EIemento(4勝), Anino(4勝)</t>
+          <t>オアシステップ(15勝), ーリベリオンー(7勝), 一惡人谷一(6勝), EIemento(4勝), Anino(4勝)</t>
         </is>
       </c>
     </row>
@@ -27284,11 +27284,11 @@
         <v>50</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>シェイド(23), 一Arch(16), xAEGISx(15), 黒の太陽(12), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
+          <t>シェイド(24), 一Arch(16), xAEGISx(15), 黒の太陽(12), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -27307,16 +27307,16 @@
         <v>35</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(15), 氣噗噗讓玻璃心碎一地(15), 臨時公會名000000302(7), VainqueurJP(6), Myst(4), PokemonGo(4), xAEGISx(4), 星隕(4)</t>
+          <t>AlmaVivaJP(15), 氣噗噗讓玻璃心碎一地(15), 臨時公會名000000302(7), VainqueurJP(6), xAEGISx(5), Döraè่mön(4), Myst(4), PokemonGo(4)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(15勝), 氣噗噗讓玻璃心碎一地(12勝), VainqueurJP(6勝), RaиkSS(2勝), Myst(2勝)</t>
+          <t>AlmaVivaJP(15勝), 氣噗噗讓玻璃心碎一地(12勝), VainqueurJP(6勝), Döraè่mön(2勝), RaиkSS(2勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-13</t>
+          <t>2025-08-01 〜 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2143</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3354</v>
+        <v>0.3394</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3374</v>
+        <v>0.3354</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -671,51 +671,51 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.3642</v>
+        <v>0.1908</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>151</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1921</v>
+        <v>0.3642</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>41</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2752</v>
+        <v>0.2733</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.5827</v>
+        <v>0.5859</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>5</v>
@@ -921,51 +921,51 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>125</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.32</v>
+        <v>0.176</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.1774</v>
+        <v>0.32</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5417</v>
+        <v>0.5372</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>9</v>
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4609</v>
+        <v>0.4569</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4907</v>
+        <v>0.4954</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>11</v>
@@ -1171,51 +1171,51 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.6226</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.619</v>
+        <v>0.1429</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1296,51 +1296,51 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.3673</v>
+        <v>0.1616</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
         <v>98</v>
       </c>
       <c r="C30" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>0.1531</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.2708</v>
+        <v>0.2784</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1400,19 +1400,19 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.337</v>
+        <v>0.3333</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.1852</v>
+        <v>0.1829</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>24</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1389</v>
+        <v>0.1507</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>24</v>
@@ -1700,19 +1700,19 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C45" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.6716</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>2</v>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1538</v>
+        <v>0.1515</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>5</v>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.2105</v>
+        <v>0.2069</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>14</v>
@@ -2071,73 +2071,73 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
         <v>37</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.027</v>
+        <v>0.2703</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0.1944</v>
+        <v>0.027</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
         <v>36</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0.2778</v>
+        <v>0.1944</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0</v>
@@ -2500,19 +2500,19 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.25</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>2</v>
@@ -2671,51 +2671,51 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>0.3529</v>
+        <v>0</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3121,73 +3121,73 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.2222</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G104" s="5" t="n">
         <v>0</v>
@@ -3196,23 +3196,23 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>0</v>
@@ -3996,23 +3996,23 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G137" s="5" t="n">
         <v>0</v>
@@ -4021,20 +4021,20 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>8</v>
@@ -4046,23 +4046,23 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E139" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G139" s="5" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>0</v>
@@ -4096,23 +4096,23 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G141" s="5" t="n">
         <v>0</v>
@@ -4871,17 +4871,17 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>1</v>
@@ -4896,7 +4896,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -4912,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>TËMPËST</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>RL1</t>
+          <t>TËMPËST</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G175" s="5" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>天真爛漫ニャ向日葵</t>
+          <t>RL1</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -4996,7 +4996,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Smasher죠</t>
+          <t>天真爛漫ニャ向日葵</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -5012,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G177" s="5" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>XyChëDëLiC</t>
+          <t>Smasher죠</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -5046,7 +5046,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>微笑Paty</t>
+          <t>XyChëDëLiC</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -5062,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G179" s="5" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>VIRULENT死</t>
+          <t>微笑Paty</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -5096,25 +5096,50 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
+          <t>VIRULENT死</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
           <t>PinöyPioneer</t>
         </is>
       </c>
-      <c r="B181" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="5" t="n">
+      <c r="B182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5220,13 +5245,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>42</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -5241,13 +5266,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -5409,13 +5434,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -5589,169 +5614,169 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -5762,14 +5787,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>2</v>
@@ -5778,106 +5803,106 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -5888,17 +5913,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -5925,85 +5950,85 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -6261,145 +6286,145 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D59" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D59" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E59" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>5</v>
@@ -6539,49 +6564,49 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -6591,25 +6616,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>7</v>
@@ -6618,19 +6643,19 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>3</v>
@@ -6639,91 +6664,91 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D72" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -6735,7 +6760,7 @@
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>0</v>
@@ -6744,145 +6769,145 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>4</v>
@@ -6891,61 +6916,61 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D85" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>0</v>
@@ -9377,7 +9402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9614,7 +9639,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -9638,26 +9663,26 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -9667,26 +9692,26 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G10" s="6" t="n">
@@ -10885,26 +10910,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
           <t>ーEspoirー</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>柿一門</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
@@ -10914,26 +10939,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
@@ -10943,30 +10968,30 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D54" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="E54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="55">
@@ -11552,26 +11577,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11581,26 +11606,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -11610,26 +11635,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
@@ -11639,7 +11664,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -11668,12 +11693,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -11687,7 +11712,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
@@ -11697,12 +11722,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
@@ -11716,7 +11741,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
@@ -11726,26 +11751,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E81" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11755,26 +11780,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11784,26 +11809,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11813,12 +11838,12 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
@@ -11832,7 +11857,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11842,26 +11867,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11871,26 +11896,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E86" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11900,12 +11925,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
@@ -11919,7 +11944,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11929,26 +11954,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11958,26 +11983,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -11987,26 +12012,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12016,29 +12041,58 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E91" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
+          <t>黒の太陽</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
           <t>AlmaVivaJP</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>AlmaVivaJP</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12103,7 +12157,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="3">
@@ -12116,10 +12170,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2049</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="4">
@@ -12132,10 +12186,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4176</v>
+        <v>0.4184</v>
       </c>
     </row>
     <row r="5">
@@ -12151,7 +12205,7 @@
         <v>169</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0789</v>
+        <v>0.0786</v>
       </c>
     </row>
     <row r="6">
@@ -12164,10 +12218,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2165</v>
+        <v>0.2162</v>
       </c>
     </row>
   </sheetData>
@@ -12239,11 +12293,11 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:22勝</t>
+          <t>雪狼族:23勝</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P181"/>
+  <dimension ref="A1:P182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16432,10 +16486,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -16484,111 +16538,111 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5" t="n">
+      <c r="K4" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="N4" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="O5" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>151</v>
@@ -16640,10 +16694,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -17004,59 +17058,59 @@
         <v>14</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>11</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>13</v>
       </c>
       <c r="M14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>125</v>
@@ -17065,53 +17119,53 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>13</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
@@ -17212,10 +17266,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -17264,10 +17318,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
@@ -17472,10 +17526,10 @@
         <v>10</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23">
@@ -17533,102 +17587,102 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="F24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="M24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="L25" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>105</v>
@@ -17793,102 +17847,102 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="L29" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O29" s="5" t="n">
         <v>3</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>98</v>
@@ -17940,10 +17994,10 @@
         <v>9</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32">
@@ -18044,10 +18098,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
@@ -18200,10 +18254,10 @@
         <v>16</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
@@ -18512,10 +18566,10 @@
         <v>9</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
@@ -18668,10 +18722,10 @@
         <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46">
@@ -18772,10 +18826,10 @@
         <v>10</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48">
@@ -18928,10 +18982,10 @@
         <v>10</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51">
@@ -19405,26 +19459,26 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>0</v>
@@ -19433,7 +19487,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>0</v>
@@ -19442,13 +19496,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P60" s="5" t="n">
         <v>37</v>
@@ -19457,35 +19511,35 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="5" t="n">
         <v>0</v>
@@ -19503,41 +19557,41 @@
         <v>0</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C62" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D62" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="H62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
@@ -19546,13 +19600,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
         <v>36</v>
@@ -20332,10 +20386,10 @@
         <v>3</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -20653,50 +20707,50 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="5" t="n">
         <v>2</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P84" s="5" t="n">
         <v>18</v>
@@ -20705,53 +20759,53 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" s="5" t="n">
         <v>2</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
@@ -21589,14 +21643,14 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>0</v>
@@ -21629,10 +21683,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P102" s="5" t="n">
         <v>9</v>
@@ -21641,14 +21695,14 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>0</v>
@@ -21675,13 +21729,13 @@
         <v>0</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O103" s="5" t="n">
         <v>0</v>
@@ -21693,14 +21747,14 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>0</v>
@@ -21727,29 +21781,29 @@
         <v>0</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>0</v>
@@ -21785,10 +21839,10 @@
         <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P105" s="5" t="n">
         <v>8</v>
@@ -23409,14 +23463,14 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>0</v>
@@ -23449,26 +23503,26 @@
         <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>0</v>
@@ -23513,11 +23567,11 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C139" s="5" t="n">
         <v>0</v>
@@ -23553,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O139" s="5" t="n">
         <v>0</v>
@@ -23565,7 +23619,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -23584,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="5" t="n">
         <v>0</v>
@@ -23596,7 +23650,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" s="5" t="n">
         <v>0</v>
@@ -23605,7 +23659,7 @@
         <v>0</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O140" s="5" t="n">
         <v>0</v>
@@ -23617,7 +23671,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
@@ -23636,7 +23690,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>0</v>
@@ -23648,7 +23702,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="5" t="n">
         <v>0</v>
@@ -23657,10 +23711,10 @@
         <v>0</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P141" s="5" t="n">
         <v>3</v>
@@ -25229,7 +25283,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -25245,7 +25299,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -25272,7 +25326,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" s="5" t="n">
         <v>1</v>
@@ -25281,7 +25335,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -25297,7 +25351,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -25321,7 +25375,7 @@
         <v>0</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O173" s="5" t="n">
         <v>0</v>
@@ -25333,11 +25387,11 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>TËMPËST</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174" s="5" t="n">
         <v>0</v>
@@ -25373,7 +25427,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" s="5" t="n">
         <v>0</v>
@@ -25385,11 +25439,11 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>RL1</t>
+          <t>TËMPËST</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175" s="5" t="n">
         <v>0</v>
@@ -25425,7 +25479,7 @@
         <v>0</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O175" s="5" t="n">
         <v>0</v>
@@ -25437,7 +25491,7 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>天真爛漫ニャ向日葵</t>
+          <t>RL1</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -25465,7 +25519,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="5" t="n">
         <v>0</v>
@@ -25477,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" s="5" t="n">
         <v>0</v>
@@ -25489,11 +25543,11 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Smasher죠</t>
+          <t>天真爛漫ニャ向日葵</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177" s="5" t="n">
         <v>0</v>
@@ -25517,7 +25571,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" s="5" t="n">
         <v>0</v>
@@ -25541,7 +25595,7 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>XyChëDëLiC</t>
+          <t>Smasher죠</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -25593,11 +25647,11 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>微笑Paty</t>
+          <t>XyChëDëLiC</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179" s="5" t="n">
         <v>0</v>
@@ -25633,7 +25687,7 @@
         <v>0</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" s="5" t="n">
         <v>0</v>
@@ -25645,7 +25699,7 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>VIRULENT死</t>
+          <t>微笑Paty</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -25685,10 +25739,10 @@
         <v>0</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P180" s="5" t="n">
         <v>1</v>
@@ -25697,52 +25751,104 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
+          <t>VIRULENT死</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
           <t>PinöyPioneer</t>
         </is>
       </c>
-      <c r="B181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="5" t="n">
+      <c r="B182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25839,7 +25945,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -26594,16 +26700,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>雪狼族(44), ・殺戮・(42), VainqueurJP(10), 雲淡風輕o(5), SkyCastIe(4), LeLien(4), 微笑Party(3), Phoenix(3)</t>
+          <t>雪狼族(45), ・殺戮・(43), VainqueurJP(10), 雲淡風輕o(5), SkyCastIe(4), LeLien(4), 微笑Party(3), Phoenix(3)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>雪狼族(43勝), VainqueurJP(7勝), LeLien(2勝), Relaх(2勝), ・殺戮・(1勝)</t>
+          <t>雪狼族(44勝), VainqueurJP(7勝), LeLien(2勝), Relaх(2勝), ・殺戮・(1勝)</t>
         </is>
       </c>
     </row>
@@ -26637,14 +26743,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族(20), 亗Luxúria亗(19), Kopitiam(11), 彡MukBANG彡(10), SkyCastIe(8), ーリベリオンー(7), 一SUN一(7), 美孚冰室(7)</t>
+          <t>ßบรнíïdо丶ๅ家族(20), 亗Luxúria亗(19), Kopitiam(11), 彡MukBANG彡(10), 美孚冰室(8), 微笑Party(8), SkyCastIe(8), ーリベリオンー(7)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -26709,16 +26815,16 @@
         <v>36</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>シェイド(29), ー麒麟ー(22), FLORISTS(15), ーリベリオンー(13), 一Arch(10), 一惡人谷一(10), ーEspoirー(9), Restart(8)</t>
+          <t>シェイド(30), ー麒麟ー(22), FLORISTS(16), ーリベリオンー(13), 一Arch(10), 一惡人谷一(10), ーEspoirー(9), Restart(8)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>シェイド(16勝), FLORISTS(7勝), 一Arch(6勝), ー麒麟ー(6勝), 一惡人谷一(5勝)</t>
+          <t>シェイド(16勝), FLORISTS(8勝), 一Arch(6勝), ー麒麟ー(6勝), 一惡人谷一(5勝)</t>
         </is>
       </c>
     </row>
@@ -26729,19 +26835,19 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(20), Outlawss(19), Иouver(17), ZirconiA(14), Restart(13), C0BRA(13), EIemento(12), Bagaиเ่(12)</t>
+          <t>亗Luxúria亗(21), Outlawss(19), Иouver(17), ZirconiA(14), Restart(13), C0BRA(13), EIemento(12), Bagaиเ่(12)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Restart(9勝), 亗Luxúria亗(7勝), C0BRA(4勝), ZirconiA(3勝), TheUniverse(3勝)</t>
+          <t>Restart(9勝), 亗Luxúria亗(8勝), C0BRA(4勝), ZirconiA(3勝), TheUniverse(3勝)</t>
         </is>
       </c>
     </row>
@@ -27031,11 +27137,11 @@
         <v>48</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo(33), 柿一門(19), 氣噗噗讓玻璃心碎一地(18), Maverickz(11), Unity(11), Myst(8), PONYTAIL(7), FLORISTS(6)</t>
+          <t>PokemonGo(33), 氣噗噗讓玻璃心碎一地(19), 柿一門(19), Maverickz(11), Unity(11), Myst(8), VainqueurJP(7), PONYTAIL(7)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -27123,16 +27229,16 @@
         <v>37</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓(30), 雲淡風輕o(22), RaиkSS(17), PONYTAIL(15), 微笑Party(12), 一SUN一(9), 廣寒宮(9), Maverickz(8)</t>
+          <t>當惡魔遇到殺手貓(31), 雲淡風輕o(22), RaиkSS(18), PONYTAIL(15), 微笑Party(12), 一SUN一(9), 廣寒宮(9), Maverickz(8)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS(14勝), PONYTAIL(14勝), 當惡魔遇到殺手貓(10勝), PokemonGO(3勝), TRAITORs(3勝)</t>
+          <t>RaиkSS(15勝), PONYTAIL(14勝), 當惡魔遇到殺手貓(10勝), PokemonGO(3勝), TRAITORs(3勝)</t>
         </is>
       </c>
     </row>
@@ -27189,10 +27295,10 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -27353,16 +27459,16 @@
         <v>57</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Pandora(35), Revenant(29), RëBîrth(28), ーEspoirー(15), 桜吹雪(15), 柿一門(14), ZirconiA(12), Restart(8)</t>
+          <t>Pandora(36), Revenant(29), RëBîrth(28), ーEspoirー(16), 柿一門(15), 桜吹雪(15), ZirconiA(12), Restart(8)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Revenant(15勝), Pandora(12勝), RëBîrth(6勝), Maverickz(3勝), ZirconiA(3勝)</t>
+          <t>Revenant(15勝), Pandora(13勝), RëBîrth(6勝), Maverickz(3勝), ZirconiA(3勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-14</t>
+          <t>2025-08-01 〜 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2151</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3394</v>
+        <v>0.3373</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1908</v>
+        <v>0.1961</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.3642</v>
+        <v>0.3618</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3214</v>
+        <v>0.3191</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>3</v>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>48</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.3478</v>
+        <v>0.3453</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>31</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>7</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3409</v>
+        <v>0.3383</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -846,51 +846,51 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>129</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="F11" s="5" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.4297</v>
+        <v>0.1085</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.5859</v>
+        <v>0.5891</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>17</v>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.2114</v>
+        <v>0.2097</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>21</v>
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>53</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4569</v>
+        <v>0.453</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.1616</v>
+        <v>0.16</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14</v>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.3673</v>
+        <v>0.3737</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>15</v>
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>27</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.2784</v>
+        <v>0.2755</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1400,19 +1400,19 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.3404</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
@@ -1446,51 +1446,51 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
         <v>83</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.6988</v>
+        <v>0.1928</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.1829</v>
+        <v>0.6988</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1596,51 +1596,51 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.2329</v>
+        <v>0.1486</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
         <v>73</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.1507</v>
+        <v>0.2329</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1671,101 +1671,101 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.7206</v>
+        <v>0.6667</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
         <v>68</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.7206</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.1493</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
         <v>66</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1515</v>
+        <v>0.1667</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.2069</v>
+        <v>0.2034</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>14</v>
@@ -2221,73 +2221,73 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>0.1176</v>
+        <v>0.4118</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>0.2059</v>
+        <v>0.1176</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>0.4242</v>
+        <v>0.2059</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>1</v>
@@ -2421,23 +2421,23 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Sangsaka</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>0.0769</v>
+        <v>0.1538</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>0</v>
@@ -2446,23 +2446,23 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Sangsaka</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.2692</v>
+        <v>0.0769</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>0</v>
@@ -2471,23 +2471,23 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.16</v>
+        <v>0.2692</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>0</v>
@@ -2500,19 +2500,19 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>2</v>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.2727</v>
+        <v>0.3043</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>10</v>
@@ -2721,23 +2721,23 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>0</v>
@@ -2746,23 +2746,23 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
         <v>17</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0</v>
+        <v>0.1765</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -3009,10 +3009,10 @@
         <v>0.2</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -3021,23 +3021,23 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E98" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -3059,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>0</v>
@@ -3071,11 +3071,11 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" s="5" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0</v>
@@ -3096,23 +3096,23 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -3121,23 +3121,23 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0</v>
@@ -3246,23 +3246,23 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>0</v>
@@ -3296,23 +3296,23 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0</v>
@@ -3321,23 +3321,23 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,67 +3346,67 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.125</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.7143</v>
+        <v>0.1429</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>6</v>
@@ -3421,23 +3421,23 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -3462,57 +3462,57 @@
         <v>3</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.1429</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -3534,10 +3534,10 @@
         <v>0.8333</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
@@ -3546,23 +3546,23 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0</v>
@@ -3571,23 +3571,23 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>22</v>
@@ -5614,61 +5614,61 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>7</v>
@@ -5677,127 +5677,127 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>2</v>
@@ -5824,85 +5824,85 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -6076,49 +6076,49 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6130,21 +6130,21 @@
         <v>20</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
@@ -6154,18 +6154,18 @@
         <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
@@ -6175,60 +6175,60 @@
         <v>4</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -6238,28 +6238,28 @@
         <v>6</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -6307,145 +6307,145 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D60" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D60" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E60" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>5</v>
@@ -6454,33 +6454,33 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
@@ -6490,91 +6490,91 @@
         <v>3</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -6585,38 +6585,38 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6627,11 +6627,11 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>5</v>
@@ -6648,56 +6648,56 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>3</v>
@@ -6711,86 +6711,86 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -6802,7 +6802,7 @@
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -7609,49 +7609,49 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -7666,88 +7666,88 @@
         <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>3</v>
@@ -7756,106 +7756,106 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
@@ -7876,91 +7876,91 @@
         <v>0</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -9605,12 +9605,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -9634,26 +9634,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
@@ -12157,7 +12157,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0818</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="3">
@@ -12170,10 +12170,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.205</v>
+        <v>0.2052</v>
       </c>
     </row>
     <row r="4">
@@ -12186,10 +12186,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4184</v>
+        <v>0.4182</v>
       </c>
     </row>
     <row r="5">
@@ -12202,10 +12202,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0786</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -12218,10 +12218,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2162</v>
+        <v>0.2163</v>
       </c>
     </row>
   </sheetData>
@@ -12235,7 +12235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12339,11 +12339,11 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:7勝, 一SUN一:4勝</t>
+          <t>Orzeca:7勝, 一SUN一:5勝</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Kaioken、TipsyTavern</t>
+          <t>cobraXverse、美孚冰室</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>TipsyTavern:1勝, Kaioken:1勝</t>
+          <t>cobraXverse:2勝</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、一惡人谷一</t>
+          <t>Kaioken、TipsyTavern</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一:2勝</t>
+          <t>TipsyTavern:1勝, Kaioken:1勝</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、一惡人谷一</t>
+          <t>Maverickz、一惡人谷一</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
+          <t>一惡人谷一:2勝</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、毛家村</t>
+          <t>Etërnîty、一惡人谷一</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>毛家村:2勝</t>
+          <t>Etërnîty:1勝, 一惡人谷一:1勝</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>一DEFIANCE、雲淡風輕o</t>
+          <t>CatlandTHM、毛家村</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:2勝</t>
+          <t>毛家村:2勝</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>MÏRÃGË、雲淡風輕o</t>
+          <t>一DEFIANCE、雲淡風輕o</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
+          <t>雲淡風輕o:2勝</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>CatlandTHM、雲淡風輕o</t>
+          <t>MÏRÃGË、雲淡風輕o</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:2勝</t>
+          <t>雲淡風輕o:1勝, MÏRÃGË:1勝</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、美孚冰室</t>
+          <t>CatlandTHM、雲淡風輕o</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝</t>
+          <t>雲淡風輕o:2勝</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、溫柔鄉</t>
+          <t>Döraè่mön、美孚冰室</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
+          <t>Döraè่mön:2勝</t>
         </is>
       </c>
     </row>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PONYTAIL</t>
+          <t>微笑Party、溫柔鄉</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -13884,30 +13884,30 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>微笑Party:1勝, 溫柔鄉:1勝</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Maverickz、PONYTAIL</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -13922,15 +13922,15 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
+          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
+          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
         </is>
       </c>
     </row>
@@ -13945,15 +13945,15 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:5勝</t>
+          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
         </is>
       </c>
     </row>
@@ -13968,15 +13968,15 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、TRAITORs</t>
+          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
+          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:5勝</t>
         </is>
       </c>
     </row>
@@ -13991,15 +13991,15 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
+          <t>PONYTAIL、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
+          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14014,15 +14014,15 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:6勝</t>
+          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>沙漠黑鷹:6勝</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14106,15 +14106,15 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
+          <t>RaиkSS:4勝</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、PONYTAIL</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝</t>
+          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、PONYTAIL</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:4勝</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14336,15 +14336,15 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14520,7 +14520,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14543,15 +14543,15 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14566,7 +14566,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 美孚冰室:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14942,7 +14942,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15609,7 +15609,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
@@ -15747,30 +15747,30 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15785,15 +15785,15 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15831,15 +15831,15 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16046,30 +16046,30 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:5勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16084,15 +16084,15 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:5勝</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
@@ -16314,13 +16314,36 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D177" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="D178" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16486,10 +16509,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -16590,10 +16613,10 @@
         <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
@@ -16642,10 +16665,10 @@
         <v>13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
@@ -16746,10 +16769,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -16798,10 +16821,10 @@
         <v>7</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -16902,59 +16925,59 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="J11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="O11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>129</v>
@@ -16963,53 +16986,53 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="G12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="K12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -17058,10 +17081,10 @@
         <v>14</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -17214,10 +17237,10 @@
         <v>14</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -17318,10 +17341,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -17890,10 +17913,10 @@
         <v>9</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -17942,10 +17965,10 @@
         <v>8</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
@@ -17994,10 +18017,10 @@
         <v>9</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
@@ -18098,10 +18121,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34">
@@ -18159,50 +18182,50 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="H35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="J35" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P35" s="5" t="n">
         <v>83</v>
@@ -18211,53 +18234,53 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -18471,102 +18494,102 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="I41" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="M41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L41" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="O41" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
         <v>73</v>
@@ -18627,102 +18650,102 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="I44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="M44" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="H45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="L45" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I45" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="N45" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>68</v>
@@ -18731,102 +18754,102 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>10</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>10</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>66</v>
@@ -18982,10 +19005,10 @@
         <v>10</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51">
@@ -19771,50 +19794,50 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H66" s="5" t="n">
+      <c r="M66" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O66" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
         <v>34</v>
@@ -19823,38 +19846,38 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="5" t="n">
         <v>0</v>
@@ -19863,7 +19886,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="5" t="n">
         <v>0</v>
@@ -19875,23 +19898,23 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>0</v>
@@ -19906,22 +19929,22 @@
         <v>0</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
@@ -20187,26 +20210,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Sangsaka</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" s="5" t="n">
         <v>1</v>
@@ -20218,19 +20241,19 @@
         <v>1</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P74" s="5" t="n">
         <v>26</v>
@@ -20239,29 +20262,29 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Sangsaka</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75" s="5" t="n">
         <v>1</v>
@@ -20270,16 +20293,16 @@
         <v>1</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O75" s="5" t="n">
         <v>0</v>
@@ -20291,29 +20314,29 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>1</v>
@@ -20322,22 +20345,22 @@
         <v>1</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
@@ -20386,10 +20409,10 @@
         <v>3</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -20438,10 +20461,10 @@
         <v>8</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
@@ -20811,102 +20834,102 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="5" t="n">
         <v>17</v>
@@ -21383,14 +21406,14 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>0</v>
@@ -21423,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P97" s="5" t="n">
         <v>10</v>
@@ -21435,14 +21458,14 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>0</v>
@@ -21460,10 +21483,10 @@
         <v>0</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>0</v>
@@ -21472,13 +21495,13 @@
         <v>0</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" s="5" t="n">
         <v>10</v>
@@ -21487,23 +21510,23 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>0</v>
@@ -21512,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>0</v>
@@ -21524,13 +21547,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" s="5" t="n">
         <v>10</v>
@@ -21539,32 +21562,32 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J100" s="5" t="n">
         <v>0</v>
@@ -21579,23 +21602,23 @@
         <v>0</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C101" s="5" t="n">
         <v>2</v>
@@ -21613,16 +21636,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="5" t="n">
         <v>0</v>
@@ -21643,14 +21666,14 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>0</v>
@@ -21674,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="5" t="n">
         <v>0</v>
@@ -21683,10 +21706,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P102" s="5" t="n">
         <v>9</v>
@@ -21903,17 +21926,17 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>0</v>
@@ -21934,19 +21957,19 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>2</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P107" s="5" t="n">
         <v>8</v>
@@ -21955,17 +21978,17 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0</v>
@@ -21977,28 +22000,28 @@
         <v>0</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="5" t="n">
         <v>8</v>
@@ -22007,17 +22030,17 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
@@ -22029,13 +22052,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K109" s="5" t="n">
         <v>0</v>
@@ -22059,32 +22082,32 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="5" t="n">
         <v>0</v>
@@ -22111,29 +22134,29 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>1</v>
@@ -22145,16 +22168,16 @@
         <v>0</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111" s="5" t="n">
         <v>8</v>
@@ -22163,11 +22186,11 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>0</v>
@@ -22182,13 +22205,13 @@
         <v>0</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="5" t="n">
         <v>0</v>
@@ -22197,29 +22220,29 @@
         <v>0</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>0</v>
@@ -22255,10 +22278,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P113" s="5" t="n">
         <v>7</v>
@@ -22267,7 +22290,7 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -22292,16 +22315,16 @@
         <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>0</v>
@@ -22310,7 +22333,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P114" s="5" t="n">
         <v>7</v>
@@ -22319,41 +22342,41 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="C115" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M115" s="5" t="n">
         <v>0</v>
@@ -22371,17 +22394,17 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>0</v>
@@ -22423,17 +22446,17 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>0</v>
@@ -22463,23 +22486,23 @@
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P117" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C118" s="5" t="n">
         <v>0</v>
@@ -22494,31 +22517,31 @@
         <v>0</v>
       </c>
       <c r="G118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P118" s="5" t="n">
         <v>6</v>
@@ -22527,11 +22550,11 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C119" s="5" t="n">
         <v>0</v>
@@ -22546,7 +22569,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
@@ -22579,11 +22602,11 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C120" s="5" t="n">
         <v>0</v>
@@ -22604,16 +22627,16 @@
         <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>0</v>
@@ -22622,7 +22645,7 @@
         <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P120" s="5" t="n">
         <v>6</v>
@@ -25909,7 +25932,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -25927,7 +25950,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -25945,7 +25968,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -25981,13 +26004,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -26005,7 +26028,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -26017,13 +26040,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -26654,16 +26677,16 @@
         <v>51</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ーEspoirー(19), Revenant(17), 厶pocalypse(15), SanctaTerra(15), C0BRA(15), 柿一門(13), EIemento(13), Bagaиเ่(13)</t>
+          <t>ーEspoirー(19), Revenant(18), 厶pocalypse(16), SanctaTerra(15), C0BRA(15), 柿一門(14), EIemento(13), Bagaиเ่(13)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(8勝), Restart(7勝), 柿一門(6勝), ーEspoirー(6勝), Revenant(5勝)</t>
+          <t>亗Luxúria亗(8勝), 柿一門(7勝), Restart(7勝), ーEspoirー(6勝), Revenant(5勝)</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26792,7 @@
         <v>45</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -26907,11 +26930,11 @@
         <v>47</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>一Arch(13), PokemonGo(12), FLORISTS(7), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
+          <t>一Arch(13), PokemonGo(12), FLORISTS(8), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -26953,16 +26976,16 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Unity(30), 黒の太陽(21), シェイド(19), xAEGISx(16), ーリベリオンー(13), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
+          <t>Unity(31), 黒の太陽(22), シェイド(20), xAEGISx(17), ーリベリオンー(13), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽(8勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
+          <t>黒の太陽(9勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
         </is>
       </c>
     </row>
@@ -27088,19 +27111,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(32), Kopitiam(26), ßบรнíïdо丶ๅ家族(26), MelonEmpire(10), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
+          <t>亗Luxúria亗(33), Kopitiam(27), ßบรнíïdо丶ๅ家族(26), MelonEmpire(10), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam(24勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
+          <t>Kopitiam(25勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
         </is>
       </c>
     </row>
@@ -27160,7 +27183,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -27252,16 +27275,16 @@
         <v>35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(28), RaиkSS(20), 當惡魔遇到殺手貓(17), 雲淡風輕o(17), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
+          <t>PONYTAIL(28), RaиkSS(21), 當惡魔遇到殺手貓(18), 雲淡風輕o(17), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(25勝), RaиkSS(16勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
+          <t>PONYTAIL(25勝), RaиkSS(17勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27436,16 +27459,16 @@
         <v>51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>柿一門(28), 義勇(21), 桜吹雪(18), 黄昏のえりしおん(16), ひよこりあ(16), Pandora(15), Restart(14), 氣噗噗讓玻璃心碎一地(12)</t>
+          <t>柿一門(28), 義勇(21), 桜吹雪(18), Pandora(16), 黄昏のえりしおん(16), ひよこりあ(16), Restart(14), 氣噗噗讓玻璃心碎一地(13)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>義勇(8勝), 柿一門(7勝), 氣噗噗讓玻璃心碎一地(4勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝)</t>
+          <t>義勇(8勝), 柿一門(7勝), 氣噗噗讓玻璃心碎一地(5勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-17</t>
+          <t>2025-08-01 〜 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2159</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3354</v>
+        <v>0.3394</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>30</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1961</v>
+        <v>0.1948</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2733</v>
+        <v>0.2781</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
@@ -846,76 +846,76 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.4264</v>
+        <v>0.1077</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.1085</v>
+        <v>0.5846</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>129</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.5891</v>
+        <v>0.4264</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.176</v>
+        <v>0.1825</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>32</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5372</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.513</v>
+        <v>0.5172</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>67</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5929</v>
+        <v>0.5877</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>54</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4954</v>
+        <v>0.4909</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>11</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.6226</v>
+        <v>0.6262</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>10</v>
@@ -1196,51 +1196,51 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.434</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.4381</v>
+        <v>0.1429</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.16</v>
+        <v>0.1683</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
@@ -1321,51 +1321,51 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
         <v>99</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.3737</v>
+        <v>0.2727</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.2755</v>
+        <v>0.3737</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.125</v>
+        <v>0.1237</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>10</v>
@@ -1446,51 +1446,51 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.1928</v>
+        <v>0.7024</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
         <v>83</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.6988</v>
+        <v>0.1928</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1546,51 +1546,51 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.5132</v>
+        <v>0.4416</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
         <v>76</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.4474</v>
+        <v>0.5132</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C46" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.1493</v>
+        <v>0.1471</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>5</v>
@@ -1771,23 +1771,23 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
         <v>60</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0</v>
@@ -1796,51 +1796,51 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>SЕRЕNIТY</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
         <v>60</v>
       </c>
       <c r="C49" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E49" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="F49" s="5" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C50" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D50" s="6" t="n">
-        <v>0.2034</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="F50" s="5" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1896,23 +1896,23 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.1091</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
@@ -1921,23 +1921,23 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.2963</v>
+        <v>0.2222</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -1946,23 +1946,23 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.2963</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2146,23 +2146,23 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>0.4118</v>
+        <v>0.4</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>1</v>
@@ -2171,76 +2171,76 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.4118</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>一DEFIANCE</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>0.3529</v>
+        <v>0.1471</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>一DEFIANCE</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>0.4118</v>
+        <v>0.3529</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C78" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.3043</v>
+        <v>0.2917</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>32</v>
@@ -3096,23 +3096,23 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0</v>
+        <v>0.7778</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -3121,23 +3121,23 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0</v>
@@ -3146,73 +3146,73 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1111</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>0</v>
@@ -3221,11 +3221,11 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C106" s="5" t="n">
         <v>0</v>
@@ -3234,10 +3234,10 @@
         <v>0</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0</v>
@@ -3246,23 +3246,23 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0.75</v>
+        <v>0.125</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>0</v>
@@ -3396,23 +3396,23 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.7143</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
@@ -3421,23 +3421,23 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -3446,23 +3446,23 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -3487,57 +3487,57 @@
         <v>3</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.1429</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -3612,7 +3612,7 @@
         <v>3</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>0</v>
@@ -3621,7 +3621,7 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -3634,7 +3634,7 @@
         <v>0.1667</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="n">
         <v>16</v>
@@ -3646,23 +3646,23 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>0</v>
@@ -3671,23 +3671,23 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C124" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F124" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G124" s="5" t="n">
         <v>0</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>45</v>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>11</v>
@@ -5509,43 +5509,43 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5593,70 +5593,70 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -5668,73 +5668,73 @@
         <v>25</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -5824,85 +5824,85 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -5913,38 +5913,38 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -5992,112 +5992,112 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -6109,84 +6109,84 @@
         <v>20</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
@@ -6196,25 +6196,25 @@
         <v>4</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
           <t>Unity</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>7</v>
@@ -6223,33 +6223,33 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
@@ -6259,130 +6259,130 @@
         <v>6</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>4</v>
@@ -6391,169 +6391,169 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D61" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D61" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E61" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D62" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -6564,23 +6564,23 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6592,79 +6592,79 @@
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -6690,56 +6690,56 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>3</v>
@@ -6753,59 +6753,59 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -7063,19 +7063,19 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>0</v>
@@ -7084,40 +7084,40 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>6</v>
@@ -7126,64 +7126,64 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -7194,28 +7194,28 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
@@ -7225,39 +7225,39 @@
         <v>5</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
@@ -7267,91 +7267,91 @@
         <v>5</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -9402,7 +9402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -9585,10 +9585,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -10997,26 +10997,26 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
@@ -11026,12 +11026,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
@@ -11055,26 +11055,26 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
@@ -11084,12 +11084,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
@@ -11113,30 +11113,30 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="60">
@@ -11287,26 +11287,26 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11316,26 +11316,26 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G66" s="6" t="n">
@@ -11345,7 +11345,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -11374,12 +11374,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
@@ -11403,7 +11403,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -11432,12 +11432,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11461,26 +11461,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
@@ -11490,55 +11490,55 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
@@ -11548,26 +11548,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -11577,26 +11577,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11606,26 +11606,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -11635,26 +11635,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
@@ -11664,7 +11664,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -11693,12 +11693,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
@@ -11722,12 +11722,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
@@ -11751,26 +11751,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11780,26 +11780,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11809,26 +11809,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11838,12 +11838,12 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11867,26 +11867,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E85" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11896,26 +11896,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11925,12 +11925,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11954,26 +11954,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11983,26 +11983,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -12012,26 +12012,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12041,58 +12041,29 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G91" s="6" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Maverickz</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12157,7 +12128,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0815</v>
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -12170,10 +12141,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2052</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="4">
@@ -12186,10 +12157,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4182</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="5">
@@ -12202,10 +12173,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="6">
@@ -12218,10 +12189,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2163</v>
+        <v>0.216</v>
       </c>
     </row>
   </sheetData>
@@ -13995,11 +13966,11 @@
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:4勝, PONYTAIL:1勝</t>
+          <t>RaиkSS:5勝, TRAITORs:5勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14129,15 +14100,15 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>AlmaVivaJP:4勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14123,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -14160,7 +14131,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14146,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14183,7 +14154,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14169,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14206,7 +14177,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14192,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14229,7 +14200,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14244,7 +14215,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14252,7 +14223,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14238,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14275,7 +14246,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝, Phoenix:1勝</t>
+          <t>RaиkSS:4勝</t>
         </is>
       </c>
     </row>
@@ -16561,10 +16532,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -16613,10 +16584,10 @@
         <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
@@ -16717,10 +16688,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
@@ -16934,154 +16905,154 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="G11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="5" t="n">
+      <c r="K11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>15</v>
-      </c>
       <c r="N13" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P13" s="5" t="n">
         <v>129</v>
@@ -17133,10 +17104,10 @@
         <v>12</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
@@ -17289,10 +17260,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
@@ -17393,10 +17364,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -17445,10 +17416,10 @@
         <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -17549,10 +17520,10 @@
         <v>10</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -17653,111 +17624,111 @@
         <v>8</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="E25" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="G26" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>11</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>105</v>
@@ -17913,59 +17884,59 @@
         <v>9</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>99</v>
@@ -17974,53 +17945,53 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="K31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="N31" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
@@ -18069,10 +18040,10 @@
         <v>1</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33">
@@ -18182,102 +18153,102 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G36" s="5" t="n">
+      <c r="H36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="J36" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>83</v>
@@ -18390,102 +18361,102 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>76</v>
@@ -18797,10 +18768,10 @@
         <v>10</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
@@ -18858,50 +18829,50 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>7</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P48" s="5" t="n">
         <v>60</v>
@@ -18910,47 +18881,47 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>SЕRЕNIТY</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L49" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H49" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O49" s="5" t="n">
         <v>0</v>
@@ -18962,53 +18933,53 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
@@ -19118,102 +19089,102 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G54" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H54" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I54" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P54" s="5" t="n">
         <v>54</v>
@@ -19222,50 +19193,50 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="M55" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55" s="5" t="n">
         <v>54</v>
@@ -19638,102 +19609,102 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O63" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" s="5" t="n">
         <v>34</v>
@@ -19742,50 +19713,50 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>一DEFIANCE</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C65" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" s="5" t="n">
         <v>34</v>
@@ -19794,50 +19765,50 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>一DEFIANCE</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
         <v>34</v>
@@ -20461,10 +20432,10 @@
         <v>8</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -21614,14 +21585,14 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>0</v>
@@ -21636,10 +21607,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>0</v>
@@ -21654,10 +21625,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P101" s="5" t="n">
         <v>9</v>
@@ -21666,11 +21637,11 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C102" s="5" t="n">
         <v>2</v>
@@ -21688,16 +21659,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="5" t="n">
         <v>0</v>
@@ -21718,14 +21689,14 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>0</v>
@@ -21749,7 +21720,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>0</v>
@@ -21770,14 +21741,14 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>0</v>
@@ -21804,13 +21775,13 @@
         <v>0</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" s="5" t="n">
         <v>0</v>
@@ -21822,17 +21793,17 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -21853,35 +21824,35 @@
         <v>0</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>0</v>
@@ -21899,38 +21870,38 @@
         <v>0</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C107" s="5" t="n">
         <v>0</v>
@@ -21966,10 +21937,10 @@
         <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P107" s="5" t="n">
         <v>8</v>
@@ -21978,17 +21949,17 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0</v>
@@ -22003,22 +21974,22 @@
         <v>0</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K108" s="5" t="n">
         <v>1</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
         <v>1</v>
@@ -22238,11 +22209,11 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>0</v>
@@ -22278,10 +22249,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P113" s="5" t="n">
         <v>7</v>
@@ -22290,11 +22261,11 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C114" s="5" t="n">
         <v>0</v>
@@ -22315,16 +22286,16 @@
         <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>0</v>
@@ -22333,7 +22304,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P114" s="5" t="n">
         <v>7</v>
@@ -22342,7 +22313,7 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -22367,16 +22338,16 @@
         <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M115" s="5" t="n">
         <v>0</v>
@@ -22385,7 +22356,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P115" s="5" t="n">
         <v>7</v>
@@ -22394,41 +22365,41 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M116" s="5" t="n">
         <v>0</v>
@@ -22446,17 +22417,17 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>0</v>
@@ -22498,17 +22469,17 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>0</v>
@@ -22538,13 +22509,13 @@
         <v>0</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -22654,17 +22625,17 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5" t="n">
         <v>0</v>
@@ -22694,10 +22665,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P121" s="5" t="n">
         <v>6</v>
@@ -22706,17 +22677,17 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>0</v>
@@ -22758,35 +22729,35 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123" s="5" t="n">
         <v>0</v>
@@ -22810,11 +22781,11 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" s="5" t="n">
         <v>0</v>
@@ -22826,19 +22797,19 @@
         <v>0</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" s="5" t="n">
         <v>0</v>
@@ -22850,13 +22821,13 @@
         <v>0</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -25932,7 +25903,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -25950,7 +25921,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -25974,7 +25945,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -25986,13 +25957,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -26010,7 +25981,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -26028,7 +25999,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -26046,7 +26017,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -26058,7 +26029,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -26700,16 +26671,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(45), 雪狼族(42), 沙漠黑鷹(41), 雲淡風輕o(17), 當惡魔遇到殺手貓(16), LeLien(13), ーリベリオンー(11), Unity(9)</t>
+          <t>・殺戮・(46), 雪狼族(43), 沙漠黑鷹(41), 雲淡風輕o(18), 當惡魔遇到殺手貓(17), LeLien(13), ーリベリオンー(11), Unity(9)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(41勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
+          <t>・殺戮・(42勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
         </is>
       </c>
     </row>
@@ -26884,16 +26855,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(40), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(18), TRAITORs(12), Phoenix(8), ・殺戮・(7)</t>
+          <t>AlmaVivaJP(41), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(19), TRAITORs(12), Phoenix(9), ・殺戮・(7)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(29勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
+          <t>AlmaVivaJP(30勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27042,14 +27013,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(12), 黒の太陽(11), ーEspoirー(10), Restart(6), xAEGISx(6)</t>
+          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(13), 黒の太陽(11), ーEspoirー(10), Restart(6), xAEGISx(6)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -27068,16 +27039,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(38), RaиkSS(27), VainqueurJP(27), PONYTAIL(23), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
+          <t>TRAITORs(39), RaиkSS(28), VainqueurJP(27), PONYTAIL(24), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(22勝), RaиkSS(9勝), PONYTAIL(8勝), VainqueurJP(8勝), AlmaVivaJP(5勝)</t>
+          <t>TRAITORs(23勝), RaиkSS(9勝), PONYTAIL(8勝), VainqueurJP(8勝), AlmaVivaJP(5勝)</t>
         </is>
       </c>
     </row>
@@ -27091,16 +27062,16 @@
         <v>41</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(22), Kopitiam(11), ーリベリオンー(10), ZirconiA(7), Иouver(7), 柿一門(5), 亗Luxúria亗(5), MelonEmpire(5)</t>
+          <t>一惡人谷一(22), ーリベリオンー(11), Kopitiam(11), ZirconiA(7), Иouver(7), Orzeca(5), 厶pocalypse(5), 柿一門(5)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(21勝), ーリベリオンー(8勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
+          <t>一惡人谷一(21勝), ーリベリオンー(9勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
         </is>
       </c>
     </row>
@@ -27206,7 +27177,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -27298,16 +27269,16 @@
         <v>52</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ひよこりあ(28), ーEspoirー(21), 義勇(20), 月下の集い(19), 桜吹雪(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
+          <t>ひよこりあ(29), ーEspoirー(22), 義勇(21), 桜吹雪(20), 月下の集い(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>義勇(11勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝), ーEspoirー(4勝)</t>
+          <t>義勇(11勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ーEspoirー(5勝), ZirconiA(5勝)</t>
         </is>
       </c>
     </row>
@@ -27341,19 +27312,19 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 柿一門(8), 桜吹雪(8), 微笑Party(7), ーEspoirー(7), EIemento(5)</t>
+          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 柿一門(9), 微笑Party(8), 桜吹雪(8), ーEspoirー(7), EIemento(5)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(10勝), Restart(9勝), 柿一門(4勝), 微笑Party(3勝), 一DEFIANCE(3勝)</t>
+          <t>亗Luxúria亗(10勝), Restart(9勝), 微笑Party(4勝), 柿一門(4勝), 一DEFIANCE(3勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-19</t>
+          <t>2025-08-01 〜 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2167</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3373</v>
+        <v>0.3353</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3394</v>
+        <v>0.3373</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>30</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1948</v>
+        <v>0.1935</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.3618</v>
+        <v>0.366</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>2</v>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>42</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2781</v>
+        <v>0.2763</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3191</v>
+        <v>0.3239</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -1096,51 +1096,51 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.3818</v>
+        <v>0.4865</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
         <v>110</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4909</v>
+        <v>0.3818</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4907</v>
+        <v>0.4954</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>9</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>32</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3404</v>
+        <v>0.3368</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.275</v>
+        <v>0.2716</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>1</v>
@@ -1775,19 +1775,19 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1967</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0</v>
@@ -1896,23 +1896,23 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
         <v>55</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.1091</v>
+        <v>0.2909</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
@@ -1921,23 +1921,23 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.2222</v>
+        <v>0.1091</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -1946,23 +1946,23 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.2963</v>
+        <v>0.2222</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.2703</v>
+        <v>0.2895</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>12</v>
@@ -2946,23 +2946,23 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
         <v>11</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>0</v>
+        <v>0.1818</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
@@ -2971,48 +2971,48 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -3021,48 +3021,48 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0</v>
@@ -3096,23 +3096,23 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0.7778</v>
+        <v>0</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -3221,48 +3221,48 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0</v>
@@ -3271,23 +3271,23 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>0</v>
@@ -3296,23 +3296,23 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0</v>
@@ -3321,23 +3321,23 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -3359,10 +3359,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -3384,35 +3384,35 @@
         <v>0.125</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.7143</v>
+        <v>0.375</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
@@ -3421,23 +3421,23 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -3446,23 +3446,23 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -3471,23 +3471,23 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3746,23 +3746,23 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -3771,23 +3771,23 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0</v>
@@ -3796,23 +3796,23 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G129" s="5" t="n">
         <v>0</v>
@@ -3821,17 +3821,17 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E130" s="5" t="n">
         <v>4</v>
@@ -3846,23 +3846,23 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G131" s="5" t="n">
         <v>0</v>
@@ -3871,23 +3871,23 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G132" s="5" t="n">
         <v>0</v>
@@ -3896,23 +3896,23 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0</v>
@@ -3921,23 +3921,23 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
@@ -3946,23 +3946,23 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G135" s="5" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -3984,10 +3984,10 @@
         <v>0</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0</v>
@@ -3996,20 +3996,20 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" s="5" t="n">
         <v>7</v>
@@ -4021,11 +4021,11 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C138" s="5" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>8</v>
@@ -4046,20 +4046,20 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>8</v>
@@ -4071,23 +4071,23 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E140" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G140" s="5" t="n">
         <v>0</v>
@@ -4471,23 +4471,23 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G156" s="5" t="n">
         <v>0</v>
@@ -4496,23 +4496,23 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G157" s="5" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
@@ -4537,7 +4537,7 @@
         <v>2</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G158" s="5" t="n">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
@@ -4562,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G159" s="5" t="n">
         <v>0</v>
@@ -4571,23 +4571,23 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -4612,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G161" s="5" t="n">
         <v>0</v>
@@ -4621,17 +4621,17 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E162" s="5" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -4662,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G163" s="5" t="n">
         <v>0</v>
@@ -4671,7 +4671,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G164" s="5" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -4721,7 +4721,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -4737,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G166" s="5" t="n">
         <v>0</v>
@@ -4746,7 +4746,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -4771,7 +4771,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -4796,7 +4796,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -4812,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G169" s="5" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G170" s="5" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0</v>
@@ -4871,23 +4871,23 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -4896,17 +4896,17 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
         <v>1</v>
@@ -4921,7 +4921,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>43</v>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>24</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>4</v>
@@ -5635,49 +5635,49 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -5689,73 +5689,73 @@
         <v>25</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -6160,138 +6160,138 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>ーEspoirー</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
@@ -6301,49 +6301,49 @@
         <v>6</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -7210,91 +7210,91 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>義勇</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -7306,136 +7306,136 @@
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7446,91 +7446,91 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
@@ -7540,88 +7540,88 @@
         <v>3</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>3</v>
@@ -7630,96 +7630,96 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D119" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
+          <t>xAEGISx</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
           <t>オアシステップ</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>一Arch</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
@@ -7729,7 +7729,7 @@
         <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -7966,61 +7966,61 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5" t="n">
         <v>4</v>
@@ -8029,96 +8029,96 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
@@ -8134,12 +8134,12 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
@@ -8149,55 +8149,55 @@
         <v>2</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -8209,21 +8209,21 @@
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
@@ -8239,64 +8239,64 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E150" s="5" t="n">
         <v>3</v>
@@ -8323,138 +8323,138 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
@@ -8464,39 +8464,39 @@
         <v>4</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
@@ -8506,193 +8506,193 @@
         <v>4</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E168" s="5" t="n">
         <v>3</v>
@@ -8701,40 +8701,40 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>4</v>
@@ -8743,12 +8743,12 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
@@ -8758,25 +8758,25 @@
         <v>1</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>1</v>
@@ -8785,7 +8785,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -8797,7 +8797,7 @@
         <v>10</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E173" s="5" t="n">
         <v>1</v>
@@ -8806,28 +8806,28 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -8839,10 +8839,10 @@
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176">
@@ -9121,75 +9121,75 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
@@ -9199,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -9217,21 +9217,21 @@
         <v>9</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
@@ -9241,25 +9241,25 @@
         <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195" s="5" t="n">
         <v>1</v>
@@ -9268,19 +9268,19 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
+          <t>ひよこりあ</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
           <t>月下の集い</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" s="5" t="n">
         <v>1</v>
@@ -9289,7 +9289,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -9301,84 +9301,84 @@
         <v>9</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
           <t>TRAITORs</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
@@ -9388,7 +9388,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9402,7 +9402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10417,12 +10417,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Outlawss</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
@@ -10446,12 +10446,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Outlawss</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
@@ -10475,7 +10475,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -10504,26 +10504,26 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
@@ -10533,12 +10533,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
@@ -10562,12 +10562,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
@@ -10591,12 +10591,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
@@ -10620,12 +10620,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -10678,26 +10678,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E44" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
@@ -10707,7 +10707,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -10765,7 +10765,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -10788,105 +10788,105 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.951</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.9</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
@@ -10910,26 +10910,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
@@ -10939,26 +10939,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
@@ -10968,55 +10968,55 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
@@ -11026,12 +11026,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
@@ -11055,26 +11055,26 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E57" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
@@ -11084,12 +11084,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
@@ -11113,55 +11113,55 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
@@ -11171,12 +11171,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -11200,55 +11200,55 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
@@ -11258,55 +11258,55 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.846</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11316,7 +11316,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -11345,12 +11345,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
@@ -11374,7 +11374,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -11403,12 +11403,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
@@ -11751,12 +11751,12 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11780,26 +11780,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11809,26 +11809,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11838,12 +11838,12 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11867,26 +11867,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11896,26 +11896,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E86" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11925,12 +11925,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11954,26 +11954,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11983,26 +11983,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -12012,26 +12012,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12041,29 +12041,58 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E91" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
+          <t>黒の太陽</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
           <t>AlmaVivaJP</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>AlmaVivaJP</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12128,7 +12157,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="3">
@@ -12141,10 +12170,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2049</v>
+        <v>0.2048</v>
       </c>
     </row>
     <row r="4">
@@ -12157,10 +12186,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.419</v>
+        <v>0.4192</v>
       </c>
     </row>
     <row r="5">
@@ -12176,7 +12205,7 @@
         <v>171</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0789</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -12189,10 +12218,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.216</v>
+        <v>0.2163</v>
       </c>
     </row>
   </sheetData>
@@ -13943,11 +13972,11 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:6勝, 亗Luxúria亗:5勝, MelonEmpire:5勝</t>
+          <t>MelonEmpire:6勝, Kopitiam:6勝, 亗Luxúria亗:5勝</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14428,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14407,7 +14436,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14451,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14430,7 +14459,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14474,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14453,7 +14482,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14497,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14476,7 +14505,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14520,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14499,7 +14528,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14543,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14522,7 +14551,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14537,15 +14566,15 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14589,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14568,7 +14597,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14612,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14591,7 +14620,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14635,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14614,7 +14643,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14658,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14637,7 +14666,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14681,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14660,7 +14689,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14704,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14698,7 +14727,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14706,7 +14735,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14750,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14729,7 +14758,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14773,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14752,7 +14781,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14796,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14775,7 +14804,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14819,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14798,7 +14827,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14842,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14821,7 +14850,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 美孚冰室:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14865,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14844,7 +14873,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14888,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14867,7 +14896,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14911,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14890,7 +14919,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14934,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14913,7 +14942,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14957,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14936,7 +14965,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14980,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14959,7 +14988,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14974,7 +15003,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -14982,7 +15011,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14997,7 +15026,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15005,7 +15034,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15049,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15028,7 +15057,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15043,7 +15072,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15051,7 +15080,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15066,7 +15095,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15074,7 +15103,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15118,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15097,7 +15126,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15141,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15120,7 +15149,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15135,7 +15164,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15143,7 +15172,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15187,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15166,7 +15195,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15210,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15189,7 +15218,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15204,7 +15233,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15212,7 +15241,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15256,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15235,7 +15264,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:1勝, 沙漠黑鷹:1勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -16480,10 +16509,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -16532,10 +16561,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -16584,10 +16613,10 @@
         <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -16636,10 +16665,10 @@
         <v>13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -16688,10 +16717,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
@@ -16740,10 +16769,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -17425,102 +17454,102 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="K21" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>110</v>
@@ -17572,10 +17601,10 @@
         <v>9</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24">
@@ -18092,10 +18121,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
@@ -18300,10 +18329,10 @@
         <v>12</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38">
@@ -18872,10 +18901,10 @@
         <v>10</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">
@@ -19089,50 +19118,50 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>4</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P53" s="5" t="n">
         <v>55</v>
@@ -19141,102 +19170,102 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H55" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I55" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P55" s="5" t="n">
         <v>54</v>
@@ -19496,10 +19525,10 @@
         <v>13</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -21273,23 +21302,23 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
@@ -21313,10 +21342,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P95" s="5" t="n">
         <v>11</v>
@@ -21325,26 +21354,26 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>0</v>
@@ -21371,13 +21400,13 @@
         <v>0</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -21417,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P97" s="5" t="n">
         <v>10</v>
@@ -21429,14 +21458,14 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>0</v>
@@ -21448,7 +21477,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>0</v>
@@ -21481,14 +21510,14 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>0</v>
@@ -21506,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>0</v>
@@ -21518,13 +21547,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="5" t="n">
         <v>10</v>
@@ -21533,23 +21562,23 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0</v>
@@ -21558,10 +21587,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" s="5" t="n">
         <v>0</v>
@@ -21570,13 +21599,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="5" t="n">
         <v>10</v>
@@ -21585,23 +21614,23 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -21625,13 +21654,13 @@
         <v>0</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -21845,14 +21874,14 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>0</v>
@@ -21864,13 +21893,13 @@
         <v>0</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="5" t="n">
         <v>0</v>
@@ -21879,16 +21908,16 @@
         <v>0</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P106" s="5" t="n">
         <v>9</v>
@@ -21897,14 +21926,14 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>0</v>
@@ -21931,25 +21960,25 @@
         <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -21974,25 +22003,25 @@
         <v>0</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P108" s="5" t="n">
         <v>8</v>
@@ -22001,11 +22030,11 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C109" s="5" t="n">
         <v>0</v>
@@ -22023,13 +22052,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
         <v>0</v>
@@ -22053,17 +22082,17 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5" t="n">
         <v>0</v>
@@ -22078,25 +22107,25 @@
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="5" t="n">
         <v>8</v>
@@ -22105,35 +22134,35 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K111" s="5" t="n">
         <v>0</v>
@@ -22157,17 +22186,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -22176,13 +22205,13 @@
         <v>0</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="5" t="n">
         <v>0</v>
@@ -22191,16 +22220,16 @@
         <v>0</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" s="5" t="n">
         <v>8</v>
@@ -22209,7 +22238,7 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -22240,53 +22269,53 @@
         <v>0</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="5" t="n">
         <v>0</v>
@@ -22307,17 +22336,17 @@
         <v>0</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C115" s="5" t="n">
         <v>0</v>
@@ -22338,16 +22367,16 @@
         <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M115" s="5" t="n">
         <v>0</v>
@@ -22356,7 +22385,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P115" s="5" t="n">
         <v>7</v>
@@ -22365,7 +22394,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -22390,16 +22419,16 @@
         <v>0</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M116" s="5" t="n">
         <v>0</v>
@@ -22408,7 +22437,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P116" s="5" t="n">
         <v>7</v>
@@ -22937,14 +22966,14 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>0</v>
@@ -22977,10 +23006,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P127" s="5" t="n">
         <v>5</v>
@@ -22989,14 +23018,14 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>0</v>
@@ -23041,14 +23070,14 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>0</v>
@@ -23087,20 +23116,20 @@
         <v>0</v>
       </c>
       <c r="P129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>0</v>
@@ -23145,14 +23174,14 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>0</v>
@@ -23197,14 +23226,14 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>0</v>
@@ -23237,10 +23266,10 @@
         <v>0</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" s="5" t="n">
         <v>4</v>
@@ -23249,20 +23278,20 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="5" t="n">
         <v>0</v>
@@ -23277,7 +23306,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" s="5" t="n">
         <v>0</v>
@@ -23301,23 +23330,23 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
@@ -23335,7 +23364,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="5" t="n">
         <v>0</v>
@@ -23353,20 +23382,20 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C135" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="5" t="n">
         <v>0</v>
@@ -23381,7 +23410,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" s="5" t="n">
         <v>0</v>
@@ -23405,23 +23434,23 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0</v>
@@ -23430,10 +23459,10 @@
         <v>0</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K136" s="5" t="n">
         <v>0</v>
@@ -23457,11 +23486,11 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C137" s="5" t="n">
         <v>0</v>
@@ -23497,10 +23526,10 @@
         <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P137" s="5" t="n">
         <v>4</v>
@@ -23509,14 +23538,14 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>0</v>
@@ -23534,16 +23563,16 @@
         <v>0</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="5" t="n">
         <v>0</v>
@@ -23555,20 +23584,20 @@
         <v>0</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>0</v>
@@ -23613,11 +23642,11 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C140" s="5" t="n">
         <v>0</v>
@@ -23653,7 +23682,7 @@
         <v>0</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
         <v>0</v>
@@ -24445,11 +24474,11 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C156" s="5" t="n">
         <v>0</v>
@@ -24485,10 +24514,10 @@
         <v>0</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P156" s="5" t="n">
         <v>2</v>
@@ -24497,17 +24526,17 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C157" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" s="5" t="n">
         <v>0</v>
@@ -24549,17 +24578,17 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
         <v>0</v>
@@ -24601,17 +24630,17 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" s="5" t="n">
         <v>0</v>
@@ -24653,17 +24682,17 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="5" t="n">
         <v>0</v>
@@ -24705,14 +24734,14 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D161" s="5" t="n">
         <v>0</v>
@@ -24757,11 +24786,11 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" s="5" t="n">
         <v>0</v>
@@ -24803,13 +24832,13 @@
         <v>0</v>
       </c>
       <c r="P162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -24861,11 +24890,11 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164" s="5" t="n">
         <v>0</v>
@@ -24880,7 +24909,7 @@
         <v>0</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="5" t="n">
         <v>0</v>
@@ -24913,7 +24942,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -24965,7 +24994,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -25017,14 +25046,14 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>0</v>
@@ -25036,7 +25065,7 @@
         <v>0</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" s="5" t="n">
         <v>0</v>
@@ -25069,7 +25098,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -25121,14 +25150,14 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>0</v>
@@ -25173,11 +25202,11 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" s="5" t="n">
         <v>0</v>
@@ -25195,7 +25224,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="5" t="n">
         <v>0</v>
@@ -25225,7 +25254,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -25241,13 +25270,13 @@
         <v>0</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" s="5" t="n">
         <v>0</v>
@@ -25277,7 +25306,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -25293,7 +25322,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -25320,7 +25349,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" s="5" t="n">
         <v>1</v>
@@ -25329,7 +25358,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -25345,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -25372,7 +25401,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" s="5" t="n">
         <v>1</v>
@@ -25381,7 +25410,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -25397,7 +25426,7 @@
         <v>0</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
@@ -25421,7 +25450,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174" s="5" t="n">
         <v>0</v>
@@ -25857,7 +25886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25939,7 +25968,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -25957,13 +25986,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25981,7 +26010,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25993,13 +26022,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -26011,13 +26040,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -26053,25 +26082,25 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>離脱(前半のみ)</t>
+          <t>新規参入(後半のみ)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -26080,7 +26109,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
@@ -26089,7 +26118,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -26098,7 +26127,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -26107,7 +26136,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -26116,7 +26145,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -26125,7 +26154,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -26134,7 +26163,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -26143,7 +26172,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -26152,7 +26181,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -26161,7 +26190,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>DoraemonSA</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -26170,7 +26199,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -26179,7 +26208,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>DoraemonSA</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -26188,7 +26217,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
@@ -26197,7 +26226,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -26206,7 +26235,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -26215,7 +26244,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>愛Eиdorphiиe</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -26224,7 +26253,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -26233,7 +26262,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>愛Eиdorphiиe</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -26242,7 +26271,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -26251,7 +26280,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -26260,7 +26289,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
@@ -26269,7 +26298,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -26287,7 +26316,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -26296,7 +26325,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>0</v>
@@ -26305,7 +26334,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -26314,7 +26343,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -26323,7 +26352,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -26332,7 +26361,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
@@ -26341,7 +26370,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -26359,7 +26388,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -26368,7 +26397,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>0</v>
@@ -26377,7 +26406,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -26386,7 +26415,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>0</v>
@@ -26395,7 +26424,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -26413,7 +26442,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -26422,7 +26451,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>0</v>
@@ -26431,7 +26460,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -26449,7 +26478,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -26467,7 +26496,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -26476,7 +26505,7 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>0</v>
@@ -26485,7 +26514,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -26503,7 +26532,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -26521,7 +26550,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -26539,7 +26568,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -26548,7 +26577,7 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>0</v>
@@ -26557,7 +26586,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -26575,7 +26604,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -26587,6 +26616,24 @@
         <v>5</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Ancîеnts</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>離脱(前半のみ)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26717,16 +26764,16 @@
         <v>69</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Revenant(43), MÏRÃGË(18), ZirconiA(17), 黄昏のえりしおん(12), 柿一門(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
+          <t>Revenant(43), MÏRÃGË(18), ZirconiA(17), 柿一門(13), 黄昏のえりしおん(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Revenant(17勝), Unity(5勝), Restart(4勝), MÏRÃGË(3勝), 黒の太陽(2勝)</t>
+          <t>Revenant(17勝), Unity(5勝), Restart(4勝), MÏRÃGË(3勝), ーArch(2勝)</t>
         </is>
       </c>
     </row>
@@ -26924,16 +26971,16 @@
         <v>38</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(53), ・殺戮・(51), 毛家村(42), 雲淡風輕o(18), 廣寒宮(9), 微笑Party(8), Oops(6), TheUniverse(6)</t>
+          <t>沙漠黑鷹(54), ・殺戮・(52), 毛家村(42), 雲淡風輕o(18), 廣寒宮(9), 微笑Party(8), Oops(6), TheUniverse(6)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(48勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
+          <t>沙漠黑鷹(49勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
         </is>
       </c>
     </row>
@@ -26993,16 +27040,16 @@
         <v>22</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(35), ßบรнíïdо丶ๅ家族(25), Kopitiam(20), SkyCastIe(17), MelonEmpire(9), 彡MukBANG彡(9), 微笑Party(6), Ancîеnts(5)</t>
+          <t>亗Luxúria亗(36), ßบรнíïdо丶ๅ家族(25), Kopitiam(21), SkyCastIe(17), MelonEmpire(10), 彡MukBANG彡(9), 微笑Party(6), Ancîеnts(5)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(16勝), SkyCastIe(13勝), ßบรнíïdо丶ๅ家族(11勝), MelonEmpire(6勝), ーリベリオンー(3勝)</t>
+          <t>亗Luxúria亗(16勝), SkyCastIe(13勝), ßบรнíïdо丶ๅ家族(11勝), MelonEmpire(7勝), ーリベリオンー(3勝)</t>
         </is>
       </c>
     </row>
@@ -27108,16 +27155,16 @@
         <v>62</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>義勇(29), ーEspoirー(19), オアシステップ(18), ー麒麟ー(17), 桜吹雪(17), Restart(14), 黄昏のえりしおん(14), 柿一門(11)</t>
+          <t>義勇(29), ーEspoirー(20), ー麒麟ー(18), オアシステップ(18), 桜吹雪(17), Restart(15), 黄昏のえりしおん(15), 柿一門(11)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>義勇(12勝), ー麒麟ー(6勝), オアシステップ(6勝), 磯野家(4勝), 柿一門(3勝)</t>
+          <t>義勇(12勝), ー麒麟ー(6勝), オアシステップ(6勝), 磯野家(4勝), Restart(3勝)</t>
         </is>
       </c>
     </row>
@@ -27358,10 +27405,10 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -27381,19 +27428,19 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>シェイド(24), 一Arch(16), xAEGISx(15), 黒の太陽(12), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
+          <t>シェイド(24), xAEGISx(16), 一Arch(16), 黒の太陽(12), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>シェイド(13勝), xAEGISx(7勝), 黒の太陽(6勝), ーリベリオンー(5勝), Unity(4勝)</t>
+          <t>シェイド(13勝), xAEGISx(8勝), 黒の太陽(6勝), ーリベリオンー(5勝), Unity(4勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-20</t>
+          <t>2025-08-01 〜 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2173</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3353</v>
+        <v>0.3393</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3373</v>
+        <v>0.3353</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>30</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.1923</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.366</v>
+        <v>0.3636</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3239</v>
+        <v>0.3217</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3383</v>
+        <v>0.3358</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.1825</v>
+        <v>0.1811</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>32</v>
@@ -946,51 +946,51 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>125</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.32</v>
+        <v>0.208</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.2097</v>
+        <v>0.32</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5285</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>9</v>
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.453</v>
+        <v>0.4576</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5172</v>
+        <v>0.5214</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>8</v>
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5877</v>
+        <v>0.5913</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>5</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.4865</v>
+        <v>0.4911</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>11</v>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>46</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.434</v>
+        <v>0.4299</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>19</v>
@@ -1271,51 +1271,51 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
         <v>102</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.5098</v>
+        <v>0.1667</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.1683</v>
+        <v>0.5098</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.2727</v>
+        <v>0.28</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>22</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>32</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3368</v>
+        <v>0.3333</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>16</v>
@@ -1446,51 +1446,51 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="D35" s="6" t="n">
-        <v>0.7024</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>29</v>
-      </c>
       <c r="G35" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.1928</v>
+        <v>0.7024</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.2436</v>
+        <v>0.2405</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>17</v>
@@ -1600,19 +1600,19 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C41" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.1486</v>
+        <v>0.1467</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>24</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>1</v>
@@ -1696,51 +1696,51 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.7206</v>
+        <v>0.1594</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
         <v>68</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.7206</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
@@ -1871,23 +1871,23 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
         <v>56</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.3036</v>
+        <v>0.2857</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0</v>
@@ -1896,23 +1896,23 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.2909</v>
+        <v>0.3036</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0</v>
@@ -3221,73 +3221,73 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.4444</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>0</v>
@@ -3296,23 +3296,23 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0</v>
@@ -3321,23 +3321,23 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -3362,7 +3362,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>0</v>
@@ -3371,23 +3371,23 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0</v>
@@ -3396,23 +3396,23 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
@@ -4396,23 +4396,23 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>知音丶酒吧</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G153" s="5" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Kitanjou</t>
+          <t>知音丶酒吧</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
@@ -4434,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G154" s="5" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>彡PAPAROCK彡</t>
+          <t>Kitanjou</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
@@ -4462,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G155" s="5" t="n">
         <v>0</v>
@@ -4471,7 +4471,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>彡PAPAROCK彡</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
@@ -4487,7 +4487,7 @@
         <v>2</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G156" s="5" t="n">
         <v>0</v>
@@ -4496,23 +4496,23 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G157" s="5" t="n">
         <v>0</v>
@@ -4521,23 +4521,23 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G158" s="5" t="n">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
@@ -4562,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G159" s="5" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
@@ -4587,7 +4587,7 @@
         <v>2</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>0</v>
@@ -4596,23 +4596,23 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G161" s="5" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -4637,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G162" s="5" t="n">
         <v>0</v>
@@ -4646,17 +4646,17 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E163" s="5" t="n">
         <v>1</v>
@@ -4671,7 +4671,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G164" s="5" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -4712,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G165" s="5" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -4746,7 +4746,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -4762,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G167" s="5" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -4796,7 +4796,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -4821,7 +4821,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="5" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -4896,23 +4896,23 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>43</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>9</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>12</v>
@@ -6412,166 +6412,166 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D62" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D62" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E62" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D63" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>4</v>
@@ -6580,7 +6580,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6592,16 +6592,16 @@
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6613,37 +6613,37 @@
         <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6655,7 +6655,7 @@
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
@@ -6664,22 +6664,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7126,43 +7126,43 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -7173,149 +7173,149 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>義勇</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -7327,70 +7327,70 @@
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>7</v>
@@ -7399,61 +7399,61 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
@@ -7462,43 +7462,43 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -7630,91 +7630,91 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t>一SUN一</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
           <t>當惡魔遇到殺手貓</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D120" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -7729,67 +7729,67 @@
         <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>3</v>
@@ -7798,106 +7798,106 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
@@ -7918,81 +7918,81 @@
         <v>0</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
@@ -8002,46 +8002,46 @@
         <v>3</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>4</v>
@@ -8050,117 +8050,117 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
+          <t>FLORISTS</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
           <t>Restart</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>シェイド</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
@@ -8170,76 +8170,76 @@
         <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -8251,21 +8251,21 @@
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
@@ -8281,64 +8281,64 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E152" s="5" t="n">
         <v>3</v>
@@ -8365,159 +8365,159 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
@@ -8527,133 +8527,133 @@
         <v>4</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -9402,7 +9402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10591,26 +10591,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
@@ -10620,12 +10620,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -10678,26 +10678,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
@@ -10707,7 +10707,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -10765,7 +10765,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -10788,105 +10788,105 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.9</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.889</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
@@ -10910,26 +10910,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
           <t>ーEspoirー</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>柿一門</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
@@ -10939,26 +10939,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
@@ -10968,55 +10968,55 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
@@ -11026,12 +11026,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
@@ -11055,26 +11055,26 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
@@ -11084,12 +11084,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
@@ -11113,55 +11113,55 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D59" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
@@ -11171,12 +11171,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -11200,55 +11200,55 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.846</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
@@ -11258,55 +11258,55 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.833</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11316,7 +11316,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -11345,12 +11345,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
@@ -11374,7 +11374,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -11403,12 +11403,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
@@ -11432,12 +11432,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11461,26 +11461,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
@@ -11490,55 +11490,55 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
@@ -11548,26 +11548,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -11577,26 +11577,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11606,26 +11606,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -11635,26 +11635,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
@@ -11664,7 +11664,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -11693,12 +11693,12 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
@@ -11722,12 +11722,12 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
@@ -11751,26 +11751,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E81" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G81" s="6" t="n">
@@ -11780,12 +11780,12 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11809,26 +11809,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11838,26 +11838,26 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E84" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11867,12 +11867,12 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11896,26 +11896,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11925,26 +11925,26 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E87" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11954,12 +11954,12 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11983,26 +11983,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -12012,26 +12012,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12041,26 +12041,26 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G91" s="6" t="n">
@@ -12070,29 +12070,58 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E92" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
+          <t>黒の太陽</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
           <t>AlmaVivaJP</t>
         </is>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>AlmaVivaJP</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12157,7 +12186,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.081</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -12170,10 +12199,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2048</v>
+        <v>0.2053</v>
       </c>
     </row>
     <row r="4">
@@ -12186,10 +12215,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4192</v>
+        <v>0.4203</v>
       </c>
     </row>
     <row r="5">
@@ -12205,7 +12234,7 @@
         <v>171</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="6">
@@ -12221,7 +12250,7 @@
         <v>470</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2163</v>
+        <v>0.2154</v>
       </c>
     </row>
   </sheetData>
@@ -12235,7 +12264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12293,11 +12322,11 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:23勝</t>
+          <t>雪狼族:24勝</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12755,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、亗Luxúria亗</t>
+          <t>一SUN一、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -12734,7 +12763,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
+          <t>當惡魔遇到殺手貓:3勝</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12778,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
+          <t>Kopitiam、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -12757,7 +12786,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝</t>
+          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
         </is>
       </c>
     </row>
@@ -12772,15 +12801,15 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、柿一門</t>
+          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>AlmaVivaJP:3勝</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12824,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Иouver、ーリベリオンー</t>
+          <t>ーリベリオンー、柿一門</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -12818,7 +12847,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>cobraXverse、微笑Party</t>
+          <t>Иouver、ーリベリオンー</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -12826,7 +12855,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, cobraXverse:1勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12870,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、雲淡風輕o</t>
+          <t>cobraXverse、微笑Party</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -12849,7 +12878,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝</t>
+          <t>微笑Party:1勝, cobraXverse:1勝</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12893,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹</t>
+          <t>Phoenix、雲淡風輕o</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -12872,7 +12901,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>Phoenix:2勝</t>
         </is>
       </c>
     </row>
@@ -12887,7 +12916,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Anino、ouтcasт</t>
+          <t>・殺戮・、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -12895,7 +12924,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Anino:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12939,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Myst、VainqueurJP</t>
+          <t>Anino、ouтcasт</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -12918,7 +12947,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Anino:2勝</t>
         </is>
       </c>
     </row>
@@ -12933,7 +12962,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst</t>
+          <t>Myst、VainqueurJP</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -12941,7 +12970,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12985,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Unity、海洋之心</t>
+          <t>Maverickz、Myst</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -12964,7 +12993,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -12979,7 +13008,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity</t>
+          <t>Unity、海洋之心</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -13002,7 +13031,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、一DEFIANCE</t>
+          <t>Phoenix、Unity</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -13010,7 +13039,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13054,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、Иouver</t>
+          <t>Maverickz、一DEFIANCE</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -13033,7 +13062,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13077,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社、雲淡風輕o</t>
+          <t>VainqueurJP、Иouver</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -13056,7 +13085,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13071,7 +13100,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Иouver、雲淡風輕o</t>
+          <t>東京熱株式會社、雲淡風輕o</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -13079,7 +13108,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, Иouver:1勝</t>
+          <t>東京熱株式會社:2勝</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13123,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、VainqueurJP</t>
+          <t>Иouver、雲淡風輕o</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -13102,7 +13131,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>雲淡風輕o:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13146,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Myst、Unity</t>
+          <t>Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -13125,7 +13154,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Unity:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13169,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、Myst</t>
+          <t>Myst、Unity</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -13148,7 +13177,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Etërnîty:1勝</t>
+          <t>Myst:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13192,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、SkyCastIe</t>
+          <t>Etërnîty、Myst</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -13171,7 +13200,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:1勝, Maverickz:1勝</t>
+          <t>Myst:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13215,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ーリベリオンー</t>
+          <t>Maverickz、SkyCastIe</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -13194,7 +13223,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>SkyCastIe:1勝, Maverickz:1勝</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13238,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、天機</t>
+          <t>xAEGISx、ーリベリオンー</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -13217,7 +13246,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:2勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13261,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴</t>
+          <t>Etërnîty、天機</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -13240,7 +13269,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 心晴:1勝</t>
+          <t>Etërnîty:2勝</t>
         </is>
       </c>
     </row>
@@ -13255,7 +13284,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
+          <t>天機、心晴</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -13263,7 +13292,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地:2勝</t>
+          <t>天機:1勝, 心晴:1勝</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13307,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、柿一門</t>
+          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -13286,7 +13315,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo:2勝</t>
+          <t>氣噗噗讓玻璃心碎一地:2勝</t>
         </is>
       </c>
     </row>
@@ -13301,7 +13330,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Myst</t>
+          <t>PokemonGo、柿一門</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -13309,7 +13338,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>PokemonGo:2勝</t>
         </is>
       </c>
     </row>
@@ -13324,7 +13353,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Myst、雲淡風輕o</t>
+          <t>Döraè่mön、Myst</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -13347,7 +13376,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、微笑Party</t>
+          <t>Myst、雲淡風輕o</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
@@ -13355,7 +13384,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13399,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、Vanartroops</t>
+          <t>Maverickz、微笑Party</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -13378,7 +13407,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13422,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、溫柔鄉</t>
+          <t>SkyCastIe、Vanartroops</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
@@ -13401,7 +13430,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>SkyCastIe:2勝</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13445,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、VainqueurJP</t>
+          <t>VainqueurJP、溫柔鄉</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -13424,7 +13453,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13468,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>一SUN一、當惡魔遇到殺手貓</t>
+          <t>RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -13447,7 +13476,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15078,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、Restart、ー麒麟ー</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15072,7 +15101,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15080,7 +15109,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15124,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15103,7 +15132,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15147,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15126,7 +15155,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15170,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15149,7 +15178,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15193,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15172,7 +15201,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15216,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15195,7 +15224,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15210,7 +15239,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15218,7 +15247,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15262,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15241,7 +15270,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15285,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15264,7 +15293,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15308,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15302,7 +15331,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15325,7 +15354,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15333,7 +15362,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15377,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15356,7 +15385,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15400,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15379,7 +15408,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15423,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15402,7 +15431,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15446,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15425,7 +15454,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15469,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15448,7 +15477,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15492,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15471,7 +15500,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15486,7 +15515,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15494,7 +15523,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15538,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15517,7 +15546,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15561,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15540,7 +15569,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15584,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15563,7 +15592,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15578,7 +15607,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15586,7 +15615,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15630,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15609,7 +15638,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15653,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15632,7 +15661,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15676,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15655,7 +15684,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15699,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15678,7 +15707,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15722,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
@@ -15701,7 +15730,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15745,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15724,7 +15753,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15768,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
@@ -15747,7 +15776,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15791,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -15770,30 +15799,30 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15808,15 +15837,15 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15860,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15839,7 +15868,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15854,15 +15883,15 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15906,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15900,7 +15929,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -15908,7 +15937,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15952,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -15931,7 +15960,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15975,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -15954,7 +15983,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15998,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
@@ -15992,7 +16021,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16000,7 +16029,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16044,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -16023,7 +16052,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16067,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16046,7 +16075,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16090,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -16069,30 +16098,30 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:5勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16107,15 +16136,15 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:5勝</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16159,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16153,7 +16182,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16176,7 +16205,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -16199,7 +16228,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16207,7 +16236,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16251,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -16230,7 +16259,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16274,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
@@ -16268,7 +16297,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -16276,7 +16305,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16320,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
@@ -16299,7 +16328,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -16314,7 +16343,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -16337,13 +16366,36 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D178" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="D179" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16509,10 +16561,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -16561,10 +16613,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
@@ -16613,10 +16665,10 @@
         <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
@@ -16665,10 +16717,10 @@
         <v>13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
@@ -16769,10 +16821,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -16925,10 +16977,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -17133,59 +17185,59 @@
         <v>12</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>13</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>11</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
         <v>125</v>
@@ -17194,53 +17246,53 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>13</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
@@ -17289,10 +17341,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
@@ -17341,10 +17393,10 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -17393,10 +17445,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -17445,10 +17497,10 @@
         <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
@@ -17497,10 +17549,10 @@
         <v>10</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
@@ -17705,10 +17757,10 @@
         <v>6</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
@@ -17818,35 +17870,35 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="J28" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>10</v>
@@ -17855,13 +17907,13 @@
         <v>7</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P28" s="5" t="n">
         <v>102</v>
@@ -17870,35 +17922,35 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="H29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>10</v>
@@ -17907,16 +17959,16 @@
         <v>7</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
@@ -17965,10 +18017,10 @@
         <v>9</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -18121,10 +18173,10 @@
         <v>12</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34">
@@ -18182,50 +18234,50 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="H35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="J35" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P35" s="5" t="n">
         <v>84</v>
@@ -18234,53 +18286,53 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
@@ -18381,10 +18433,10 @@
         <v>2</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
@@ -18537,10 +18589,10 @@
         <v>9</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
@@ -18702,102 +18754,102 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>4</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>4</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J46" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>68</v>
@@ -19066,50 +19118,50 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="F52" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52" s="5" t="n">
         <v>56</v>
@@ -19118,53 +19170,53 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54">
@@ -21874,11 +21926,11 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" s="5" t="n">
         <v>0</v>
@@ -21893,28 +21945,28 @@
         <v>0</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" s="5" t="n">
         <v>2</v>
@@ -21926,14 +21978,14 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>0</v>
@@ -21945,13 +21997,13 @@
         <v>0</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
@@ -21960,16 +22012,16 @@
         <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P107" s="5" t="n">
         <v>9</v>
@@ -21978,14 +22030,14 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="5" t="n">
         <v>0</v>
@@ -22012,29 +22064,29 @@
         <v>0</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N108" s="5" t="n">
         <v>2</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C109" s="5" t="n">
         <v>0</v>
@@ -22070,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P109" s="5" t="n">
         <v>8</v>
@@ -22082,11 +22134,11 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C110" s="5" t="n">
         <v>0</v>
@@ -22107,25 +22159,25 @@
         <v>0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="5" t="n">
         <v>8</v>
@@ -22134,7 +22186,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -22156,28 +22208,28 @@
         <v>0</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="5" t="n">
         <v>8</v>
@@ -22186,17 +22238,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -22208,13 +22260,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K112" s="5" t="n">
         <v>0</v>
@@ -22238,17 +22290,17 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>0</v>
@@ -22269,10 +22321,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0</v>
@@ -22281,7 +22333,7 @@
         <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" s="5" t="n">
         <v>8</v>
@@ -24318,7 +24370,7 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>知音丶酒吧</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
@@ -24346,10 +24398,10 @@
         <v>0</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="5" t="n">
         <v>0</v>
@@ -24361,7 +24413,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P153" s="5" t="n">
         <v>2</v>
@@ -24370,11 +24422,11 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Kitanjou</t>
+          <t>知音丶酒吧</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C154" s="5" t="n">
         <v>0</v>
@@ -24398,10 +24450,10 @@
         <v>0</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" s="5" t="n">
         <v>0</v>
@@ -24422,11 +24474,11 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>彡PAPAROCK彡</t>
+          <t>Kitanjou</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C155" s="5" t="n">
         <v>0</v>
@@ -24435,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F155" s="5" t="n">
         <v>0</v>
@@ -24474,7 +24526,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>一SPY乂FäMILY一</t>
+          <t>彡PAPAROCK彡</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
@@ -24487,7 +24539,7 @@
         <v>0</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5" t="n">
         <v>0</v>
@@ -24514,10 +24566,10 @@
         <v>0</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P156" s="5" t="n">
         <v>2</v>
@@ -24526,11 +24578,11 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>UnityJP</t>
+          <t>一SPY乂FäMILY一</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C157" s="5" t="n">
         <v>0</v>
@@ -24566,10 +24618,10 @@
         <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" s="5" t="n">
         <v>2</v>
@@ -24578,17 +24630,17 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>WHITEBONE</t>
+          <t>UnityJP</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" s="5" t="n">
         <v>0</v>
@@ -24630,17 +24682,17 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Valhalla家</t>
+          <t>WHITEBONE</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
         <v>0</v>
@@ -24682,17 +24734,17 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>Valhalla家</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" s="5" t="n">
         <v>0</v>
@@ -24734,17 +24786,17 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="5" t="n">
         <v>0</v>
@@ -24786,14 +24838,14 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>0</v>
@@ -24838,11 +24890,11 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" s="5" t="n">
         <v>0</v>
@@ -24884,13 +24936,13 @@
         <v>0</v>
       </c>
       <c r="P163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -24942,11 +24994,11 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" s="5" t="n">
         <v>0</v>
@@ -24961,7 +25013,7 @@
         <v>0</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="5" t="n">
         <v>0</v>
@@ -24994,7 +25046,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -25046,7 +25098,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -25098,14 +25150,14 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>0</v>
@@ -25117,7 +25169,7 @@
         <v>0</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="5" t="n">
         <v>0</v>
@@ -25150,7 +25202,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -25202,14 +25254,14 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170" s="5" t="n">
         <v>0</v>
@@ -25254,11 +25306,11 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" s="5" t="n">
         <v>0</v>
@@ -25276,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171" s="5" t="n">
         <v>0</v>
@@ -25306,7 +25358,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -25322,13 +25374,13 @@
         <v>0</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" s="5" t="n">
         <v>0</v>
@@ -25358,7 +25410,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -25374,7 +25426,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -25401,7 +25453,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P173" s="5" t="n">
         <v>1</v>
@@ -25992,7 +26044,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -26004,13 +26056,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CRUSHSA</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -26028,7 +26080,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>CRUSHSA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -26741,16 +26793,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>雪狼族(45), ・殺戮・(43), VainqueurJP(10), 雲淡風輕o(5), SkyCastIe(4), LeLien(4), 微笑Party(3), Phoenix(3)</t>
+          <t>雪狼族(46), ・殺戮・(44), VainqueurJP(10), 雲淡風輕o(5), SkyCastIe(4), LeLien(4), 微笑Party(3), Phoenix(3)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>雪狼族(44勝), VainqueurJP(7勝), LeLien(2勝), Relaх(2勝), ・殺戮・(1勝)</t>
+          <t>雪狼族(45勝), VainqueurJP(7勝), LeLien(2勝), Relaх(2勝), ・殺戮・(1勝)</t>
         </is>
       </c>
     </row>
@@ -26787,16 +26839,16 @@
         <v>39</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族(20), 亗Luxúria亗(19), Kopitiam(11), 彡MukBANG彡(10), 美孚冰室(8), 微笑Party(8), SkyCastIe(8), ーリベリオンー(7)</t>
+          <t>ßบรнíïdо丶ๅ家族(20), 亗Luxúria亗(19), Kopitiam(11), 彡MukBANG彡(10), 微笑Party(9), 美孚冰室(9), ーリベリオンー(8), SkyCastIe(8)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族(10勝), 彡MukBANG彡(7勝), ーリベリオンー(6勝), SkyCastIe(6勝), Orzeca(4勝)</t>
+          <t>ßบรнíïdо丶ๅ家族(10勝), ーリベリオンー(7勝), 彡MukBANG彡(7勝), SkyCastIe(6勝), Orzeca(4勝)</t>
         </is>
       </c>
     </row>
@@ -26856,16 +26908,16 @@
         <v>36</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>シェイド(30), ー麒麟ー(22), FLORISTS(16), ーリベリオンー(13), 一Arch(10), 一惡人谷一(10), ーEspoirー(9), Restart(8)</t>
+          <t>シェイド(30), ー麒麟ー(23), FLORISTS(17), ーリベリオンー(13), 一Arch(10), 一惡人谷一(10), Restart(9), ーEspoirー(9)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>シェイド(16勝), FLORISTS(8勝), 一Arch(6勝), ー麒麟ー(6勝), 一惡人谷一(5勝)</t>
+          <t>シェイド(16勝), FLORISTS(9勝), 一Arch(6勝), ー麒麟ー(6勝), 一惡人谷一(5勝)</t>
         </is>
       </c>
     </row>
@@ -26879,16 +26931,16 @@
         <v>50</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(21), Outlawss(19), Иouver(17), ZirconiA(14), Restart(13), C0BRA(13), EIemento(12), Bagaиเ่(12)</t>
+          <t>亗Luxúria亗(22), Outlawss(19), Иouver(17), ZirconiA(14), Restart(13), C0BRA(13), EIemento(12), Bagaиเ่(12)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Restart(9勝), 亗Luxúria亗(8勝), C0BRA(4勝), ZirconiA(3勝), TheUniverse(3勝)</t>
+          <t>亗Luxúria亗(9勝), Restart(9勝), C0BRA(4勝), ZirconiA(3勝), TheUniverse(3勝)</t>
         </is>
       </c>
     </row>
@@ -26925,16 +26977,16 @@
         <v>34</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Unity(27), 一Arch(19), Phoenix(18), xAEGISx(17), シェイド(12), VainqueurJP(11), ーリベリオンー(9), 黒の太陽(5)</t>
+          <t>Unity(27), Phoenix(19), 一Arch(19), xAEGISx(18), シェイド(13), VainqueurJP(11), ーリベリオンー(9), 黒の太陽(5)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Unity(12勝), Phoenix(8勝), 一Arch(7勝), シェイド(5勝), VainqueurJP(5勝)</t>
+          <t>Unity(12勝), Phoenix(8勝), 一Arch(7勝), シェイド(6勝), VainqueurJP(5勝)</t>
         </is>
       </c>
     </row>
@@ -27178,16 +27230,16 @@
         <v>48</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo(33), 氣噗噗讓玻璃心碎一地(19), 柿一門(19), Maverickz(11), Unity(11), Myst(8), VainqueurJP(7), PONYTAIL(7)</t>
+          <t>PokemonGo(33), 氣噗噗讓玻璃心碎一地(19), 柿一門(19), Maverickz(11), Unity(11), PONYTAIL(8), VainqueurJP(8), Myst(8)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地(11勝), PokemonGo(9勝), Unity(7勝), PONYTAIL(6勝), VainqueurJP(6勝)</t>
+          <t>氣噗噗讓玻璃心碎一地(11勝), PokemonGo(9勝), PONYTAIL(7勝), Unity(7勝), VainqueurJP(6勝)</t>
         </is>
       </c>
     </row>
@@ -27270,16 +27322,16 @@
         <v>37</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓(31), 雲淡風輕o(22), RaиkSS(18), PONYTAIL(15), 微笑Party(12), 一SUN一(9), 廣寒宮(9), Maverickz(8)</t>
+          <t>當惡魔遇到殺手貓(32), 雲淡風輕o(22), RaиkSS(18), PONYTAIL(15), 微笑Party(12), 一SUN一(10), 廣寒宮(9), Maverickz(8)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS(15勝), PONYTAIL(14勝), 當惡魔遇到殺手貓(10勝), PokemonGO(3勝), TRAITORs(3勝)</t>
+          <t>RaиkSS(15勝), PONYTAIL(14勝), 當惡魔遇到殺手貓(11勝), PokemonGO(3勝), TRAITORs(3勝)</t>
         </is>
       </c>
     </row>
@@ -27336,10 +27388,10 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -27497,14 +27549,14 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Pandora(36), Revenant(29), RëBîrth(28), ーEspoirー(16), 柿一門(15), 桜吹雪(15), ZirconiA(12), Restart(8)</t>
+          <t>Pandora(36), Revenant(30), RëBîrth(29), ーEspoirー(16), 柿一門(15), 桜吹雪(15), ZirconiA(12), Restart(8)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-21</t>
+          <t>2025-08-01 〜 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2182</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>57</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3393</v>
+        <v>0.3373</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1923</v>
+        <v>0.1975</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
@@ -825,19 +825,19 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3358</v>
+        <v>0.3333</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>1</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1077</v>
+        <v>0.1069</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>22</v>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.5846</v>
+        <v>0.5878</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>17</v>
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.4264</v>
+        <v>0.4231</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>14</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.1811</v>
+        <v>0.1797</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>32</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5285</v>
+        <v>0.5242</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
@@ -1171,51 +1171,51 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.6262</v>
+        <v>0.4352</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
         <v>107</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.4299</v>
+        <v>0.6262</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.1748</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>15</v>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.28</v>
+        <v>0.2772</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>22</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>37</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.3737</v>
+        <v>0.37</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>15</v>
@@ -1371,51 +1371,51 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
         <v>97</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.1237</v>
+        <v>0.3402</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1237</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.1905</v>
+        <v>0.1882</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>24</v>
@@ -1600,13 +1600,13 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.1467</v>
+        <v>0.1447</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>24</v>
@@ -1646,48 +1646,48 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.1449</v>
+        <v>0.6571</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.1571</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>2</v>
@@ -1696,26 +1696,26 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
         <v>69</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.1594</v>
+        <v>0.1449</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1775,19 +1775,19 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.1967</v>
+        <v>0.1935</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.5789</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>14</v>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.2895</v>
+        <v>0.2821</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>12</v>
@@ -2396,23 +2396,23 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
         <v>27</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0</v>
+        <v>0.1852</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G73" s="5" t="n">
         <v>0</v>
@@ -2421,23 +2421,23 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>0</v>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.2917</v>
+        <v>0.32</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>11</v>
@@ -2921,23 +2921,23 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
         <v>12</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
@@ -2946,23 +2946,23 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>20</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>VIRULENT死</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -4621,23 +4621,23 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G162" s="5" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -4662,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G163" s="5" t="n">
         <v>0</v>
@@ -4671,17 +4671,17 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E164" s="5" t="n">
         <v>1</v>
@@ -4696,7 +4696,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -4712,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G165" s="5" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -4737,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G166" s="5" t="n">
         <v>0</v>
@@ -4746,7 +4746,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -4771,7 +4771,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G168" s="5" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -4821,7 +4821,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -4846,7 +4846,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G171" s="5" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G172" s="5" t="n">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -4912,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -4937,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>TËMPËST</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>RL1</t>
+          <t>TËMPËST</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -4987,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G176" s="5" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>天真爛漫ニャ向日葵</t>
+          <t>RL1</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -5021,7 +5021,7 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Smasher죠</t>
+          <t>天真爛漫ニャ向日葵</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -5037,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G178" s="5" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>XyChëDëLiC</t>
+          <t>Smasher죠</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -5071,7 +5071,7 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>微笑Paty</t>
+          <t>XyChëDëLiC</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -5087,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G180" s="5" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>VIRULENT死</t>
+          <t>微笑Paty</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>23</v>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>4</v>
@@ -5572,133 +5572,133 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -5710,84 +5710,84 @@
         <v>25</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -5797,70 +5797,70 @@
         <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -5992,61 +5992,61 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>7</v>
@@ -6055,91 +6055,91 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -6151,79 +6151,79 @@
         <v>20</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
           <t>ーEspoirー</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6235,7 +6235,7 @@
         <v>20</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>2</v>
@@ -6244,12 +6244,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
@@ -6259,7 +6259,7 @@
         <v>4</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -6412,187 +6412,187 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D63" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D63" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E63" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>4</v>
@@ -6601,7 +6601,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6613,16 +6613,16 @@
         <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6634,37 +6634,37 @@
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6676,7 +6676,7 @@
         <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0</v>
@@ -6811,124 +6811,124 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>4</v>
@@ -6937,22 +6937,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -6979,211 +6979,211 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -7194,149 +7194,149 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D97" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
           <t>ZirconiA</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>義勇</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -7348,52 +7348,52 @@
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -8764,40 +8764,40 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
         <v>1</v>
@@ -8806,7 +8806,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -8818,7 +8818,7 @@
         <v>10</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5" t="n">
         <v>1</v>
@@ -8827,49 +8827,49 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -8881,7 +8881,7 @@
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E177" s="5" t="n">
         <v>0</v>
@@ -8890,75 +8890,75 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
@@ -8968,67 +8968,67 @@
         <v>2</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D183" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E183" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E184" s="5" t="n">
         <v>0</v>
@@ -9037,7 +9037,7 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -9058,19 +9058,19 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E186" s="5" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -9091,16 +9091,16 @@
         <v>10</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="C188" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E188" s="5" t="n">
         <v>3</v>
@@ -9121,22 +9121,22 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -9634,7 +9634,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
@@ -9663,7 +9663,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -9672,17 +9672,17 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -11171,12 +11171,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
@@ -11200,55 +11200,55 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
@@ -11258,55 +11258,55 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.846</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
@@ -11316,7 +11316,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -11345,12 +11345,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
@@ -11374,7 +11374,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -11403,12 +11403,12 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
@@ -11432,12 +11432,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
@@ -11461,26 +11461,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
@@ -11490,55 +11490,55 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
@@ -11548,26 +11548,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -11577,26 +11577,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="G75" s="6" t="n">
@@ -11606,12 +11606,12 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
@@ -12186,7 +12186,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0804</v>
       </c>
     </row>
     <row r="3">
@@ -12199,10 +12199,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2053</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="4">
@@ -12215,10 +12215,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4203</v>
+        <v>0.4201</v>
       </c>
     </row>
     <row r="5">
@@ -12231,10 +12231,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0784</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="6">
@@ -12247,10 +12247,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2154</v>
+        <v>0.2151</v>
       </c>
     </row>
   </sheetData>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、雲淡風輕o</t>
+          <t>cobraXverse、微笑Party</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:3勝</t>
+          <t>cobraXverse:2勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs</t>
+          <t>TRAITORs、雲淡風輕o</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP</t>
+          <t>Phoenix、TRAITORs</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, Unity:1勝</t>
+          <t>TRAITORs:3勝</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Phoenix</t>
+          <t>Unity、VainqueurJP</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:3勝</t>
+          <t>VainqueurJP:2勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse、xAEGISx</t>
+          <t>Maverickz、Phoenix</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:2勝, TheUniverse:1勝</t>
+          <t>Phoenix:3勝</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS</t>
+          <t>TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝</t>
+          <t>xAEGISx:2勝, TheUniverse:1勝</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、雲淡風輕o</t>
+          <t>Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:3勝</t>
+          <t>RaиkSS:3勝</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>一SUN一、當惡魔遇到殺手貓</t>
+          <t>Maverickz、雲淡風輕o</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:3勝</t>
+          <t>Maverickz:3勝</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、亗Luxúria亗</t>
+          <t>一SUN一、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
+          <t>當惡魔遇到殺手貓:3勝</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
+          <t>Kopitiam、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝</t>
+          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
         </is>
       </c>
     </row>
@@ -12824,15 +12824,15 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、柿一門</t>
+          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>AlmaVivaJP:3勝</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Иouver、ーリベリオンー</t>
+          <t>ーリベリオンー、柿一門</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>cobraXverse、微笑Party</t>
+          <t>Иouver、ーリベリオンー</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, cobraXverse:1勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -14001,11 +14001,11 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>MelonEmpire:6勝, Kopitiam:6勝, 亗Luxúria亗:5勝</t>
+          <t>Kopitiam:7勝, MelonEmpire:6勝, 亗Luxúria亗:5勝</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝, Phoenix:1勝</t>
+          <t>RaиkSS:5勝</t>
         </is>
       </c>
     </row>
@@ -14181,15 +14181,15 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>AlmaVivaJP:4勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝</t>
+          <t>雪狼族:4勝</t>
         </is>
       </c>
     </row>
@@ -16561,10 +16561,10 @@
         <v>16</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
@@ -16665,10 +16665,10 @@
         <v>16</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
@@ -16977,10 +16977,10 @@
         <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -17029,10 +17029,10 @@
         <v>8</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -17081,10 +17081,10 @@
         <v>14</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -17133,10 +17133,10 @@
         <v>10</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -17185,10 +17185,10 @@
         <v>12</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -17341,10 +17341,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -17662,102 +17662,102 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="J24" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="G25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="N25" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="O25" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>107</v>
@@ -17913,10 +17913,10 @@
         <v>9</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29">
@@ -18017,10 +18017,10 @@
         <v>9</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
@@ -18069,59 +18069,59 @@
         <v>8</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O32" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>97</v>
@@ -18130,53 +18130,53 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
@@ -18277,10 +18277,10 @@
         <v>16</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36">
@@ -18589,10 +18589,10 @@
         <v>9</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
@@ -18650,154 +18650,154 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>6</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="L45" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>69</v>
@@ -18953,10 +18953,10 @@
         <v>10</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
@@ -19109,10 +19109,10 @@
         <v>5</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
@@ -19577,10 +19577,10 @@
         <v>13</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
@@ -20210,50 +20210,50 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="N73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="P73" s="5" t="n">
         <v>27</v>
@@ -20262,53 +20262,53 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
@@ -20513,10 +20513,10 @@
         <v>8</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
@@ -21302,17 +21302,17 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0</v>
@@ -21342,10 +21342,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P94" s="5" t="n">
         <v>12</v>
@@ -21354,17 +21354,17 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
@@ -21394,13 +21394,13 @@
         <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -24786,17 +24786,17 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>哪裡有彩虹告訴我</t>
+          <t>VIRULENT死</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" s="5" t="n">
         <v>0</v>
@@ -24829,7 +24829,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P161" s="5" t="n">
         <v>2</v>
@@ -24838,17 +24838,17 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>SkyCast</t>
+          <t>哪裡有彩虹告訴我</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5" t="n">
         <v>0</v>
@@ -24890,14 +24890,14 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>OrtuรAquilล่</t>
+          <t>SkyCast</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>0</v>
@@ -24942,11 +24942,11 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>OrtuรAquilล่</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" s="5" t="n">
         <v>0</v>
@@ -24988,13 +24988,13 @@
         <v>0</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>PandoraJP</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -25046,11 +25046,11 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Amicitia</t>
+          <t>PandoraJP</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166" s="5" t="n">
         <v>0</v>
@@ -25065,7 +25065,7 @@
         <v>0</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="5" t="n">
         <v>0</v>
@@ -25098,7 +25098,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>おねがいマイメロディ</t>
+          <t>Amicitia</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -25150,7 +25150,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>AmicitiaJP</t>
+          <t>おねがいマイメロディ</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -25202,14 +25202,14 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>一DEFIAN</t>
+          <t>AmicitiaJP</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>0</v>
@@ -25221,7 +25221,7 @@
         <v>0</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" s="5" t="n">
         <v>0</v>
@@ -25254,7 +25254,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Zircon</t>
+          <t>一DEFIAN</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -25306,14 +25306,14 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>ZxFamily</t>
+          <t>Zircon</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>0</v>
@@ -25358,11 +25358,11 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>一Happiness一</t>
+          <t>ZxFamily</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" s="5" t="n">
         <v>0</v>
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="5" t="n">
         <v>0</v>
@@ -25410,7 +25410,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>KhokBanTai</t>
+          <t>一Happiness一</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -25426,13 +25426,13 @@
         <v>0</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="5" t="n">
         <v>0</v>
@@ -25462,7 +25462,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>赤いツバサ</t>
+          <t>KhokBanTai</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -25514,11 +25514,11 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>TËMPËST</t>
+          <t>赤いツバサ</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175" s="5" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>0</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
         <v>0</v>
@@ -25566,11 +25566,11 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>RL1</t>
+          <t>TËMPËST</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" s="5" t="n">
         <v>0</v>
@@ -25606,7 +25606,7 @@
         <v>0</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176" s="5" t="n">
         <v>0</v>
@@ -25618,7 +25618,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>天真爛漫ニャ向日葵</t>
+          <t>RL1</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -25646,7 +25646,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" s="5" t="n">
         <v>0</v>
@@ -25658,7 +25658,7 @@
         <v>0</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" s="5" t="n">
         <v>0</v>
@@ -25670,11 +25670,11 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Smasher죠</t>
+          <t>天真爛漫ニャ向日葵</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C178" s="5" t="n">
         <v>0</v>
@@ -25698,7 +25698,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K178" s="5" t="n">
         <v>0</v>
@@ -25722,7 +25722,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>XyChëDëLiC</t>
+          <t>Smasher죠</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -25774,11 +25774,11 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>微笑Paty</t>
+          <t>XyChëDëLiC</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180" s="5" t="n">
         <v>0</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O180" s="5" t="n">
         <v>0</v>
@@ -25826,7 +25826,7 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>VIRULENT死</t>
+          <t>微笑Paty</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -25866,10 +25866,10 @@
         <v>0</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P181" s="5" t="n">
         <v>1</v>
@@ -26002,7 +26002,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -26020,7 +26020,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -26744,19 +26744,19 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ーEspoirー(19), Revenant(18), 厶pocalypse(16), SanctaTerra(15), C0BRA(15), 柿一門(14), EIemento(13), Bagaиเ่(13)</t>
+          <t>Revenant(19), ーEspoirー(19), 厶pocalypse(17), 柿一門(15), SanctaTerra(15), C0BRA(15), EIemento(13), Bagaиเ่(13)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(8勝), 柿一門(7勝), Restart(7勝), ーEspoirー(6勝), Revenant(5勝)</t>
+          <t>柿一門(8勝), 亗Luxúria亗(8勝), Restart(7勝), ーEspoirー(6勝), Revenant(5勝)</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26862,7 @@
         <v>45</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー(8勝), ーEspoirー(8勝), Orzeca(7勝), 一SUN一(4勝), ßบรнíïdо丶ๅ家族(4勝)</t>
+          <t>ーリベリオンー(8勝), ーEspoirー(8勝), Orzeca(7勝), cobraXverse(4勝), 一SUN一(4勝)</t>
         </is>
       </c>
     </row>
@@ -27000,11 +27000,11 @@
         <v>47</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>一Arch(13), PokemonGo(12), FLORISTS(8), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
+          <t>一Arch(13), PokemonGo(12), FLORISTS(9), Maverickz(7), Döraè่mön(7), 黒の太陽(6), MÏRÃGË(6), 一SUN一(6)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -27046,11 +27046,11 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Unity(31), 黒の太陽(22), シェイド(20), xAEGISx(17), ーリベリオンー(13), FLORISTS(12), Phoenix(12), 黄昏のえりしおん(11)</t>
+          <t>Unity(32), 黒の太陽(23), シェイド(20), xAEGISx(17), Phoenix(13), ーリベリオンー(13), FLORISTS(12), 黄昏のえりしおん(11)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -27184,16 +27184,16 @@
         <v>35</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(33), Kopitiam(27), ßบรнíïdо丶ๅ家族(26), MelonEmpire(10), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
+          <t>亗Luxúria亗(34), Kopitiam(28), ßบรнíïdо丶ๅ家族(26), MelonEmpire(11), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam(25勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
+          <t>Kopitiam(26勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
         </is>
       </c>
     </row>
@@ -27253,16 +27253,16 @@
         <v>25</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön(14), Phoenix(11), Myst(11), 微笑Party(7), VainqueurJP(6), 溫柔鄉(6), 美孚冰室(5), Иouver(5)</t>
+          <t>Döraè่mön(15), Phoenix(11), Myst(11), 微笑Party(7), VainqueurJP(6), 溫柔鄉(6), 美孚冰室(5), Иouver(5)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Myst(11勝), Döraè่mön(10勝), Phoenix(9勝), VainqueurJP(6勝), 雪狼族(3勝)</t>
+          <t>Döraè่mön(11勝), Myst(11勝), Phoenix(9勝), VainqueurJP(6勝), 雪狼族(3勝)</t>
         </is>
       </c>
     </row>
@@ -27345,16 +27345,16 @@
         <v>35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(28), RaиkSS(21), 當惡魔遇到殺手貓(18), 雲淡風輕o(17), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
+          <t>PONYTAIL(28), RaиkSS(22), 當惡魔遇到殺手貓(19), 雲淡風輕o(18), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(25勝), RaиkSS(17勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
+          <t>PONYTAIL(25勝), RaиkSS(18勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27529,11 +27529,11 @@
         <v>51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>柿一門(28), 義勇(21), 桜吹雪(18), Pandora(16), 黄昏のえりしおん(16), ひよこりあ(16), Restart(14), 氣噗噗讓玻璃心碎一地(13)</t>
+          <t>柿一門(28), 義勇(21), 桜吹雪(18), Pandora(16), 黄昏のえりしおん(16), ひよこりあ(16), 氣噗噗讓玻璃心碎一地(14), Restart(14)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-24</t>
+          <t>2025-08-01 〜 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2190</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3353</v>
+        <v>0.3393</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.3636</v>
+        <v>0.3613</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2763</v>
+        <v>0.281</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3217</v>
+        <v>0.3194</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.1797</v>
+        <v>0.186</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>32</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5214</v>
+        <v>0.5254</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.4911</v>
+        <v>0.4867</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>11</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>54</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4954</v>
+        <v>0.4909</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>9</v>
@@ -1246,23 +1246,23 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.4078</v>
+        <v>0.1731</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
@@ -1271,23 +1271,23 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
         <v>103</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.1748</v>
+        <v>0.4078</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
@@ -1296,51 +1296,51 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
         <v>102</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.5098</v>
+        <v>0.2745</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.2772</v>
+        <v>0.5098</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.1882</v>
+        <v>0.186</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>24</v>
@@ -1546,76 +1546,76 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
         <v>77</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.4416</v>
+        <v>0.1429</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.5132</v>
+        <v>0.4416</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
         <v>76</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.1447</v>
+        <v>0.5132</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1646,23 +1646,23 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.6571</v>
+        <v>0.1549</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>2</v>
@@ -1671,23 +1671,23 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
         <v>70</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.1571</v>
+        <v>0.6571</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>2</v>
@@ -2146,48 +2146,48 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>35</v>
       </c>
       <c r="C63" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D63" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="F63" s="5" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.4118</v>
+        <v>0.4</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>1</v>
@@ -2196,26 +2196,26 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
         <v>34</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>0.1471</v>
+        <v>0.4118</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2446,23 +2446,23 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Sangsaka</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.0769</v>
+        <v>0.3077</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>0</v>
@@ -2471,23 +2471,23 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Sangsaka</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.2692</v>
+        <v>0.0769</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>0</v>
@@ -2496,51 +2496,51 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>REGENCY彡</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0.24</v>
+        <v>0.2692</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>REGENCY彡</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
         <v>25</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2971,23 +2971,23 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
         <v>11</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>0</v>
+        <v>0.8182</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>0</v>
@@ -2996,23 +2996,23 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -3121,23 +3121,23 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0</v>
@@ -3146,23 +3146,23 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G103" s="5" t="n">
         <v>0</v>
@@ -3171,73 +3171,73 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.1111</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>0.4444</v>
+        <v>0</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0</v>
@@ -3246,73 +3246,73 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.4444</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0</v>
@@ -4071,17 +4071,17 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="E140" s="5" t="n">
         <v>3</v>
@@ -4096,17 +4096,17 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E141" s="5" t="n">
         <v>3</v>
@@ -4121,7 +4121,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>HYLO匚乇尺乇u丂</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -4137,7 +4137,7 @@
         <v>3</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G142" s="5" t="n">
         <v>0</v>
@@ -4146,11 +4146,11 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>M三OW</t>
+          <t>HYLO匚乇尺乇u丂</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143" s="5" t="n">
         <v>0</v>
@@ -4159,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G143" s="5" t="n">
         <v>0</v>
@@ -4171,23 +4171,23 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>FestivalSA</t>
+          <t>M三OW</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144" s="5" t="n">
         <v>0</v>
@@ -4196,20 +4196,20 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>DemiseSA</t>
+          <t>FestivalSA</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5" t="n">
         <v>4</v>
@@ -4221,7 +4221,7 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>RevenantSA</t>
+          <t>DemiseSA</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G146" s="5" t="n">
         <v>0</v>
@@ -4246,7 +4246,7 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>OBLIxVION</t>
+          <t>RevenantSA</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
@@ -4262,7 +4262,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G147" s="5" t="n">
         <v>0</v>
@@ -4271,7 +4271,7 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>ZirconiAJP</t>
+          <t>OBLIxVION</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
@@ -4287,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G148" s="5" t="n">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>DEMIG0DS</t>
+          <t>ZirconiAJP</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
@@ -4312,7 +4312,7 @@
         <v>2</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G149" s="5" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>DEMIG0DS</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>49</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>46</v>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>4</v>
@@ -5992,96 +5992,96 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -6091,34 +6091,34 @@
         <v>4</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6130,7 +6130,7 @@
         <v>21</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>6</v>
@@ -6139,22 +6139,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -6165,59 +6165,59 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -6412,7 +6412,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -6424,7 +6424,7 @@
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
@@ -6433,187 +6433,187 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D64" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D64" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E64" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D65" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>4</v>
@@ -6622,7 +6622,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6634,16 +6634,16 @@
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6655,84 +6655,84 @@
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
@@ -6742,28 +6742,28 @@
         <v>4</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -6774,44 +6774,44 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -6826,28 +6826,28 @@
         <v>3</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -6958,19 +6958,19 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>0</v>
@@ -6979,19 +6979,19 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0</v>
@@ -7000,211 +7000,211 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -7215,17 +7215,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -9547,26 +9547,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
@@ -9576,26 +9576,26 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
@@ -12186,7 +12186,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0804</v>
+        <v>0.0801</v>
       </c>
     </row>
     <row r="3">
@@ -12199,10 +12199,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2059</v>
+        <v>0.2063</v>
       </c>
     </row>
     <row r="4">
@@ -12215,10 +12215,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4201</v>
+        <v>0.4199</v>
       </c>
     </row>
     <row r="5">
@@ -12231,10 +12231,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0785</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -12250,7 +12250,7 @@
         <v>471</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2151</v>
+        <v>0.2145</v>
       </c>
     </row>
   </sheetData>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、一Arch</t>
+          <t>cobraXverse、微笑Party</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>一Arch:4勝</t>
+          <t>微笑Party:2勝, cobraXverse:2勝</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、美孚冰室</t>
+          <t>Maverickz、一Arch</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:2勝, 微笑Party:2勝</t>
+          <t>一Arch:4勝</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Phoenix</t>
+          <t>微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:3勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:2勝, 微笑Party:2勝</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Myst、溫柔鄉</t>
+          <t>Döraè่mön、Phoenix</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Myst:4勝</t>
+          <t>Phoenix:3勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社、雪狼族</t>
+          <t>Myst、溫柔鄉</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社:2勝, 雪狼族:2勝</t>
+          <t>Myst:4勝</t>
         </is>
       </c>
     </row>
@@ -12594,15 +12594,15 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>cobraXverse、微笑Party</t>
+          <t>東京熱株式會社、雪狼族</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>cobraXverse:2勝, 微笑Party:1勝</t>
+          <t>東京熱株式會社:2勝, 雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>・殺戮・:3勝</t>
         </is>
       </c>
     </row>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15906,15 +15906,15 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -16613,10 +16613,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
@@ -16717,10 +16717,10 @@
         <v>13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
@@ -16769,10 +16769,10 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
@@ -16821,10 +16821,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -17185,10 +17185,10 @@
         <v>12</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
@@ -17445,10 +17445,10 @@
         <v>11</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
@@ -17549,10 +17549,10 @@
         <v>10</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -17653,10 +17653,10 @@
         <v>9</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -17818,102 +17818,102 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C27" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>9</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I27" s="5" t="n">
+      <c r="J27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="L27" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>8</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>9</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P28" s="5" t="n">
         <v>103</v>
@@ -17922,50 +17922,50 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="E29" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="K29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="N29" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>102</v>
@@ -17974,53 +17974,53 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="M30" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
@@ -18277,10 +18277,10 @@
         <v>16</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
@@ -18442,50 +18442,50 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="I39" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>7</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>77</v>
@@ -18494,102 +18494,102 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P41" s="5" t="n">
         <v>76</v>
@@ -18650,102 +18650,102 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>6</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>6</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="M44" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P44" s="5" t="n">
         <v>70</v>
@@ -19690,50 +19690,50 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P63" s="5" t="n">
         <v>35</v>
@@ -19742,102 +19742,102 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Etërnîty</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O64" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I64" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P64" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Etërnîty</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" s="5" t="n">
         <v>34</v>
@@ -20314,50 +20314,50 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Sangsaka</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P75" s="5" t="n">
         <v>26</v>
@@ -20366,29 +20366,29 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Sangsaka</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>1</v>
@@ -20397,16 +20397,16 @@
         <v>1</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
@@ -20418,63 +20418,63 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>REGENCY彡</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>REGENCY彡</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C78" s="5" t="n">
         <v>0</v>
@@ -20483,37 +20483,37 @@
         <v>0</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P78" s="5" t="n">
         <v>25</v>
@@ -21406,23 +21406,23 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P96" s="5" t="n">
         <v>11</v>
@@ -21458,23 +21458,23 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -21498,13 +21498,13 @@
         <v>0</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -21718,14 +21718,14 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>縱橫</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>0</v>
@@ -21740,10 +21740,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>0</v>
@@ -21758,10 +21758,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P102" s="5" t="n">
         <v>9</v>
@@ -21770,11 +21770,11 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Grîmoîrê</t>
+          <t>縱橫</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C103" s="5" t="n">
         <v>2</v>
@@ -21792,16 +21792,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J103" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>0</v>
@@ -21822,14 +21822,14 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>Grîmoîrê</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>0</v>
@@ -21853,7 +21853,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="5" t="n">
         <v>0</v>
@@ -21874,17 +21874,17 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Lullàby</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -21905,19 +21905,19 @@
         <v>0</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P105" s="5" t="n">
         <v>9</v>
@@ -21926,17 +21926,17 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>Lullàby</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0</v>
@@ -21957,16 +21957,16 @@
         <v>0</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O106" s="5" t="n">
         <v>2</v>
@@ -21978,11 +21978,11 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>神聖堂</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" s="5" t="n">
         <v>0</v>
@@ -21997,28 +21997,28 @@
         <v>0</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" s="5" t="n">
         <v>2</v>
@@ -22030,14 +22030,14 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>鎮山河</t>
+          <t>神聖堂</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
         <v>0</v>
@@ -22049,13 +22049,13 @@
         <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="5" t="n">
         <v>0</v>
@@ -22064,16 +22064,16 @@
         <v>0</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P108" s="5" t="n">
         <v>9</v>
@@ -22082,14 +22082,14 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>鎮山河</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>0</v>
@@ -22116,19 +22116,19 @@
         <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N109" s="5" t="n">
         <v>2</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
@@ -23694,11 +23694,11 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C140" s="5" t="n">
         <v>0</v>
@@ -23731,13 +23731,13 @@
         <v>0</v>
       </c>
       <c r="M140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" s="5" t="n">
         <v>3</v>
@@ -23746,11 +23746,11 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>NISKALLA</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C141" s="5" t="n">
         <v>0</v>
@@ -23765,7 +23765,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="5" t="n">
         <v>0</v>
@@ -23798,7 +23798,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>HYLO匚乇尺乇u丂</t>
+          <t>NISKALLA</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -23817,10 +23817,10 @@
         <v>0</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I142" s="5" t="n">
         <v>0</v>
@@ -23829,7 +23829,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="5" t="n">
         <v>0</v>
@@ -23850,7 +23850,7 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>M三OW</t>
+          <t>HYLO匚乇尺乇u丂</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
@@ -23869,10 +23869,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I143" s="5" t="n">
         <v>0</v>
@@ -23881,10 +23881,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="5" t="n">
         <v>0</v>
@@ -23896,20 +23896,20 @@
         <v>0</v>
       </c>
       <c r="P143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>FestivalSA</t>
+          <t>M三OW</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>0</v>
@@ -23933,10 +23933,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="5" t="n">
         <v>0</v>
@@ -23954,14 +23954,14 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>DemiseSA</t>
+          <t>FestivalSA</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>0</v>
@@ -24006,7 +24006,7 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>RevenantSA</t>
+          <t>DemiseSA</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
@@ -24058,11 +24058,11 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>OBLIxVION</t>
+          <t>RevenantSA</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C147" s="5" t="n">
         <v>0</v>
@@ -24071,7 +24071,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F147" s="5" t="n">
         <v>0</v>
@@ -24110,11 +24110,11 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>ZirconiAJP</t>
+          <t>OBLIxVION</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C148" s="5" t="n">
         <v>0</v>
@@ -24123,7 +24123,7 @@
         <v>0</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F148" s="5" t="n">
         <v>0</v>
@@ -24162,11 +24162,11 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>DEMIG0DS</t>
+          <t>ZirconiAJP</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" s="5" t="n">
         <v>0</v>
@@ -24193,7 +24193,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" s="5" t="n">
         <v>0</v>
@@ -24214,11 +24214,11 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>DEMIG0DS</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150" s="5" t="n">
         <v>0</v>
@@ -24245,16 +24245,16 @@
         <v>0</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" s="5" t="n">
         <v>0</v>
@@ -26002,7 +26002,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -26038,13 +26038,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -26062,7 +26062,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -26074,7 +26074,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -26770,16 +26770,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(46), 雪狼族(43), 沙漠黑鷹(41), 雲淡風輕o(18), 當惡魔遇到殺手貓(17), LeLien(13), ーリベリオンー(11), Unity(9)</t>
+          <t>・殺戮・(47), 雪狼族(44), 沙漠黑鷹(42), 當惡魔遇到殺手貓(18), 雲淡風輕o(18), LeLien(13), ーリベリオンー(11), Unity(9)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(42勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
+          <t>・殺戮・(43勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
         </is>
       </c>
     </row>
@@ -27115,16 +27115,16 @@
         <v>39</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(39), シェイド(23), 一Arch(14), FLORISTS(13), 黒の太陽(11), ーEspoirー(10), Restart(6), xAEGISx(6)</t>
+          <t>オアシステップ(39), シェイド(23), FLORISTS(14), 一Arch(14), 黒の太陽(11), ーEspoirー(10), xAEGISx(7), Restart(6)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(16勝), シェイド(11勝), 一Arch(6勝), FLORISTS(5勝), オアシスステップ(3勝)</t>
+          <t>オアシステップ(16勝), シェイド(11勝), 一Arch(6勝), FLORISTS(5勝), オアシスステップ(4勝)</t>
         </is>
       </c>
     </row>
@@ -27158,19 +27158,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(22), ーリベリオンー(11), Kopitiam(11), ZirconiA(7), Иouver(7), Orzeca(5), 厶pocalypse(5), 柿一門(5)</t>
+          <t>一惡人谷一(22), ーリベリオンー(12), Kopitiam(11), ZirconiA(7), Иouver(7), Orzeca(5), 厶pocalypse(5), 柿一門(5)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(21勝), ーリベリオンー(9勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
+          <t>一惡人谷一(21勝), ーリベリオンー(10勝), 亗Luxúria亗(4勝), ZirconiA(4勝), Kopitiam(3勝)</t>
         </is>
       </c>
     </row>
@@ -27276,11 +27276,11 @@
         <v>48</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>一Arch(18), Maverickz(10), TheUniverse(10), 亗Luxúria亗(10), 一SUN一(8), RëBîrth(8), Revenant(7), cobraXverse(6)</t>
+          <t>一Arch(18), Maverickz(10), TheUniverse(10), 亗Luxúria亗(10), 一SUN一(8), RëBîrth(8), Revenant(7), Pandora(6)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -27365,19 +27365,19 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ひよこりあ(29), ーEspoirー(22), 義勇(21), 桜吹雪(20), 月下の集い(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
+          <t>ひよこりあ(29), ーEspoirー(23), 義勇(21), 桜吹雪(20), 月下の集い(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>義勇(11勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ーEspoirー(5勝), ZirconiA(5勝)</t>
+          <t>義勇(11勝), ーEspoirー(6勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝)</t>
         </is>
       </c>
     </row>
@@ -27414,16 +27414,16 @@
         <v>47</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 柿一門(9), 微笑Party(8), 桜吹雪(8), ーEspoirー(7), EIemento(5)</t>
+          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 微笑Party(9), 柿一門(9), 桜吹雪(8), ーEspoirー(7), EIemento(5)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(10勝), Restart(9勝), 微笑Party(4勝), 柿一門(4勝), 一DEFIANCE(3勝)</t>
+          <t>亗Luxúria亗(10勝), Restart(9勝), 微笑Party(5勝), 柿一門(4勝), 一DEFIANCE(3勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-25</t>
+          <t>2025-08-01 〜 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2196</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>57</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3393</v>
+        <v>0.3373</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.3613</v>
+        <v>0.359</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3194</v>
+        <v>0.3172</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1069</v>
+        <v>0.1061</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>22</v>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>77</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.5878</v>
+        <v>0.5833</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>17</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.186</v>
+        <v>0.1846</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>32</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>2</v>
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.208</v>
+        <v>0.2063</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>21</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.5242</v>
+        <v>0.528</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>16</v>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>68</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5913</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
@@ -1121,151 +1121,151 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.3818</v>
+        <v>0.4955</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
         <v>110</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4909</v>
+        <v>0.3818</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.4352</v>
+        <v>0.6239</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.6262</v>
+        <v>0.4352</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.181</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.1731</v>
+        <v>0.1429</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>37</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3663</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>15</v>
@@ -1421,51 +1421,51 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0.3488</v>
+        <v>0.1839</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
         <v>86</v>
       </c>
       <c r="C35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="E35" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.7024</v>
+        <v>0.7059</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>9</v>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.2716</v>
+        <v>0.2805</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>11</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.1538</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>25</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>1</v>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C40" s="5" t="n">
         <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.4416</v>
+        <v>0.4359</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>5</v>
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.1791</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>1</v>
@@ -1775,19 +1775,19 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.2063</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>14</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0</v>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.2807</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>5</v>
@@ -2046,23 +2046,23 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.4103</v>
+        <v>0.275</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>0</v>
@@ -2071,23 +2071,23 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
         <v>39</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.2821</v>
+        <v>0.4103</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>0</v>
@@ -2146,51 +2146,51 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4167</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
         <v>35</v>
       </c>
       <c r="C64" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D64" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="F64" s="5" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2671,57 +2671,57 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>0</v>
@@ -2846,23 +2846,23 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>DarkChaos</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>0</v>
@@ -2871,23 +2871,23 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>DarkChaos</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>0</v>
@@ -2896,23 +2896,23 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C93" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="E93" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D93" s="6" t="n">
-        <v>0.3077</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="F93" s="5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G93" s="5" t="n">
         <v>0</v>
@@ -2921,23 +2921,23 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.3077</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
@@ -3021,73 +3021,73 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E100" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -3109,10 +3109,10 @@
         <v>0</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -3121,23 +3121,23 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="E102" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0</v>
@@ -3471,23 +3471,23 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3496,73 +3496,73 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.1429</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0</v>
@@ -3571,23 +3571,23 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3596,23 +3596,23 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.5</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>0</v>
@@ -3696,20 +3696,20 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6667</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>10</v>
@@ -3721,23 +3721,23 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G126" s="5" t="n">
         <v>0</v>
@@ -3746,23 +3746,23 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -3771,23 +3771,23 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0</v>
@@ -3796,23 +3796,23 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G129" s="5" t="n">
         <v>0</v>
@@ -3821,23 +3821,23 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G130" s="5" t="n">
         <v>0</v>
@@ -3846,17 +3846,17 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>4</v>
@@ -3871,7 +3871,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
@@ -3887,7 +3887,7 @@
         <v>4</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G132" s="5" t="n">
         <v>0</v>
@@ -5434,13 +5434,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -5593,106 +5593,106 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>Revenant</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>柿一門</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -5761,54 +5761,54 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -5818,49 +5818,49 @@
         <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -5929,43 +5929,43 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -5992,117 +5992,117 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
@@ -6112,34 +6112,34 @@
         <v>4</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -6151,7 +6151,7 @@
         <v>21</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>6</v>
@@ -6349,54 +6349,54 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
@@ -6406,34 +6406,34 @@
         <v>2</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -6445,7 +6445,7 @@
         <v>19</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
@@ -6454,106 +6454,106 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D65" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D65" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -7063,127 +7063,127 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -7399,82 +7399,82 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E110" s="5" t="n">
         <v>0</v>
@@ -7483,124 +7483,124 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>4</v>
@@ -7609,82 +7609,82 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>3</v>
@@ -7693,19 +7693,19 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="5" t="n">
         <v>5</v>
@@ -7714,49 +7714,49 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -7771,67 +7771,67 @@
         <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>3</v>
@@ -7840,33 +7840,33 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
@@ -7876,49 +7876,49 @@
         <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
@@ -7939,81 +7939,81 @@
         <v>0</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
           <t>xAEGISx</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
@@ -8023,46 +8023,46 @@
         <v>3</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" s="5" t="n">
         <v>4</v>
@@ -8071,117 +8071,117 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D141" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
@@ -8197,12 +8197,12 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
@@ -8212,70 +8212,70 @@
         <v>2</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
@@ -8296,18 +8296,18 @@
         <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
@@ -8317,123 +8317,123 @@
         <v>1</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
@@ -8443,102 +8443,102 @@
         <v>6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
           <t>柿一門</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
-        <is>
-          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
@@ -8548,172 +8548,172 @@
         <v>4</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E169" s="5" t="n">
         <v>3</v>
@@ -8722,40 +8722,40 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>4</v>
@@ -8764,22 +8764,22 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -9142,19 +9142,19 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
         <v>1</v>
@@ -9163,54 +9163,54 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
@@ -9220,13 +9220,13 @@
         <v>0</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -9238,21 +9238,21 @@
         <v>9</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
@@ -9262,25 +9262,25 @@
         <v>1</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" s="5" t="n">
         <v>1</v>
@@ -9289,19 +9289,19 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
+          <t>ひよこりあ</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
           <t>月下の集い</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197" s="5" t="n">
         <v>1</v>
@@ -9310,7 +9310,7 @@
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
@@ -9322,73 +9322,73 @@
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
           <t>TRAITORs</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="inlineStr">
-        <is>
-          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9402,7 +9402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -9982,26 +9982,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
@@ -10011,26 +10011,26 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G21" s="6" t="n">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -10069,12 +10069,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G23" s="6" t="n">
@@ -10098,12 +10098,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G24" s="6" t="n">
@@ -10127,26 +10127,26 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G25" s="6" t="n">
@@ -10156,26 +10156,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
@@ -10185,26 +10185,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
@@ -10214,26 +10214,26 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
@@ -10243,12 +10243,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
@@ -10272,26 +10272,26 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
@@ -10301,26 +10301,26 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -10388,12 +10388,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
@@ -10417,26 +10417,26 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Outlawss</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
@@ -10446,12 +10446,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Outlawss</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
@@ -10475,7 +10475,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -10504,26 +10504,26 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
@@ -10533,12 +10533,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
@@ -10562,12 +10562,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
@@ -10591,26 +10591,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
@@ -10620,26 +10620,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -10649,12 +10649,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -10707,26 +10707,26 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
@@ -11780,12 +11780,12 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>TheEnd</t>
         </is>
       </c>
       <c r="G82" s="6" t="n">
@@ -11809,26 +11809,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>TheEnd</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G83" s="6" t="n">
@@ -11838,26 +11838,26 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G84" s="6" t="n">
@@ -11867,12 +11867,12 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
@@ -11896,26 +11896,26 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E86" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
@@ -11925,26 +11925,26 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
@@ -11954,12 +11954,12 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
@@ -11983,26 +11983,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
@@ -12012,26 +12012,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>SkyCastIe</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
@@ -12041,26 +12041,26 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E91" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>SkyCastIe</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="G91" s="6" t="n">
@@ -12070,58 +12070,29 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Maverickz</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>AlmaVivaJP</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -12186,7 +12157,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0801</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="3">
@@ -12199,7 +12170,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0.2063</v>
@@ -12215,10 +12186,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4199</v>
+        <v>0.4211</v>
       </c>
     </row>
     <row r="5">
@@ -12234,7 +12205,7 @@
         <v>174</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="6">
@@ -12247,10 +12218,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2145</v>
+        <v>0.214</v>
       </c>
     </row>
   </sheetData>
@@ -12264,7 +12235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12368,11 +12339,11 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:7勝, 一SUN一:5勝</t>
+          <t>Orzeca:8勝, 一SUN一:5勝</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14566,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14603,7 +14574,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -14618,15 +14589,15 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14612,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14649,7 +14620,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14635,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14672,7 +14643,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14658,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14695,7 +14666,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14681,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14718,7 +14689,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14704,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14741,7 +14712,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14727,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14779,7 +14750,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14787,7 +14758,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14773,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14810,7 +14781,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14796,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14833,7 +14804,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14848,7 +14819,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14856,7 +14827,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14842,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Pandora、xAEGISx、黒の太陽</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14879,7 +14850,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>黒の太陽:1勝, Pandora:1勝</t>
         </is>
       </c>
     </row>
@@ -14894,7 +14865,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14902,7 +14873,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 美孚冰室:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -14917,7 +14888,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14925,7 +14896,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -14940,7 +14911,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -14948,7 +14919,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -14963,7 +14934,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14986,7 +14957,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -14994,7 +14965,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -15009,7 +14980,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -15017,7 +14988,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15003,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -15040,7 +15011,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15026,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15063,7 +15034,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15049,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Restart、ー麒麟ー</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15086,7 +15057,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15072,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15109,7 +15080,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15095,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、Restart、ー麒麟ー</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15132,7 +15103,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15118,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15155,7 +15126,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15141,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15178,7 +15149,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15164,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15201,7 +15172,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15187,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15224,7 +15195,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15210,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15247,7 +15218,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15233,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15270,7 +15241,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15285,7 +15256,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15293,7 +15264,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15279,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15316,7 +15287,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15302,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15339,7 +15310,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15325,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15377,7 +15348,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15385,7 +15356,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15371,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15408,7 +15379,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15394,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15431,7 +15402,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15446,7 +15417,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15454,7 +15425,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15440,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15477,7 +15448,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15463,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15500,7 +15471,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15486,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15523,7 +15494,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15509,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>Oops、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15546,7 +15517,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15532,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15569,7 +15540,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15555,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15592,7 +15563,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15578,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、・殺戮・</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15615,7 +15586,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15630,7 +15601,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15638,7 +15609,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15624,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15661,7 +15632,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15676,7 +15647,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15684,7 +15655,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15699,7 +15670,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15707,7 +15678,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15693,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
@@ -15730,7 +15701,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15716,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15768,7 +15739,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
@@ -15776,7 +15747,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15791,7 +15762,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -15799,7 +15770,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15785,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
@@ -15822,76 +15793,76 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:3勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15906,15 +15877,15 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -15929,15 +15900,15 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:3勝</t>
         </is>
       </c>
     </row>
@@ -15952,15 +15923,15 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -15975,15 +15946,15 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15969,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
@@ -16006,7 +15977,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16021,7 +15992,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16029,7 +16000,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16015,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -16052,7 +16023,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16038,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16075,7 +16046,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16061,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -16098,7 +16069,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16084,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16121,45 +16092,45 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:5勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16167,22 +16138,22 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16190,7 +16161,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16205,15 +16176,15 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:5勝</t>
         </is>
       </c>
     </row>
@@ -16228,7 +16199,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16251,7 +16222,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -16259,7 +16230,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16245,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
@@ -16282,7 +16253,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16297,7 +16268,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -16305,7 +16276,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16291,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
@@ -16328,7 +16299,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16314,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -16351,7 +16322,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16337,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
@@ -16374,7 +16345,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16389,13 +16360,82 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D179" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="D182" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16613,10 +16653,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -16717,10 +16757,10 @@
         <v>13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -16821,10 +16861,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -17029,10 +17069,10 @@
         <v>8</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -17081,10 +17121,10 @@
         <v>14</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -17185,10 +17225,10 @@
         <v>12</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15">
@@ -17237,10 +17277,10 @@
         <v>14</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -17341,10 +17381,10 @@
         <v>11</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -17497,10 +17537,10 @@
         <v>9</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
@@ -17558,102 +17598,102 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C22" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D22" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="F22" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>110</v>
@@ -17662,154 +17702,154 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="G24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="N24" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="O24" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="J25" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>105</v>
@@ -17818,53 +17858,53 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>9</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28">
@@ -18069,10 +18109,10 @@
         <v>8</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
@@ -18182,102 +18222,102 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="M34" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I35" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J35" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="N35" s="5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P35" s="5" t="n">
         <v>86</v>
@@ -18329,10 +18369,10 @@
         <v>5</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
@@ -18381,10 +18421,10 @@
         <v>12</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
@@ -18485,10 +18525,10 @@
         <v>9</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
@@ -18537,10 +18577,10 @@
         <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
@@ -18901,10 +18941,10 @@
         <v>3</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -18953,10 +18993,10 @@
         <v>10</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49">
@@ -19161,10 +19201,10 @@
         <v>4</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
@@ -19482,26 +19522,26 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -19510,7 +19550,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" s="5" t="n">
         <v>0</v>
@@ -19519,41 +19559,41 @@
         <v>0</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>0</v>
@@ -19562,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>0</v>
@@ -19571,13 +19611,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
         <v>39</v>
@@ -19690,102 +19730,102 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Astrklotho</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Astrklotho</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P64" s="5" t="n">
         <v>35</v>
@@ -20782,102 +20822,102 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Demise</t>
+          <t>Oops</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I84" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="5" t="n">
         <v>2</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O84" s="5" t="n">
         <v>3</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>Demise</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" s="5" t="n">
         <v>2</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P85" s="5" t="n">
         <v>18</v>
@@ -20886,7 +20926,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Oops</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -20899,25 +20939,25 @@
         <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L86" s="5" t="n">
         <v>2</v>
@@ -20926,10 +20966,10 @@
         <v>2</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P86" s="5" t="n">
         <v>18</v>
@@ -21146,29 +21186,29 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>DarkChaos</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>0</v>
@@ -21183,13 +21223,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P91" s="5" t="n">
         <v>13</v>
@@ -21198,29 +21238,29 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>DarkChaos</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
@@ -21235,10 +21275,10 @@
         <v>0</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O92" s="5" t="n">
         <v>0</v>
@@ -21250,17 +21290,17 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0</v>
@@ -21302,17 +21342,17 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0</v>
@@ -21342,13 +21382,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -21510,11 +21550,11 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C98" s="5" t="n">
         <v>0</v>
@@ -21529,7 +21569,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>0</v>
@@ -21550,10 +21590,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P98" s="5" t="n">
         <v>10</v>
@@ -21562,14 +21602,14 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>0</v>
@@ -21581,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -21614,14 +21654,14 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>DEMIIGODS혼혈</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>0</v>
@@ -21639,10 +21679,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" s="5" t="n">
         <v>0</v>
@@ -21651,13 +21691,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" s="5" t="n">
         <v>10</v>
@@ -21666,23 +21706,23 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>臨時公會名000000302</t>
+          <t>DEMIIGODS혼혈</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
@@ -21691,10 +21731,10 @@
         <v>0</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" s="5" t="n">
         <v>0</v>
@@ -21703,13 +21743,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" s="5" t="n">
         <v>10</v>
@@ -21718,23 +21758,23 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>臨時公會名000000302</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>0</v>
@@ -21758,13 +21798,13 @@
         <v>0</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P102" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -22446,17 +22486,17 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>0</v>
@@ -22471,25 +22511,25 @@
         <v>0</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P116" s="5" t="n">
         <v>7</v>
@@ -22498,14 +22538,14 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>0</v>
@@ -22523,16 +22563,16 @@
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0</v>
@@ -22541,7 +22581,7 @@
         <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P117" s="5" t="n">
         <v>7</v>
@@ -22550,17 +22590,17 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>0</v>
@@ -22602,17 +22642,17 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="5" t="n">
         <v>0</v>
@@ -22621,7 +22661,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
@@ -22648,17 +22688,17 @@
         <v>0</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C120" s="5" t="n">
         <v>0</v>
@@ -22673,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H120" s="5" t="n">
         <v>0</v>
@@ -22706,17 +22746,17 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="5" t="n">
         <v>0</v>
@@ -22746,10 +22786,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P121" s="5" t="n">
         <v>6</v>
@@ -22914,11 +22954,11 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C125" s="5" t="n">
         <v>0</v>
@@ -22954,23 +22994,23 @@
         <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P125" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C126" s="5" t="n">
         <v>0</v>
@@ -22991,10 +23031,10 @@
         <v>0</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="5" t="n">
         <v>0</v>
@@ -23018,7 +23058,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -23043,10 +23083,10 @@
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K127" s="5" t="n">
         <v>0</v>
@@ -23058,10 +23098,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P127" s="5" t="n">
         <v>5</v>
@@ -23070,14 +23110,14 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>0</v>
@@ -23110,10 +23150,10 @@
         <v>0</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P128" s="5" t="n">
         <v>5</v>
@@ -23122,14 +23162,14 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>0</v>
@@ -23174,14 +23214,14 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Ancîеnts</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>0</v>
@@ -23220,20 +23260,20 @@
         <v>0</v>
       </c>
       <c r="P130" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>0</v>
@@ -23278,14 +23318,14 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>0</v>
@@ -23318,10 +23358,10 @@
         <v>0</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P132" s="5" t="n">
         <v>4</v>
@@ -25938,7 +25978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25984,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -26020,7 +26060,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -26056,7 +26096,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -26116,7 +26156,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -26128,13 +26168,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -26152,25 +26192,25 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>離脱(前半のみ)</t>
+          <t>新規参入(後半のみ)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>彡MukBANG彡</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -26179,7 +26219,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -26188,7 +26228,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>彡MukBANG彡</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -26197,7 +26237,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -26206,7 +26246,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -26215,7 +26255,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -26224,7 +26264,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -26233,7 +26273,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -26242,7 +26282,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Relaх</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -26251,7 +26291,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -26260,7 +26300,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>DoraemonSA</t>
+          <t>Relaх</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -26269,7 +26309,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
@@ -26278,7 +26318,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Vanartroops</t>
+          <t>DoraemonSA</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -26287,7 +26327,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -26296,7 +26336,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>溫柔鄉</t>
+          <t>Vanartroops</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -26305,7 +26345,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -26314,7 +26354,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>愛Eиdorphiиe</t>
+          <t>溫柔鄉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -26323,7 +26363,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -26332,7 +26372,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>愛Eиdorphiиe</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -26341,7 +26381,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
@@ -26350,7 +26390,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -26359,7 +26399,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -26368,7 +26408,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -26386,7 +26426,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -26395,7 +26435,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -26404,7 +26444,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -26413,7 +26453,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
@@ -26422,7 +26462,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -26431,7 +26471,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
@@ -26440,7 +26480,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>殺戮THM</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -26458,7 +26498,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Оnyх</t>
+          <t>殺戮THM</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -26467,7 +26507,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>0</v>
@@ -26476,7 +26516,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>米丨FÖSSIL丨米</t>
+          <t>Оnyх</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -26485,7 +26525,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>0</v>
@@ -26494,7 +26534,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -26512,7 +26552,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -26521,7 +26561,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>0</v>
@@ -26530,7 +26570,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -26548,7 +26588,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -26566,7 +26606,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -26575,7 +26615,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>0</v>
@@ -26584,7 +26624,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -26602,7 +26642,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -26620,7 +26660,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -26638,7 +26678,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -26647,7 +26687,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>0</v>
@@ -26656,7 +26696,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TRAITORsJP</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -26674,7 +26714,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Ancîеnts</t>
+          <t>TRAITORsJP</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -26686,6 +26726,24 @@
         <v>5</v>
       </c>
       <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Ancîеnts</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>離脱(前半のみ)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26813,19 +26871,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Revenant(43), MÏRÃGË(18), ZirconiA(17), 柿一門(13), 黄昏のえりしおん(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
+          <t>Revenant(43), MÏRÃGË(19), ZirconiA(17), 柿一門(13), 黄昏のえりしおん(12), Pandora(10), RëBîrth(10), Maverickz(8)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Revenant(17勝), Unity(5勝), Restart(4勝), MÏRÃGË(3勝), ーArch(2勝)</t>
+          <t>Revenant(17勝), Unity(5勝), MÏRÃGË(4勝), Restart(4勝), ーArch(2勝)</t>
         </is>
       </c>
     </row>
@@ -26954,16 +27012,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(41), RaиkSS(32), PONYTAIL(26), Myst(20), VainqueurJP(19), TRAITORs(12), Phoenix(9), ・殺戮・(7)</t>
+          <t>AlmaVivaJP(42), RaиkSS(33), PONYTAIL(26), Myst(20), VainqueurJP(19), TRAITORs(12), Phoenix(9), ・殺戮・(8)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(30勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
+          <t>AlmaVivaJP(31勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27023,16 +27081,16 @@
         <v>38</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(54), ・殺戮・(52), 毛家村(42), 雲淡風輕o(18), 廣寒宮(9), 微笑Party(8), Oops(6), TheUniverse(6)</t>
+          <t>沙漠黑鷹(55), ・殺戮・(52), 毛家村(42), 雲淡風輕o(19), 廣寒宮(9), 微笑Party(8), Oops(7), TheUniverse(6)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹(49勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
+          <t>沙漠黑鷹(50勝), ・殺戮・(4勝), TheUniverse(2勝), 毛家村(1勝), xAEGISx(1勝)</t>
         </is>
       </c>
     </row>
@@ -27092,11 +27150,11 @@
         <v>22</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(36), ßบรнíïdо丶ๅ家族(25), Kopitiam(21), SkyCastIe(17), MelonEmpire(10), 彡MukBANG彡(9), 微笑Party(6), Ancîеnts(5)</t>
+          <t>亗Luxúria亗(36), ßบรнíïdо丶ๅ家族(25), Kopitiam(21), SkyCastIe(17), MelonEmpire(11), 彡MukBANG彡(9), 微笑Party(7), 美孚冰室(5)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -27138,16 +27196,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(39), RaиkSS(28), VainqueurJP(27), PONYTAIL(24), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
+          <t>TRAITORs(40), VainqueurJP(28), RaиkSS(28), PONYTAIL(25), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(23勝), RaиkSS(9勝), PONYTAIL(8勝), VainqueurJP(8勝), AlmaVivaJP(5勝)</t>
+          <t>TRAITORs(23勝), VainqueurJP(9勝), RaиkSS(9勝), PONYTAIL(8勝), AlmaVivaJP(5勝)</t>
         </is>
       </c>
     </row>
@@ -27207,16 +27265,16 @@
         <v>62</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>義勇(29), ーEspoirー(20), ー麒麟ー(18), オアシステップ(18), 桜吹雪(17), Restart(15), 黄昏のえりしおん(15), 柿一門(11)</t>
+          <t>義勇(30), ーEspoirー(20), ー麒麟ー(19), オアシステップ(18), 桜吹雪(17), 黄昏のえりしおん(16), Restart(16), 柿一門(11)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>義勇(12勝), ー麒麟ー(6勝), オアシステップ(6勝), 磯野家(4勝), Restart(3勝)</t>
+          <t>義勇(12勝), ー麒麟ー(6勝), オアシステップ(6勝), 磯野家(4勝), 黄昏のえりしおん(3勝)</t>
         </is>
       </c>
     </row>
@@ -27437,16 +27495,16 @@
         <v>41</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(24), PokemonGo(10), xAEGISx(9), VainqueurJP(8), TheUniverse(7), PONYTAIL(7), RaиkSS(6), Maverickz(6)</t>
+          <t>TRAITORs(25), PokemonGo(10), xAEGISx(9), VainqueurJP(8), TheUniverse(7), PONYTAIL(7), ZirconiA(6), RaиkSS(6)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(21勝), VainqueurJP(6勝), RaиkSS(5勝), PONYTAIL(5勝), PokemonGo(3勝)</t>
+          <t>TRAITORs(22勝), VainqueurJP(6勝), RaиkSS(5勝), PONYTAIL(5勝), PokemonGo(3勝)</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27518,7 @@
         <v>51</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -27480,14 +27538,14 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>シェイド(24), xAEGISx(16), 一Arch(16), 黒の太陽(12), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
+          <t>シェイド(24), xAEGISx(17), 一Arch(16), 黒の太陽(13), ーリベリオンー(10), Restart(7), Astrklotho(6), 愛Eиdorphiиe(6)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -27506,7 +27564,7 @@
         <v>35</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-09-28</t>
+          <t>2025-08-01 〜 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2215</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3412</v>
+        <v>0.3392</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1962</v>
+        <v>0.195</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.3382</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -846,101 +846,101 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1053</v>
+        <v>0.5896</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>133</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.5865</v>
+        <v>0.1053</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>131</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.1832</v>
+        <v>0.4198</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.4231</v>
+        <v>0.1832</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>27</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.2126</v>
+        <v>0.2109</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>21</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>62</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5254</v>
+        <v>0.521</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.4352</v>
+        <v>0.4404</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>19</v>
@@ -1296,51 +1296,51 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
         <v>103</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.4078</v>
+        <v>0.3689</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.3725</v>
+        <v>0.4078</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.3367</v>
+        <v>0.3434</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>16</v>
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C43" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.1528</v>
+        <v>0.1507</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>5</v>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.6571</v>
+        <v>0.662</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>7</v>
@@ -1696,51 +1696,51 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
         <v>69</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.1449</v>
+        <v>0.7246</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.7206</v>
+        <v>0.1449</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.2031</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>14</v>
@@ -2021,23 +2021,23 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.2619</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0</v>
@@ -2046,23 +2046,23 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
         <v>41</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.2683</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>0</v>
@@ -2175,19 +2175,19 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.1389</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>海洋之心</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -2384,38 +2384,38 @@
         <v>0.1786</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>海洋之心</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0.1852</v>
+        <v>0.1786</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -2821,23 +2821,23 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
         <v>14</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>0.2143</v>
+        <v>0.1429</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>0</v>
@@ -2846,23 +2846,23 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>0.1538</v>
+        <v>0.2143</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>0</v>
@@ -2946,23 +2946,23 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
         <v>12</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.75</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
@@ -2971,23 +2971,23 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>0.8182</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>20</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>0</v>
@@ -3371,23 +3371,23 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0</v>
@@ -3396,23 +3396,23 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
@@ -3421,23 +3421,23 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -3446,23 +3446,23 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -3484,10 +3484,10 @@
         <v>0.1429</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3571,23 +3571,23 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.7143</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3596,23 +3596,23 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>0</v>
@@ -3621,23 +3621,23 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>0.1667</v>
+        <v>0.5</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G122" s="5" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -3659,7 +3659,7 @@
         <v>0.1667</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F123" s="5" t="n">
         <v>16</v>
@@ -3671,23 +3671,23 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G124" s="5" t="n">
         <v>0</v>
@@ -3696,23 +3696,23 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>0</v>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>24</v>
@@ -5555,91 +5555,91 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>27</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -5648,55 +5648,55 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>Revenant</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>柿一門</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -5744,117 +5744,117 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -5864,55 +5864,55 @@
         <v>3</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -5924,136 +5924,136 @@
         <v>23</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6064,14 +6064,14 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>6</v>
@@ -6080,124 +6080,124 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>7</v>
@@ -6206,28 +6206,28 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -6239,21 +6239,21 @@
         <v>20</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -6263,70 +6263,70 @@
         <v>7</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -7067,12 +7067,12 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
@@ -7082,13 +7082,13 @@
         <v>2</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -7100,31 +7100,31 @@
         <v>16</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -7135,101 +7135,101 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -7865,19 +7865,19 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>3</v>
@@ -7886,54 +7886,54 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
@@ -7943,130 +7943,130 @@
         <v>2</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>2</v>
@@ -8075,22 +8075,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
@@ -8111,39 +8111,39 @@
         <v>3</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
+          <t>EIemento</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
           <t>柿一門</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
@@ -8159,58 +8159,58 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D142" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E142" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>2</v>
@@ -8222,54 +8222,54 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
@@ -8279,81 +8279,81 @@
         <v>2</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
@@ -8369,64 +8369,64 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -8437,14 +8437,14 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E155" s="5" t="n">
         <v>3</v>
@@ -8453,106 +8453,106 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
@@ -9125,28 +9125,28 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="C189" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>3</v>
@@ -9167,40 +9167,40 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" s="5" t="n">
         <v>1</v>
@@ -9209,54 +9209,54 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
@@ -9266,13 +9266,13 @@
         <v>0</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -9284,21 +9284,21 @@
         <v>9</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
@@ -9308,25 +9308,25 @@
         <v>1</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" s="5" t="n">
         <v>1</v>
@@ -9335,19 +9335,19 @@
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
+          <t>ひよこりあ</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
           <t>月下の集い</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="inlineStr">
-        <is>
-          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E198" s="5" t="n">
         <v>1</v>
@@ -9356,7 +9356,7 @@
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -9368,52 +9368,52 @@
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
+          <t>Maverickz</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
           <t>TRAITORs</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
-        <is>
-          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9572,7 +9572,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -9581,17 +9581,17 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
@@ -9601,7 +9601,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
@@ -11254,26 +11254,26 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
@@ -11283,26 +11283,26 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
@@ -11312,55 +11312,55 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0.846</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G66" s="6" t="n">
@@ -12240,7 +12240,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0795</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -12253,10 +12253,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2059</v>
+        <v>0.2066</v>
       </c>
     </row>
     <row r="4">
@@ -12269,10 +12269,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4221</v>
+        <v>0.4217</v>
       </c>
     </row>
     <row r="5">
@@ -12285,10 +12285,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.079</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -12301,10 +12301,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2135</v>
+        <v>0.2133</v>
       </c>
     </row>
   </sheetData>
@@ -12318,7 +12318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12855,7 +12855,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、亗Luxúria亗</t>
+          <t>RaиkSS、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
+          <t>RaиkSS:3勝</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
+          <t>Kopitiam、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:3勝</t>
+          <t>亗Luxúria亗:2勝, Kopitiam:1勝</t>
         </is>
       </c>
     </row>
@@ -12901,15 +12901,15 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、柿一門</t>
+          <t>AlmaVivaJP、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>AlmaVivaJP:3勝</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Иouver、ーリベリオンー</t>
+          <t>ーリベリオンー、柿一門</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、雲淡風輕o</t>
+          <t>Иouver、ーリベリオンー</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹</t>
+          <t>Phoenix、雲淡風輕o</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>Phoenix:2勝</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Anino、ouтcasт</t>
+          <t>・殺戮・、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Anino:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Myst、VainqueurJP</t>
+          <t>Anino、ouтcasт</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Anino:2勝</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst</t>
+          <t>Myst、VainqueurJP</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Unity、海洋之心</t>
+          <t>Maverickz、Myst</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity</t>
+          <t>Unity、海洋之心</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、一DEFIANCE</t>
+          <t>Phoenix、Unity</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、Иouver</t>
+          <t>Maverickz、一DEFIANCE</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社、雲淡風輕o</t>
+          <t>VainqueurJP、Иouver</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>東京熱株式會社:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Иouver、雲淡風輕o</t>
+          <t>東京熱株式會社、雲淡風輕o</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>雲淡風輕o:1勝, Иouver:1勝</t>
+          <t>東京熱株式會社:2勝</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、VainqueurJP</t>
+          <t>Иouver、雲淡風輕o</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>雲淡風輕o:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Myst、Unity</t>
+          <t>Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Unity:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、Myst</t>
+          <t>Myst、Unity</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Myst:1勝, Etërnîty:1勝</t>
+          <t>Myst:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、SkyCastIe</t>
+          <t>Etërnîty、Myst</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:1勝, Maverickz:1勝</t>
+          <t>Myst:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>REGENCY彡、TнэÖяdeг</t>
+          <t>Maverickz、SkyCastIe</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>REGENCY彡:1勝, TнэÖяdeг:1勝</t>
+          <t>SkyCastIe:1勝, Maverickz:1勝</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ーリベリオンー</t>
+          <t>REGENCY彡、TнэÖяdeг</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝</t>
+          <t>REGENCY彡:1勝, TнэÖяdeг:1勝</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、天機</t>
+          <t>xAEGISx、ーリベリオンー</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty:2勝</t>
+          <t>ーリベリオンー:2勝</t>
         </is>
       </c>
     </row>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴</t>
+          <t>Etërnîty、天機</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 心晴:1勝</t>
+          <t>Etërnîty:2勝</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
+          <t>天機、心晴</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地:2勝</t>
+          <t>天機:1勝, 心晴:1勝</t>
         </is>
       </c>
     </row>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、柿一門</t>
+          <t>PokemonGo、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo:2勝</t>
+          <t>氣噗噗讓玻璃心碎一地:2勝</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Myst</t>
+          <t>PokemonGo、柿一門</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>PokemonGo:2勝</t>
         </is>
       </c>
     </row>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Myst、雲淡風輕o</t>
+          <t>Döraè่mön、Myst</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、微笑Party</t>
+          <t>Myst、雲淡風輕o</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Maverickz:2勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、Vanartroops</t>
+          <t>Maverickz、微笑Party</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe:2勝</t>
+          <t>Maverickz:2勝</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、溫柔鄉</t>
+          <t>SkyCastIe、Vanartroops</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>SkyCastIe:2勝</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、VainqueurJP</t>
+          <t>VainqueurJP、溫柔鄉</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓</t>
+          <t>RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>VainqueurJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -14005,7 +14005,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、PONYTAIL</t>
+          <t>天機、氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
@@ -14013,30 +14013,30 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>氣噗噗讓玻璃心碎一地:1勝, 天機:1勝</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>三つ巴</t>
+          <t>タイマン</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Maverickz、PONYTAIL</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -14051,15 +14051,15 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
+          <t>Kopitiam、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
+          <t>Kopitiam:14勝, 亗Luxúria亗:12勝, ßบรнíïdо丶ๅ家族:8勝</t>
         </is>
       </c>
     </row>
@@ -14074,15 +14074,15 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、彡MukBANG彡</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam:7勝, MelonEmpire:6勝, 亗Luxúria亗:5勝</t>
+          <t>ßบรнíïdо丶ๅ家族:14勝, 彡MukBANG彡:9勝, 亗Luxúria亗:8勝</t>
         </is>
       </c>
     </row>
@@ -14097,15 +14097,15 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、TRAITORs</t>
+          <t>Kopitiam、MelonEmpire、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝, TRAITORs:5勝, PONYTAIL:1勝</t>
+          <t>Kopitiam:8勝, MelonEmpire:6勝, 亗Luxúria亗:5勝</t>
         </is>
       </c>
     </row>
@@ -14120,15 +14120,15 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
+          <t>PONYTAIL、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
+          <t>RaиkSS:5勝, TRAITORs:5勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14143,15 +14143,15 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹</t>
+          <t>AlmaVivaJP、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:6勝</t>
+          <t>RaиkSS:4勝, AlmaVivaJP:2勝, PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、RaиkSS</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:6勝</t>
+          <t>沙漠黑鷹:6勝</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
+          <t>AlmaVivaJP:6勝</t>
         </is>
       </c>
     </row>
@@ -14212,7 +14212,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:5勝, RaиkSS:1勝</t>
+          <t>RaиkSS:3勝, VainqueurJP:2勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -14235,15 +14235,15 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、雪狼族、雲淡風輕o</t>
+          <t>RaиkSS、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:5勝</t>
+          <t>TRAITORs:5勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:5勝</t>
+          <t>雪狼族:5勝</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
+          <t>RaиkSS、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝, Phoenix:1勝</t>
+          <t>RaиkSS:5勝</t>
         </is>
       </c>
     </row>
@@ -14304,15 +14304,15 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>C0BRA、Иouver、厶pocalypse</t>
+          <t>AlmaVivaJP、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
+          <t>AlmaVivaJP:4勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>C0BRA、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
+          <t>C0BRA:2勝, 厶pocalypse:1勝, Иouver:1勝</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
+          <t>xAEGISx、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:2勝, シェイド:2勝</t>
+          <t>xAEGISx:3勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、xAEGISx</t>
+          <t>シェイド、ーリベリオンー、ー麒麟ー</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
+          <t>ーリベリオンー:2勝, シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14396,7 +14396,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、PONYTAIL</t>
+          <t>Phoenix、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:4勝</t>
+          <t>Phoenix:2勝, Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Myst、PONYTAIL</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:4勝</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>TRAITORs:2勝, AlmaVivaJP:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14465,15 +14465,15 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -14718,15 +14718,15 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Pandora、xAEGISx、黒の太陽</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, Pandora:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Pandora、xAEGISx、黒の太陽</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>黒の太陽:1勝, Pandora:1勝</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 美孚冰室:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Restart、ー麒麟ー</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、シェイド、一SUN一</t>
+          <t>FLORISTS、Restart、ー麒麟ー</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>一SUN一:2勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>Orzeca、シェイド、一SUN一</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>一SUN一:2勝</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Oops、沙漠黑鷹、雲淡風輕o</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>Oops、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
+          <t>AlmaVivaJP、RaиkSS、・殺戮・</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、・殺戮・</t>
+          <t>AlmaVivaJP、PONYTAIL、・殺戮・</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>AlmaVivaJP:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、Myst、・殺戮・</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
+          <t>AlmaVivaJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Myst、RaиkSS、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>AlmaVivaJP:1勝, RaиkSS:1勝</t>
         </is>
       </c>
     </row>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、TRAITORs、VainqueurJP</t>
+          <t>Myst、RaиkSS、VainqueurJP</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
+          <t>Phoenix、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>VainqueurJP:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、RaиkSS、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:1勝, Phoenix:1勝</t>
+          <t>AlmaVivaJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Anino、Myst、Vanartroops</t>
+          <t>Phoenix、RaиkSS、TRAITORs</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Myst:2勝</t>
+          <t>RaиkSS:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、VainqueurJP</t>
+          <t>Anino、Myst、Vanartroops</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
+          <t>Myst:2勝</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
+          <t>Myst、PONYTAIL、VainqueurJP</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
+          <t>PONYTAIL:1勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、TRAITORs</t>
+          <t>AlmaVivaJP、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
@@ -16014,30 +16014,30 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
+          <t>TRAITORs:1勝, PONYTAIL:1勝</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>四つ巴</t>
+          <t>三つ巴</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Myst、PONYTAIL、TRAITORs</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:5勝</t>
+          <t>PONYTAIL:1勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -16052,15 +16052,15 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:3勝</t>
+          <t>沙漠黑鷹:5勝</t>
         </is>
       </c>
     </row>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
+          <t>・殺戮・:3勝</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>Unity、シェイド、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>黒の太陽:1勝, シェイド:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -16121,15 +16121,15 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
+          <t>・殺戮・、東京熱株式會社、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Restart:2勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>Restart、RëBîrth、ZirconiA、Иouver</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>Restart:2勝</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
+          <t>・殺戮・、微笑Party、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
+          <t>Unity、xAEGISx、ーリベリオンー、黒の太陽</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
+          <t>Unity、xAEGISx、黄昏のえりしおん、黒の太陽</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:2勝</t>
+          <t>xAEGISx:1勝, 黄昏のえりしおん:1勝</t>
         </is>
       </c>
     </row>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>FLORISTS、Unity、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -16313,30 +16313,30 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:2勝</t>
+          <t>黒の太陽:2勝</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>五つ巴</t>
+          <t>四つ巴</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
+          <t>PONYTAIL、RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:5勝</t>
+          <t>PONYTAIL:2勝</t>
         </is>
       </c>
     </row>
@@ -16351,15 +16351,15 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:2勝</t>
+          <t>・殺戮・:5勝</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
+          <t>・殺戮・、一SUN一、沙漠黑鷹、當惡魔遇到殺手貓、雪狼族</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、當惡魔遇到殺手貓、美孚冰室、雪狼族</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
+          <t>・殺戮・、柿一門、沙漠黑鷹、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
+          <t>・殺戮・、沙漠黑鷹、美孚冰室、雪狼族、雲淡風輕o</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
+          <t>・殺戮・:2勝</t>
         </is>
       </c>
     </row>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
+          <t>LeLien、Phoenix、Unity、ーリベリオンー、一Arch</t>
         </is>
       </c>
       <c r="D180" s="5" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Revenant:2勝</t>
+          <t>ーリベリオンー:1勝, Phoenix:1勝</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
+          <t>Pandora、Revenant、RëBîrth、ーEspoirー、桜吹雪</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
+          <t>Bagaиเ่、C0BRA、Kopitiam、Revenant、Иouver</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
+          <t>Revenant:2勝</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>オアシステップ、ーEspoirー、柿一門、義勇、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>黄昏のえりしおん:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+          <t>Oops、・殺戮・、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
@@ -16581,13 +16581,36 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
+          <t>・殺戮・、柿一門、毛家村、沙漠黑鷹、雲淡風輕o</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>沙漠黑鷹:2勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>五つ巴</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
           <t>・殺戮・、廣寒宮、毛家村、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
-      <c r="D185" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
+      <c r="D186" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>沙漠黑鷹:1勝, ・殺戮・:1勝</t>
         </is>
@@ -16604,7 +16627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P183"/>
+  <dimension ref="A1:Q183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16622,7 +16645,8 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16703,6 +16727,11 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
@@ -16756,7 +16785,10 @@
         <v>11</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>170</v>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="3">
@@ -16808,6 +16840,9 @@
         <v>13</v>
       </c>
       <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="n">
         <v>170</v>
       </c>
     </row>
@@ -16860,7 +16895,10 @@
         <v>14</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>158</v>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="5">
@@ -16912,6 +16950,9 @@
         <v>10</v>
       </c>
       <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
         <v>157</v>
       </c>
     </row>
@@ -16964,6 +17005,9 @@
         <v>8</v>
       </c>
       <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>154</v>
       </c>
     </row>
@@ -17016,6 +17060,9 @@
         <v>11</v>
       </c>
       <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>146</v>
       </c>
     </row>
@@ -17068,6 +17115,9 @@
         <v>3</v>
       </c>
       <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
         <v>139</v>
       </c>
     </row>
@@ -17120,6 +17170,9 @@
         <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
         <v>137</v>
       </c>
     </row>
@@ -17172,215 +17225,230 @@
         <v>7</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>133</v>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
         <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="J13" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="M13" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="N13" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5" t="n">
         <v>131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="5" t="n">
+      <c r="G14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="I14" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O14" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -17432,7 +17500,10 @@
         <v>7</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>127</v>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -17484,6 +17555,9 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
         <v>125</v>
       </c>
     </row>
@@ -17536,6 +17610,9 @@
         <v>7</v>
       </c>
       <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
         <v>125</v>
       </c>
     </row>
@@ -17588,6 +17665,9 @@
         <v>9</v>
       </c>
       <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
         <v>119</v>
       </c>
     </row>
@@ -17640,7 +17720,10 @@
         <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="20">
@@ -17692,6 +17775,9 @@
         <v>7</v>
       </c>
       <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
         <v>116</v>
       </c>
     </row>
@@ -17744,6 +17830,9 @@
         <v>9</v>
       </c>
       <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
         <v>114</v>
       </c>
     </row>
@@ -17796,6 +17885,9 @@
         <v>7</v>
       </c>
       <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
         <v>111</v>
       </c>
     </row>
@@ -17848,6 +17940,9 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
         <v>110</v>
       </c>
     </row>
@@ -17900,6 +17995,9 @@
         <v>7</v>
       </c>
       <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
         <v>109</v>
       </c>
     </row>
@@ -17952,7 +18050,10 @@
         <v>4</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="26">
@@ -18004,6 +18105,9 @@
         <v>9</v>
       </c>
       <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -18056,6 +18160,9 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -18108,111 +18215,120 @@
         <v>13</v>
       </c>
       <c r="P28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5" t="n">
         <v>103</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="H29" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>10</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="5" t="n">
         <v>103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F30" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="H30" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>10</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>102</v>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -18264,6 +18380,9 @@
         <v>1</v>
       </c>
       <c r="P31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="5" t="n">
         <v>102</v>
       </c>
     </row>
@@ -18316,7 +18435,10 @@
         <v>10</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="33">
@@ -18368,6 +18490,9 @@
         <v>1</v>
       </c>
       <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
         <v>97</v>
       </c>
     </row>
@@ -18420,6 +18545,9 @@
         <v>11</v>
       </c>
       <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
         <v>88</v>
       </c>
     </row>
@@ -18472,6 +18600,9 @@
         <v>0</v>
       </c>
       <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
         <v>86</v>
       </c>
     </row>
@@ -18524,6 +18655,9 @@
         <v>4</v>
       </c>
       <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
         <v>85</v>
       </c>
     </row>
@@ -18576,6 +18710,9 @@
         <v>5</v>
       </c>
       <c r="P37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="n">
         <v>82</v>
       </c>
     </row>
@@ -18628,6 +18765,9 @@
         <v>2</v>
       </c>
       <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
         <v>79</v>
       </c>
     </row>
@@ -18680,6 +18820,9 @@
         <v>12</v>
       </c>
       <c r="P39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="5" t="n">
         <v>78</v>
       </c>
     </row>
@@ -18732,6 +18875,9 @@
         <v>4</v>
       </c>
       <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
         <v>78</v>
       </c>
     </row>
@@ -18784,6 +18930,9 @@
         <v>0</v>
       </c>
       <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
         <v>76</v>
       </c>
     </row>
@@ -18836,6 +18985,9 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
         <v>73</v>
       </c>
     </row>
@@ -18888,7 +19040,10 @@
         <v>12</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="44">
@@ -18940,111 +19095,120 @@
         <v>5</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="5" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="H46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="K46" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>4</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="47">
@@ -19096,6 +19260,9 @@
         <v>2</v>
       </c>
       <c r="P47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="5" t="n">
         <v>67</v>
       </c>
     </row>
@@ -19148,7 +19315,10 @@
         <v>13</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>64</v>
+        <v>1</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="49">
@@ -19200,6 +19370,9 @@
         <v>0</v>
       </c>
       <c r="P49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -19252,6 +19425,9 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -19304,6 +19480,9 @@
         <v>5</v>
       </c>
       <c r="P51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="5" t="n">
         <v>59</v>
       </c>
     </row>
@@ -19356,6 +19535,9 @@
         <v>5</v>
       </c>
       <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
         <v>57</v>
       </c>
     </row>
@@ -19408,6 +19590,9 @@
         <v>0</v>
       </c>
       <c r="P53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="5" t="n">
         <v>56</v>
       </c>
     </row>
@@ -19460,6 +19645,9 @@
         <v>2</v>
       </c>
       <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
         <v>55</v>
       </c>
     </row>
@@ -19512,6 +19700,9 @@
         <v>0</v>
       </c>
       <c r="P55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="5" t="n">
         <v>54</v>
       </c>
     </row>
@@ -19564,6 +19755,9 @@
         <v>0</v>
       </c>
       <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
         <v>46</v>
       </c>
     </row>
@@ -19616,110 +19810,119 @@
         <v>0</v>
       </c>
       <c r="P57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="5" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="N58" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>41</v>
+        <v>1</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="5" t="n">
         <v>41</v>
       </c>
     </row>
@@ -19772,6 +19975,9 @@
         <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
         <v>39</v>
       </c>
     </row>
@@ -19824,6 +20030,9 @@
         <v>7</v>
       </c>
       <c r="P61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="5" t="n">
         <v>37</v>
       </c>
     </row>
@@ -19876,6 +20085,9 @@
         <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
         <v>37</v>
       </c>
     </row>
@@ -19928,6 +20140,9 @@
         <v>0</v>
       </c>
       <c r="P63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="5" t="n">
         <v>36</v>
       </c>
     </row>
@@ -19980,7 +20195,10 @@
         <v>2</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -20032,6 +20250,9 @@
         <v>0</v>
       </c>
       <c r="P65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -20084,6 +20305,9 @@
         <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -20136,6 +20360,9 @@
         <v>0</v>
       </c>
       <c r="P67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -20188,6 +20415,9 @@
         <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
         <v>34</v>
       </c>
     </row>
@@ -20240,6 +20470,9 @@
         <v>0</v>
       </c>
       <c r="P69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="5" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20292,6 +20525,9 @@
         <v>0</v>
       </c>
       <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
         <v>29</v>
       </c>
     </row>
@@ -20344,111 +20580,120 @@
         <v>2</v>
       </c>
       <c r="P71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>海洋之心</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="5" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>海洋之心</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="5" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="74">
@@ -20500,6 +20745,9 @@
         <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -20552,6 +20800,9 @@
         <v>8</v>
       </c>
       <c r="P75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -20604,6 +20855,9 @@
         <v>4</v>
       </c>
       <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -20656,6 +20910,9 @@
         <v>0</v>
       </c>
       <c r="P77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -20708,6 +20965,9 @@
         <v>0</v>
       </c>
       <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -20760,6 +21020,9 @@
         <v>1</v>
       </c>
       <c r="P79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="5" t="n">
         <v>22</v>
       </c>
     </row>
@@ -20812,6 +21075,9 @@
         <v>1</v>
       </c>
       <c r="P80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -20864,6 +21130,9 @@
         <v>0</v>
       </c>
       <c r="P81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -20916,6 +21185,9 @@
         <v>0</v>
       </c>
       <c r="P82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20968,6 +21240,9 @@
         <v>4</v>
       </c>
       <c r="P83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -21020,6 +21295,9 @@
         <v>0</v>
       </c>
       <c r="P84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -21072,6 +21350,9 @@
         <v>3</v>
       </c>
       <c r="P85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -21124,6 +21405,9 @@
         <v>0</v>
       </c>
       <c r="P86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -21176,6 +21460,9 @@
         <v>0</v>
       </c>
       <c r="P87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="5" t="n">
         <v>17</v>
       </c>
     </row>
@@ -21228,6 +21515,9 @@
         <v>0</v>
       </c>
       <c r="P88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21280,23 +21570,26 @@
         <v>1</v>
       </c>
       <c r="P89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E90" s="5" t="n">
         <v>0</v>
@@ -21326,29 +21619,32 @@
         <v>0</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="5" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>0</v>
@@ -21378,13 +21674,16 @@
         <v>0</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="Q91" s="5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="92">
@@ -21436,6 +21735,9 @@
         <v>0</v>
       </c>
       <c r="P92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -21488,6 +21790,9 @@
         <v>0</v>
       </c>
       <c r="P93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -21540,23 +21845,26 @@
         <v>0</v>
       </c>
       <c r="P94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="5" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
@@ -21586,29 +21894,32 @@
         <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="5" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>0</v>
@@ -21638,13 +21949,16 @@
         <v>0</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="Q96" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -21696,6 +22010,9 @@
         <v>0</v>
       </c>
       <c r="P97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -21748,6 +22065,9 @@
         <v>8</v>
       </c>
       <c r="P98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21800,6 +22120,9 @@
         <v>0</v>
       </c>
       <c r="P99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21852,6 +22175,9 @@
         <v>3</v>
       </c>
       <c r="P100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21904,6 +22230,9 @@
         <v>0</v>
       </c>
       <c r="P101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21956,6 +22285,9 @@
         <v>1</v>
       </c>
       <c r="P102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22008,6 +22340,9 @@
         <v>3</v>
       </c>
       <c r="P103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22060,6 +22395,9 @@
         <v>0</v>
       </c>
       <c r="P104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22112,6 +22450,9 @@
         <v>0</v>
       </c>
       <c r="P105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22164,6 +22505,9 @@
         <v>0</v>
       </c>
       <c r="P106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22216,6 +22560,9 @@
         <v>0</v>
       </c>
       <c r="P107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22268,6 +22615,9 @@
         <v>2</v>
       </c>
       <c r="P108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22320,6 +22670,9 @@
         <v>0</v>
       </c>
       <c r="P109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22372,6 +22725,9 @@
         <v>0</v>
       </c>
       <c r="P110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22424,23 +22780,26 @@
         <v>1</v>
       </c>
       <c r="P111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -22452,47 +22811,50 @@
         <v>0</v>
       </c>
       <c r="H112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I112" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>0</v>
@@ -22504,13 +22866,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K113" s="5" t="n">
         <v>0</v>
@@ -22528,38 +22890,41 @@
         <v>0</v>
       </c>
       <c r="P113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" s="5" t="n">
         <v>0</v>
@@ -22580,38 +22945,41 @@
         <v>0</v>
       </c>
       <c r="P114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0</v>
@@ -22632,23 +23000,26 @@
         <v>0</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="Q115" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>0</v>
@@ -22678,12 +23049,15 @@
         <v>0</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -22736,6 +23110,9 @@
         <v>2</v>
       </c>
       <c r="P117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -22788,6 +23165,9 @@
         <v>0</v>
       </c>
       <c r="P118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -22840,17 +23220,20 @@
         <v>0</v>
       </c>
       <c r="P119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>RestartJP</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C120" s="5" t="n">
         <v>0</v>
@@ -22865,44 +23248,47 @@
         <v>0</v>
       </c>
       <c r="G120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P120" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="Q120" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>RestartJP</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C121" s="5" t="n">
         <v>0</v>
@@ -22917,7 +23303,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
@@ -22944,23 +23330,26 @@
         <v>0</v>
       </c>
       <c r="P121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>ひよこ座流星群</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>0</v>
@@ -22996,23 +23385,26 @@
         <v>0</v>
       </c>
       <c r="P122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>一MÃRVËL</t>
+          <t>ひよこ座流星群</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0</v>
@@ -23048,41 +23440,44 @@
         <v>0</v>
       </c>
       <c r="P123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>一MÃRVËL</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" s="5" t="n">
         <v>0</v>
@@ -23100,13 +23495,16 @@
         <v>0</v>
       </c>
       <c r="P124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -23116,25 +23514,25 @@
         <v>0</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" s="5" t="n">
         <v>0</v>
@@ -23146,12 +23544,15 @@
         <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -23204,6 +23605,9 @@
         <v>0</v>
       </c>
       <c r="P126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23256,6 +23660,9 @@
         <v>0</v>
       </c>
       <c r="P127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23308,6 +23715,9 @@
         <v>2</v>
       </c>
       <c r="P128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23360,6 +23770,9 @@
         <v>0</v>
       </c>
       <c r="P129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23412,6 +23825,9 @@
         <v>0</v>
       </c>
       <c r="P130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23464,6 +23880,9 @@
         <v>0</v>
       </c>
       <c r="P131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23516,6 +23935,9 @@
         <v>0</v>
       </c>
       <c r="P132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23568,6 +23990,9 @@
         <v>0</v>
       </c>
       <c r="P133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23620,6 +24045,9 @@
         <v>0</v>
       </c>
       <c r="P134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23672,6 +24100,9 @@
         <v>0</v>
       </c>
       <c r="P135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23724,6 +24155,9 @@
         <v>0</v>
       </c>
       <c r="P136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23776,6 +24210,9 @@
         <v>0</v>
       </c>
       <c r="P137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23828,6 +24265,9 @@
         <v>0</v>
       </c>
       <c r="P138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23880,6 +24320,9 @@
         <v>0</v>
       </c>
       <c r="P139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23932,6 +24375,9 @@
         <v>1</v>
       </c>
       <c r="P140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23984,6 +24430,9 @@
         <v>0</v>
       </c>
       <c r="P141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24036,6 +24485,9 @@
         <v>3</v>
       </c>
       <c r="P142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24088,6 +24540,9 @@
         <v>0</v>
       </c>
       <c r="P143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24140,6 +24595,9 @@
         <v>0</v>
       </c>
       <c r="P144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24192,6 +24650,9 @@
         <v>0</v>
       </c>
       <c r="P145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24244,6 +24705,9 @@
         <v>0</v>
       </c>
       <c r="P146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24296,6 +24760,9 @@
         <v>0</v>
       </c>
       <c r="P147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24348,6 +24815,9 @@
         <v>0</v>
       </c>
       <c r="P148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24400,6 +24870,9 @@
         <v>0</v>
       </c>
       <c r="P149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24452,6 +24925,9 @@
         <v>0</v>
       </c>
       <c r="P150" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24504,6 +24980,9 @@
         <v>0</v>
       </c>
       <c r="P151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24556,6 +25035,9 @@
         <v>0</v>
       </c>
       <c r="P152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24608,6 +25090,9 @@
         <v>0</v>
       </c>
       <c r="P153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24660,6 +25145,9 @@
         <v>0</v>
       </c>
       <c r="P154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24712,6 +25200,9 @@
         <v>0</v>
       </c>
       <c r="P155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24764,6 +25255,9 @@
         <v>0</v>
       </c>
       <c r="P156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24816,6 +25310,9 @@
         <v>1</v>
       </c>
       <c r="P157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24868,6 +25365,9 @@
         <v>0</v>
       </c>
       <c r="P158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24920,6 +25420,9 @@
         <v>0</v>
       </c>
       <c r="P159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24972,6 +25475,9 @@
         <v>0</v>
       </c>
       <c r="P160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25024,6 +25530,9 @@
         <v>2</v>
       </c>
       <c r="P161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25076,6 +25585,9 @@
         <v>0</v>
       </c>
       <c r="P162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25128,6 +25640,9 @@
         <v>0</v>
       </c>
       <c r="P163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25180,6 +25695,9 @@
         <v>0</v>
       </c>
       <c r="P164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25232,6 +25750,9 @@
         <v>0</v>
       </c>
       <c r="P165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25284,6 +25805,9 @@
         <v>0</v>
       </c>
       <c r="P166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25336,6 +25860,9 @@
         <v>0</v>
       </c>
       <c r="P167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25388,6 +25915,9 @@
         <v>0</v>
       </c>
       <c r="P168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25440,6 +25970,9 @@
         <v>0</v>
       </c>
       <c r="P169" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25492,6 +26025,9 @@
         <v>0</v>
       </c>
       <c r="P170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25544,6 +26080,9 @@
         <v>0</v>
       </c>
       <c r="P171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25596,6 +26135,9 @@
         <v>0</v>
       </c>
       <c r="P172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25648,6 +26190,9 @@
         <v>0</v>
       </c>
       <c r="P173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25700,6 +26245,9 @@
         <v>0</v>
       </c>
       <c r="P174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25752,6 +26300,9 @@
         <v>0</v>
       </c>
       <c r="P175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25804,6 +26355,9 @@
         <v>1</v>
       </c>
       <c r="P176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25856,6 +26410,9 @@
         <v>0</v>
       </c>
       <c r="P177" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25908,6 +26465,9 @@
         <v>0</v>
       </c>
       <c r="P178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25960,6 +26520,9 @@
         <v>0</v>
       </c>
       <c r="P179" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26012,6 +26575,9 @@
         <v>0</v>
       </c>
       <c r="P180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26064,6 +26630,9 @@
         <v>0</v>
       </c>
       <c r="P181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26116,6 +26685,9 @@
         <v>0</v>
       </c>
       <c r="P182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26168,6 +26740,9 @@
         <v>0</v>
       </c>
       <c r="P183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26209,7 +26784,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>後半参加数(2026-03〜2026-09)</t>
+          <t>後半参加数(2026-03〜2026-10)</t>
         </is>
       </c>
     </row>
@@ -26264,7 +26839,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -26282,7 +26857,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -26372,7 +26947,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -27009,16 +27584,16 @@
         <v>52</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Revenant(19), ーEspoirー(19), 厶pocalypse(17), 柿一門(15), SanctaTerra(15), C0BRA(15), EIemento(13), Bagaиเ่(13)</t>
+          <t>Revenant(20), ーEspoirー(19), 厶pocalypse(18), 柿一門(16), SanctaTerra(15), C0BRA(15), EIemento(13), Bagaиเ่(13)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>柿一門(8勝), 亗Luxúria亗(8勝), Restart(7勝), ーEspoirー(6勝), Revenant(5勝)</t>
+          <t>柿一門(8勝), 亗Luxúria亗(8勝), Restart(7勝), Revenant(6勝), ーEspoirー(6勝)</t>
         </is>
       </c>
     </row>
@@ -27259,10 +27834,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -27308,16 +27883,16 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Unity(32), 黒の太陽(23), シェイド(20), xAEGISx(17), Phoenix(13), ーリベリオンー(13), FLORISTS(12), 黄昏のえりしおん(11)</t>
+          <t>Unity(33), 黒の太陽(24), シェイド(20), xAEGISx(17), Phoenix(14), ーリベリオンー(14), FLORISTS(12), 黄昏のえりしおん(11)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽(9勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), 黄昏のえりしおん(4勝)</t>
+          <t>黒の太陽(9勝), xAEGISx(6勝), シェイド(6勝), Unity(5勝), Phoenix(4勝)</t>
         </is>
       </c>
     </row>
@@ -27446,16 +28021,16 @@
         <v>35</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(34), Kopitiam(28), ßบรнíïdо丶ๅ家族(26), MelonEmpire(11), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
+          <t>亗Luxúria亗(35), Kopitiam(29), ßบรнíïdо丶ๅ家族(26), MelonEmpire(12), 彡MukBANG彡(7), Иouver(5), 厶pocalypse(4), SkyCastIe(4)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam(26勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
+          <t>Kopitiam(27勝), ßบรнíïdо丶ๅ家族(8勝), SkyCastIe(4勝), 彡MukBANG彡(3勝), Kaioken(2勝)</t>
         </is>
       </c>
     </row>
@@ -27558,19 +28133,19 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(20), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
+          <t>一惡人谷一(21), 雲淡風輕o(14), xAEGISx(12), Etërnîty(9), 毛家村(8), Demise(4), 一DEFIANCE(4), CatlandTHM(4)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(16勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
+          <t>一惡人谷一(17勝), xAEGISx(10勝), 雲淡風輕o(8勝), Etërnîty(5勝), 毛家村(4勝)</t>
         </is>
       </c>
     </row>
@@ -27607,16 +28182,16 @@
         <v>35</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(28), RaиkSS(22), 當惡魔遇到殺手貓(19), 雲淡風輕o(18), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
+          <t>PONYTAIL(28), RaиkSS(23), 當惡魔遇到殺手貓(20), 雲淡風輕o(18), Maverickz(11), 美孚冰室(10), 微笑Party(10), VainqueurJP(9)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL(25勝), RaиkSS(18勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
+          <t>PONYTAIL(25勝), RaиkSS(19勝), VainqueurJP(4勝), TheUniverse(3勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27791,16 +28366,16 @@
         <v>51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>柿一門(28), 義勇(21), 桜吹雪(18), Pandora(16), 黄昏のえりしおん(16), ひよこりあ(16), 氣噗噗讓玻璃心碎一地(14), Restart(14)</t>
+          <t>柿一門(28), 義勇(21), 桜吹雪(18), Pandora(16), 黄昏のえりしおん(16), ひよこりあ(16), 氣噗噗讓玻璃心碎一地(15), Restart(14)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>義勇(8勝), 柿一門(7勝), 氣噗噗讓玻璃心碎一地(5勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝)</t>
+          <t>義勇(8勝), 柿一門(7勝), 氣噗噗讓玻璃心碎一地(6勝), 黄昏のえりしおん(4勝), 桜吹雪(4勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-10-01</t>
+          <t>2025-08-01 〜 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2222</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3392</v>
+        <v>0.3372</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3353</v>
+        <v>0.3392</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.195</v>
+        <v>0.1938</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>57</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.3631</v>
+        <v>0.3608</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>31</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2792</v>
+        <v>0.2774</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3151</v>
+        <v>0.3129</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>19</v>
@@ -846,101 +846,101 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>134</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.5896</v>
+        <v>0.1045</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.1053</v>
+        <v>0.5896</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.4198</v>
+        <v>0.1818</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>131</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.1832</v>
+        <v>0.4198</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4538</v>
+        <v>0.4583</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>62</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.521</v>
+        <v>0.5167</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>8</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>56</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.4912</v>
+        <v>0.487</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>11</v>
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4955</v>
+        <v>0.4911</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>9</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.6239</v>
+        <v>0.6273</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>10</v>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.2718</v>
+        <v>0.2692</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>22</v>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.2805</v>
+        <v>0.2892</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>11</v>
@@ -1546,51 +1546,51 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.1538</v>
+        <v>0.4304</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
         <v>78</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.4359</v>
+        <v>0.1538</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1621,51 +1621,51 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.2329</v>
+        <v>0.1486</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
         <v>73</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.1507</v>
+        <v>0.2329</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2025,19 +2025,19 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>0.2619</v>
+        <v>0.2791</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0</v>
@@ -2421,23 +2421,23 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>0</v>
@@ -2446,23 +2446,23 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
         <v>27</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.2963</v>
+        <v>0</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>0</v>
@@ -2871,23 +2871,23 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>DarkChaos</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>0</v>
+        <v>0.6923</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>0</v>
@@ -2896,23 +2896,23 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>DarkChaos</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G93" s="5" t="n">
         <v>0</v>
@@ -2921,23 +2921,23 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C94" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="E94" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D94" s="6" t="n">
-        <v>0.3077</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="F94" s="5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>0</v>
@@ -2946,23 +2946,23 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>0.75</v>
+        <v>0.3077</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>0</v>
@@ -2996,23 +2996,23 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
         <v>11</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>0</v>
+        <v>0.5455</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -3021,23 +3021,23 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4545</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>0</v>
@@ -3046,51 +3046,51 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -3371,17 +3371,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>4</v>
@@ -3396,23 +3396,23 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0</v>
@@ -3421,23 +3421,23 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -3446,23 +3446,23 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -3471,23 +3471,23 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0</v>
@@ -3496,23 +3496,23 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0</v>
@@ -3521,73 +3521,73 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>0.7143</v>
+        <v>0.1429</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G120" s="5" t="n">
         <v>0</v>
@@ -3871,23 +3871,23 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E132" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="G132" s="5" t="n">
         <v>0</v>
@@ -3896,23 +3896,23 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G133" s="5" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
@@ -3934,10 +3934,10 @@
         <v>0.5</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
@@ -3946,23 +3946,23 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G135" s="5" t="n">
         <v>0</v>
@@ -3971,23 +3971,23 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0</v>
@@ -3996,23 +3996,23 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G137" s="5" t="n">
         <v>0</v>
@@ -4021,23 +4021,23 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E138" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G138" s="5" t="n">
         <v>0</v>
@@ -4046,11 +4046,11 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C139" s="5" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>8</v>
@@ -4071,7 +4071,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>8</v>
@@ -4096,17 +4096,17 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="E141" s="5" t="n">
         <v>3</v>
@@ -4121,23 +4121,23 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G142" s="5" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>49</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>47</v>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>4</v>
@@ -5408,43 +5408,43 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>40</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -5471,85 +5471,85 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>36</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>30</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -5870,12 +5870,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -5885,49 +5885,49 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -5975,75 +5975,75 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -6053,28 +6053,28 @@
         <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -6085,14 +6085,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>6</v>
@@ -6101,22 +6101,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -6332,49 +6332,49 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -6386,84 +6386,84 @@
         <v>20</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -6473,165 +6473,165 @@
         <v>2</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D66" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D66" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="E66" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
@@ -6641,55 +6641,55 @@
         <v>3</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6701,31 +6701,31 @@
         <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -6736,38 +6736,38 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -6878,103 +6878,103 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E85" s="5" t="n">
         <v>4</v>
@@ -6983,22 +6983,22 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -7172,148 +7172,148 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -7345,70 +7345,70 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
@@ -7418,118 +7418,118 @@
         <v>5</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -7544,112 +7544,112 @@
         <v>5</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -7660,14 +7660,14 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>3</v>
@@ -7676,33 +7676,33 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
@@ -7712,165 +7712,165 @@
         <v>4</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>一SUN一</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
           <t>當惡魔遇到殺手貓</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
+          <t>xAEGISx</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
           <t>オアシステップ</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>一Arch</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
@@ -7880,25 +7880,25 @@
         <v>2</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>3</v>
@@ -7907,22 +7907,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -8327,43 +8327,43 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
@@ -8384,18 +8384,18 @@
         <v>1</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
@@ -8405,123 +8405,123 @@
         <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
@@ -8531,60 +8531,60 @@
         <v>6</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
           <t>柿一門</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
@@ -8594,172 +8594,172 @@
         <v>4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>廣寒宮</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>廣寒宮</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>海尼根飲酒俱樂部</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>3</v>
@@ -8768,40 +8768,40 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>4</v>
@@ -8810,12 +8810,12 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
@@ -8825,25 +8825,25 @@
         <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="5" t="n">
         <v>1</v>
@@ -8852,7 +8852,7 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -8864,7 +8864,7 @@
         <v>10</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175" s="5" t="n">
         <v>1</v>
@@ -8873,49 +8873,49 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
+          <t>rabbits</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
           <t>ひよこりあ</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -8927,7 +8927,7 @@
         <v>10</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E178" s="5" t="n">
         <v>0</v>
@@ -8936,75 +8936,75 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>磯野家</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>磯野家</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Kaioken</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
@@ -9014,67 +9014,67 @@
         <v>2</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Kaioken</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E184" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
           <t>一SUN一</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
-        <is>
-          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E185" s="5" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -9104,19 +9104,19 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E187" s="5" t="n">
         <v>0</v>
@@ -9125,19 +9125,19 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" s="5" t="n">
         <v>0</v>
@@ -9146,22 +9146,22 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -9188,40 +9188,40 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" s="5" t="n">
         <v>1</v>
@@ -9230,54 +9230,54 @@
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
@@ -9287,81 +9287,81 @@
         <v>0</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
@@ -9377,33 +9377,33 @@
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -9572,7 +9572,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
@@ -9601,7 +9601,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -9610,17 +9610,17 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
@@ -12240,7 +12240,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="3">
@@ -12253,10 +12253,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2066</v>
+        <v>0.2064</v>
       </c>
     </row>
     <row r="4">
@@ -12269,10 +12269,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4217</v>
+        <v>0.4222</v>
       </c>
     </row>
     <row r="5">
@@ -12288,7 +12288,7 @@
         <v>176</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="6">
@@ -12301,10 +12301,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2133</v>
+        <v>0.2135</v>
       </c>
     </row>
   </sheetData>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -14741,15 +14741,15 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -16355,11 +16355,11 @@
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・:5勝</t>
+          <t>・殺戮・:6勝</t>
         </is>
       </c>
     </row>
@@ -16785,10 +16785,10 @@
         <v>11</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
@@ -16840,10 +16840,10 @@
         <v>13</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
@@ -16895,10 +16895,10 @@
         <v>14</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
@@ -16950,10 +16950,10 @@
         <v>10</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
@@ -17005,10 +17005,10 @@
         <v>8</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
@@ -17060,10 +17060,10 @@
         <v>11</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -17234,50 +17234,50 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>1</v>
@@ -17289,163 +17289,163 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="5" t="n">
+      <c r="G13" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="I13" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="O13" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="J14" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="M14" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="N14" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>131</v>
@@ -17665,10 +17665,10 @@
         <v>9</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -17720,10 +17720,10 @@
         <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -17830,10 +17830,10 @@
         <v>9</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22">
@@ -17885,10 +17885,10 @@
         <v>7</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
@@ -17995,10 +17995,10 @@
         <v>7</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
@@ -18215,10 +18215,10 @@
         <v>13</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29">
@@ -18710,10 +18710,10 @@
         <v>5</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
@@ -18774,105 +18774,105 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>7</v>
       </c>
       <c r="M39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="N39" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="O39" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="I40" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>7</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>0</v>
@@ -18939,32 +18939,32 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>7</v>
@@ -18973,53 +18973,53 @@
         <v>9</v>
       </c>
       <c r="L42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="M42" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="N42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P42" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>7</v>
@@ -19028,19 +19028,19 @@
         <v>9</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="5" t="n">
         <v>73</v>
@@ -19865,10 +19865,10 @@
         <v>9</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
@@ -20699,105 +20699,105 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P75" s="5" t="n">
         <v>0</v>
@@ -21689,29 +21689,29 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>DarkChaos</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
@@ -21726,16 +21726,16 @@
         <v>0</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>2</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="5" t="n">
         <v>13</v>
@@ -21744,29 +21744,29 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>UprisE</t>
+          <t>DarkChaos</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>0</v>
@@ -21781,10 +21781,10 @@
         <v>0</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O93" s="5" t="n">
         <v>0</v>
@@ -21799,17 +21799,17 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>UprisE</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0</v>
@@ -21854,17 +21854,17 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
@@ -21894,16 +21894,16 @@
         <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -21964,23 +21964,23 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>你淦嘛哎呦</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -22004,13 +22004,13 @@
         <v>0</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="5" t="n">
         <v>11</v>
@@ -22019,7 +22019,7 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>低調時尚</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -22050,50 +22050,50 @@
         <v>0</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>M4lySi4</t>
+          <t>你淦嘛哎呦</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -22123,17 +22123,17 @@
         <v>0</v>
       </c>
       <c r="Q99" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>低調時尚</t>
+          <t>M4lySi4</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C100" s="5" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H100" s="5" t="n">
         <v>0</v>
@@ -22160,10 +22160,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M100" s="5" t="n">
         <v>0</v>
@@ -22172,7 +22172,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P100" s="5" t="n">
         <v>0</v>
@@ -22789,17 +22789,17 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>阿公店</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
@@ -22829,13 +22829,13 @@
         <v>0</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>4</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="5" t="n">
         <v>8</v>
@@ -22844,17 +22844,17 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>星河夜夢</t>
+          <t>阿公店</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>0</v>
@@ -22866,31 +22866,31 @@
         <v>0</v>
       </c>
       <c r="H113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I113" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="5" t="n">
         <v>8</v>
@@ -22899,17 +22899,17 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ねこ</t>
+          <t>星河夜夢</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>0</v>
@@ -22921,13 +22921,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>0</v>
@@ -22954,32 +22954,32 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CatlandTHM</t>
+          <t>ねこ</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0</v>
@@ -23009,32 +23009,32 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>T乇卂卩卂尺TY</t>
+          <t>CatlandTHM</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="5" t="n">
         <v>0</v>
@@ -23058,17 +23058,17 @@
         <v>0</v>
       </c>
       <c r="Q116" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>T乇卂卩卂尺TY</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C117" s="5" t="n">
         <v>0</v>
@@ -23089,16 +23089,16 @@
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0</v>
@@ -23107,7 +23107,7 @@
         <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P117" s="5" t="n">
         <v>0</v>
@@ -23119,14 +23119,14 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>MiXëR</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>0</v>
@@ -23144,16 +23144,16 @@
         <v>0</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M118" s="5" t="n">
         <v>0</v>
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P118" s="5" t="n">
         <v>0</v>
@@ -23174,17 +23174,17 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Twinz</t>
+          <t>MiXëR</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="5" t="n">
         <v>0</v>
@@ -23229,17 +23229,17 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>Twinz</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>0</v>
@@ -23269,13 +23269,13 @@
         <v>0</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="5" t="n">
         <v>7</v>
@@ -23889,14 +23889,14 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>INCURSION</t>
+          <t>TнэÖяdeг</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>0</v>
@@ -23932,10 +23932,10 @@
         <v>0</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="5" t="n">
         <v>4</v>
@@ -23944,14 +23944,14 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>花落微雨醉紅塵</t>
+          <t>INCURSION</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>0</v>
@@ -23999,14 +23999,14 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Rest㐅Less</t>
+          <t>花落微雨醉紅塵</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>0</v>
@@ -24054,20 +24054,20 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>PARMESAN</t>
+          <t>Rest㐅Less</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="5" t="n">
         <v>0</v>
@@ -24082,7 +24082,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
         <v>0</v>
@@ -24109,23 +24109,23 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>PARMESAN</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5" t="n">
         <v>0</v>
@@ -24137,13 +24137,13 @@
         <v>0</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="5" t="n">
         <v>0</v>
@@ -24164,23 +24164,23 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Doraemon</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C137" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
         <v>0</v>
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="5" t="n">
         <v>0</v>
@@ -24219,14 +24219,14 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>歐皇</t>
+          <t>Doraemon</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>0</v>
@@ -24244,16 +24244,16 @@
         <v>0</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="5" t="n">
         <v>0</v>
@@ -24274,14 +24274,14 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>日耀星辰</t>
+          <t>歐皇</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>0</v>
@@ -24299,16 +24299,16 @@
         <v>0</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="5" t="n">
         <v>0</v>
@@ -24323,20 +24323,20 @@
         <v>0</v>
       </c>
       <c r="Q139" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>obIivion</t>
+          <t>日耀星辰</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>0</v>
@@ -24366,13 +24366,13 @@
         <v>0</v>
       </c>
       <c r="M140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" s="5" t="n">
         <v>0</v>
@@ -24384,11 +24384,11 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>PhoenixJP</t>
+          <t>obIivion</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C141" s="5" t="n">
         <v>0</v>
@@ -24421,13 +24421,13 @@
         <v>0</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" s="5" t="n">
         <v>0</v>
@@ -24439,11 +24439,11 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>TнэÖяdeг</t>
+          <t>PhoenixJP</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C142" s="5" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P142" s="5" t="n">
         <v>0</v>
@@ -26821,7 +26821,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -26857,7 +26857,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -26875,7 +26875,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -26893,7 +26893,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -26917,7 +26917,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>KOMADRONA</t>
+          <t>PokemonGO</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -26929,13 +26929,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PokemonGO</t>
+          <t>KOMADRONA</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -27607,16 +27607,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(47), 雪狼族(44), 沙漠黑鷹(42), 當惡魔遇到殺手貓(18), 雲淡風輕o(18), LeLien(13), ーリベリオンー(11), Unity(9)</t>
+          <t>・殺戮・(48), 雪狼族(45), 沙漠黑鷹(43), 當惡魔遇到殺手貓(19), 雲淡風輕o(19), LeLien(13), ーリベリオンー(11), Unity(9)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・(43勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
+          <t>・殺戮・(44勝), LeLien(4勝), ーリベリオンー(4勝), 沙漠黑鷹(1勝), Myst(1勝)</t>
         </is>
       </c>
     </row>
@@ -27722,16 +27722,16 @@
         <v>37</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Phoenix(17), TRAITORs(16), TheUniverse(13), xAEGISx(12), 微笑Party(7), FLORISTS(7), 一SUN一(6), 雲淡風輕o(6)</t>
+          <t>TRAITORs(17), Phoenix(17), TheUniverse(13), xAEGISx(12), 微笑Party(7), FLORISTS(7), 一SUN一(6), 雲淡風輕o(6)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(14勝), Phoenix(10勝), TheUniverse(5勝), xAEGISx(4勝), RaиkSS(3勝)</t>
+          <t>TRAITORs(15勝), Phoenix(10勝), TheUniverse(5勝), xAEGISx(4勝), RaиkSS(3勝)</t>
         </is>
       </c>
     </row>
@@ -27952,16 +27952,16 @@
         <v>39</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(39), シェイド(23), FLORISTS(14), 一Arch(14), 黒の太陽(11), ーEspoirー(10), xAEGISx(7), Restart(6)</t>
+          <t>オアシステップ(39), シェイド(24), FLORISTS(15), 一Arch(14), 黒の太陽(11), ーEspoirー(10), xAEGISx(7), オアシスステップ(6)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ(16勝), シェイド(11勝), 一Arch(6勝), FLORISTS(5勝), オアシスステップ(4勝)</t>
+          <t>オアシステップ(16勝), シェイド(12勝), 一Arch(6勝), FLORISTS(5勝), オアシスステップ(4勝)</t>
         </is>
       </c>
     </row>
@@ -27998,11 +27998,11 @@
         <v>42</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>一惡人谷一(22), ーリベリオンー(12), Kopitiam(11), ZirconiA(7), Иouver(7), Orzeca(5), 厶pocalypse(5), 柿一門(5)</t>
+          <t>一惡人谷一(22), ーリベリオンー(13), Kopitiam(11), ZirconiA(7), Иouver(7), MelonEmpire(6), 亗Luxúria亗(6), Orzeca(5)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -28110,10 +28110,10 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -28205,16 +28205,16 @@
         <v>53</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ひよこりあ(29), ーEspoirー(23), 義勇(21), 桜吹雪(20), 月下の集い(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
+          <t>ひよこりあ(29), ーEspoirー(24), 義勇(22), 桜吹雪(20), 月下の集い(19), TheEnd(17), のら猫(15), ZirconiA(14)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>義勇(11勝), ーEspoirー(6勝), 黄昏のえりしおん(6勝), TheEnd(6勝), ZirconiA(5勝)</t>
+          <t>義勇(11勝), 黄昏のえりしおん(7勝), ーEspoirー(6勝), TheEnd(6勝), ZirconiA(5勝)</t>
         </is>
       </c>
     </row>
@@ -28248,14 +28248,14 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 微笑Party(9), 柿一門(9), 桜吹雪(8), ーEspoirー(7), EIemento(5)</t>
+          <t>亗Luxúria亗(17), Restart(13), ßบรнíïdо丶ๅ家族(11), 微笑Party(10), 柿一門(9), 桜吹雪(8), ーEspoirー(7), EIemento(5)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-10-02</t>
+          <t>2025-08-01 〜 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2229</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.3392</v>
+        <v>0.3372</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>12</v>
@@ -846,51 +846,51 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1045</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>134</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.5896</v>
+        <v>0.1045</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -971,51 +971,51 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.32</v>
+        <v>0.5317</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
         <v>125</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.528</v>
+        <v>0.32</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>68</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5812</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
@@ -1146,51 +1146,51 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.3818</v>
+        <v>0.6216</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
         <v>110</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.6273</v>
+        <v>0.3818</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.7059</v>
+        <v>0.7093</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>9</v>
@@ -5723,127 +5723,127 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -5912,19 +5912,19 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Kopitiam</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>MelonEmpire</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>6</v>
@@ -5933,85 +5933,85 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>Kopitiam</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>MelonEmpire</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6038,64 +6038,64 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -6106,14 +6106,14 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>6</v>
@@ -6920,82 +6920,82 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>4</v>
@@ -7004,40 +7004,40 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E88" s="5" t="n">
         <v>0</v>
@@ -7046,54 +7046,54 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
@@ -7103,13 +7103,13 @@
         <v>2</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -7121,10 +7121,10 @@
         <v>16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -9862,26 +9862,26 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
@@ -9891,12 +9891,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="G16" s="6" t="n">
@@ -9920,12 +9920,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="G18" s="6" t="n">
@@ -9978,26 +9978,26 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="G19" s="6" t="n">
@@ -10007,12 +10007,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
@@ -12240,7 +12240,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.079</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="3">
@@ -12256,7 +12256,7 @@
         <v>460</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2064</v>
+        <v>0.2062</v>
       </c>
     </row>
     <row r="4">
@@ -12269,10 +12269,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4222</v>
+        <v>0.4227</v>
       </c>
     </row>
     <row r="5">
@@ -12288,7 +12288,7 @@
         <v>176</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.079</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="6">
@@ -12304,7 +12304,7 @@
         <v>476</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2135</v>
+        <v>0.2134</v>
       </c>
     </row>
   </sheetData>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Myst、TRAITORs、VainqueurJP</t>
+          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
+          <t>VainqueurJP:3勝, TRAITORs:1勝</t>
         </is>
       </c>
     </row>
@@ -14488,15 +14488,15 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、オアシスステップ、シェイド</t>
+          <t>Myst、TRAITORs、VainqueurJP</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>オアシスステップ:2勝, シェイド:1勝</t>
+          <t>TRAITORs:2勝, VainqueurJP:1勝, Myst:1勝</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、cobraXverse、一Arch</t>
+          <t>FLORISTS、オアシスステップ、シェイド</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön:2勝, 一Arch:1勝</t>
+          <t>オアシスステップ:2勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>Döraè่mön、cobraXverse、一Arch</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
+          <t>Döraè่mön:2勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、微笑Party、雪狼族</t>
+          <t>SkyCastIe、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:3勝</t>
+          <t>ßบรнíïdо丶ๅ家族:2勝, SkyCastIe:1勝</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
+          <t>・殺戮・、微笑Party、雪狼族</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
+          <t>雪狼族:3勝</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
+          <t>・殺戮・、沙漠黑鷹、雪狼族</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>沙漠黑鷹:2勝, 雪狼族:1勝</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、微笑Party、美孚冰室</t>
+          <t>PONYTAIL、當惡魔遇到殺手貓、雲淡風輕o</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Döraè่mön、Revenant、xAEGISx</t>
+          <t>SkyCastIe、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
+          <t>美孚冰室:1勝, SkyCastIe:1勝, 微笑Party:1勝</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Myst、PONYTAIL、RaиkSS</t>
+          <t>Döraè่mön、Revenant、xAEGISx</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL:3勝</t>
+          <t>Revenant:1勝, xAEGISx:1勝, Döraè่mön:1勝</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
+          <t>AlmaVivaJP、RaиkSS、・殺戮・</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
+          <t>AlmaVivaJP:3勝</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>PONYTAIL、TRAITORs、VainqueurJP</t>
+          <t>Myst、PONYTAIL、RaиkSS</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝, TRAITORs:1勝</t>
+          <t>PONYTAIL:3勝</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、Myst、TRAITORs</t>
+          <t>AlmaVivaJP、Maverickz、VainqueurJP</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
+          <t>AlmaVivaJP:2勝, VainqueurJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14764,15 +14764,15 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>シェイド、一Arch、黄昏のえりしおん</t>
+          <t>AlmaVivaJP、Myst、TRAITORs</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, 一Arch:1勝</t>
+          <t>TRAITORs:1勝, Myst:1勝, AlmaVivaJP:1勝</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、黒の太陽</t>
+          <t>シェイド、一Arch、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
+          <t>シェイド:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、黒の太陽</t>
+          <t>FLORISTS、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:2勝</t>
+          <t>FLORISTS:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、黒の太陽</t>
+          <t>オアシステップ、シェイド、黒の太陽</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
+          <t>オアシステップ:2勝</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーリベリオンー</t>
+          <t>xAEGISx、オアシステップ、黒の太陽</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>シェイド:2勝</t>
+          <t>xAEGISx:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Restart、シェイド、一Arch</t>
+          <t>オアシステップ、シェイド、ーリベリオンー</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Restart、オアシステップ、一Arch</t>
+          <t>Restart、シェイド、一Arch</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>一Arch:1勝, オアシステップ:1勝</t>
+          <t>シェイド:2勝</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ、シェイド、ーEspoirー</t>
+          <t>Restart、オアシステップ、一Arch</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
+          <t>一Arch:1勝, オアシステップ:1勝</t>
         </is>
       </c>
     </row>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Etërnîty、オアシステップ、シェイド</t>
+          <t>オアシステップ、シェイド、ーEspoirー</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, Etërnîty:1勝</t>
+          <t>オアシステップ:1勝, ーEspoirー:1勝</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Pandora、xAEGISx、黒の太陽</t>
+          <t>Etërnîty、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>黒の太陽:1勝, Pandora:1勝</t>
+          <t>オアシステップ:1勝, Etërnîty:1勝</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
+          <t>Pandora、xAEGISx、黒の太陽</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
+          <t>黒の太陽:1勝, Pandora:1勝</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Bagaиเ่、Grîmoîrê、米丨FÖSSIL丨米</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>Grîmoîrê:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, 美孚冰室:1勝</t>
+          <t>Orzeca:1勝, 一SUN一:1勝</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
+          <t>微笑Party、柿一門、美孚冰室</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>微笑Party:1勝, 美孚冰室:1勝</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
+          <t>ßบรнíïdо丶ๅ家族、ーEspoirー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
+          <t>ZirconiA、ßบรнíïdо丶ๅ家族、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
+          <t>亗Luxúria亗:2勝</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、VainqueurJP、一SUN一</t>
+          <t>ßบรнíïdо丶ๅ家族、亗Luxúria亗、微笑Party</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>亗Luxúria亗:1勝, ßบรнíïdо丶ๅ家族:1勝</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs、TheUniverse、xAEGISx</t>
+          <t>Orzeca、VainqueurJP、一SUN一</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>TheUniverse:1勝, xAEGISx:1勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
+          <t>TRAITORs、TheUniverse、xAEGISx</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
+          <t>TheUniverse:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、微笑Party、美孚冰室</t>
+          <t>Kopitiam、ーリベリオンー、亗Luxúria亗</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>微笑Party:1勝, FLORISTS:1勝</t>
+          <t>ーリベリオンー:1勝, 亗Luxúria亗:1勝</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Restart、ー麒麟ー</t>
+          <t>FLORISTS、微笑Party、美孚冰室</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>微笑Party:1勝, FLORISTS:1勝</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、シェイド、一SUN一</t>
+          <t>FLORISTS、Restart、ー麒麟ー</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>一SUN一:2勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
+          <t>Orzeca、シェイド、一SUN一</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS:2勝</t>
+          <t>一SUN一:2勝</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、シェイド、ー麒麟ー</t>
+          <t>FLORISTS、ーEspoirー、黄昏のえりしおん</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>シェイド:1勝, ー麒麟ー:1勝</t>
+          <t>FLORISTS:2勝</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>SЕRЕNIТY、Twinz、Иouver</t>
+          <t>FLORISTS、シェイド、ー麒麟ー</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
+          <t>シェイド:1勝, ー麒麟ー:1勝</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>FLORISTS、Unity、xAEGISx</t>
+          <t>SЕRЕNIТY、Twinz、Иouver</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Unity:1勝, xAEGISx:1勝</t>
+          <t>Twinz:1勝, SЕRЕNIТY:1勝</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Unity、xAEGISx、一Arch</t>
+          <t>FLORISTS、Unity、xAEGISx</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Unity:2勝</t>
+          <t>Unity:1勝, xAEGISx:1勝</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Phoenix、Unity、一Arch</t>
+          <t>Unity、xAEGISx、一Arch</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Phoenix:1勝, 一Arch:1勝</t>
+          <t>Unity:2勝</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Unity、VainqueurJP、xAEGISx</t>
+          <t>Phoenix、Unity、一Arch</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx:1勝, Unity:1勝</t>
+          <t>Phoenix:1勝, 一Arch:1勝</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>xAEGISx、オアシステップ、シェイド</t>
+          <t>Unity、VainqueurJP、xAEGISx</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>オアシステップ:1勝, シェイド:1勝</t>
+          <t>xAEGISx:1勝, Unity:1勝</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Maverickz、Myst、RaиkSS</t>
+          <t>xAEGISx、オアシステップ、シェイド</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>オアシステップ:1勝, シェイド:1勝</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>・殺戮・、歐皇、雪狼族</t>
+          <t>Maverickz、Myst、RaиkSS</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>雪狼族:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>SkyCastIe、・殺戮・、雪狼族</t>
+          <t>・殺戮・、歐皇、雪狼族</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP、・殺戮・、雪狼族</t>
+          <t>SkyCastIe、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
+          <t>VainqueurJP、・殺戮・、雪狼族</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>RaиkSS:2勝</t>
+          <t>雪狼族:2勝</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
+          <t>RaиkSS、微笑Party、當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓:2勝</t>
+          <t>RaиkSS:2勝</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
+          <t>當惡魔遇到殺手貓、美孚冰室、雲淡風輕o</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>一DEFlANCE:2勝</t>
+          <t>當惡魔遇到殺手貓:2勝</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー、一Arch、黒の太陽</t>
+          <t>Ancîеnts、一DEFIANCE、一DEFlANCE</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
+          <t>一DEFlANCE:2勝</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Myst、Phoenix、VainqueurJP</t>
+          <t>ーリベリオンー、一Arch、黒の太陽</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>VainqueurJP:2勝</t>
+          <t>ーリベリオンー:1勝, 黒の太陽:1勝</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>PokemonGo、TRAITORs、xAEGISx</t>
+          <t>Myst、Phoenix、VainqueurJP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs:2勝</t>
+          <t>VainqueurJP:2勝</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Oops、沙漠黑鷹、雲淡風輕o</t>
+          <t>PokemonGo、TRAITORs、xAEGISx</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>沙漠黑鷹:2勝</t>
+          <t>TRAITORs:2勝</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>天機、心晴、海尼根飲酒俱樂部</t>
+          <t>Oops、沙漠黑鷹、雲淡風輕o</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
+          <t>沙漠黑鷹:2勝</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Bagaиเ่、Иouver、厶pocalypse</t>
+          <t>天機、心晴、海尼根飲酒俱樂部</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
+          <t>天機:1勝, 海尼根飲酒俱樂部:1勝</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP、RaиkSS、・殺戮・</t>
+          <t>Bagaиเ่、Иouver、厶pocalypse</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP:2勝</t>
+          <t>厶pocalypse:1勝, Bagaиเ่:1勝</t>
         </is>
       </c>
     </row>
@@ -16840,10 +16840,10 @@
         <v>13</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
@@ -17234,105 +17234,105 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>1</v>
@@ -17509,105 +17509,105 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ßบรнíïdо丶ๅ家族</t>
+          <t>VainqueurJP</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="G16" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>12</v>
       </c>
       <c r="K16" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VainqueurJP</t>
+          <t>ßบรнíïdо丶ๅ家族</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="I17" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>0</v>
@@ -17775,10 +17775,10 @@
         <v>7</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
@@ -17894,108 +17894,108 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" s="5" t="n">
+      <c r="I23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="M23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="G24" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>110</v>
@@ -18655,10 +18655,10 @@
         <v>4</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
@@ -27791,16 +27791,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(42), RaиkSS(33), PONYTAIL(26), Myst(20), VainqueurJP(19), TRAITORs(12), Phoenix(9), ・殺戮・(8)</t>
+          <t>AlmaVivaJP(43), RaиkSS(34), PONYTAIL(26), Myst(20), VainqueurJP(19), TRAITORs(12), ・殺戮・(9), Phoenix(9)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AlmaVivaJP(31勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
+          <t>AlmaVivaJP(32勝), RaиkSS(13勝), PONYTAIL(7勝), VainqueurJP(4勝), Myst(3勝)</t>
         </is>
       </c>
     </row>
@@ -27975,16 +27975,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(40), VainqueurJP(28), RaиkSS(28), PONYTAIL(25), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
+          <t>TRAITORs(41), VainqueurJP(29), RaиkSS(28), PONYTAIL(26), Myst(19), AlmaVivaJP(15), Maverickz(6), Phoenix(5)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TRAITORs(23勝), VainqueurJP(9勝), RaиkSS(9勝), PONYTAIL(8勝), AlmaVivaJP(5勝)</t>
+          <t>TRAITORs(23勝), VainqueurJP(10勝), RaиkSS(9勝), PONYTAIL(8勝), AlmaVivaJP(5勝)</t>
         </is>
       </c>
     </row>

--- a/report/output/拠点戦_過去データ分析.xlsx
+++ b/report/output/拠点戦_過去データ分析.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 〜 2026-10-03</t>
+          <t>2025-08-01 〜 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2231</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -621,23 +621,23 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>亗Luxúria亗</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>58</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.3372</v>
+        <v>0.3353</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>亗Luxúria亗</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -662,7 +662,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1938</v>
+        <v>0.1925</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>20</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>43</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2774</v>
+        <v>0.2756</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>21</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.3382</v>
+        <v>0.3431</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>17</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>79</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5809</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>17</v>
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.1818</v>
+        <v>0.1805</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>32</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>2</v>
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.2109</v>
+        <v>0.2171</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.4583</v>
+        <v>0.4628</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>8</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.5167</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>18</v>
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4911</v>
+        <v>0.4956</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>9</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>69</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.6216</v>
+        <v>0.6161</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>10</v>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.181</v>
+        <v>0.1792</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>16</v>
@@ -1246,51 +1246,51 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
         <v>105</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.2667</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.2692</v>
+        <v>0.1429</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.2892</v>
+        <v>0.2857</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>11</v>
@@ -1521,23 +1521,23 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.2405</v>
+        <v>0.425</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0</v>
@@ -1546,51 +1546,51 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
         <v>79</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.4304</v>
+        <v>0.1646</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.1538</v>
+        <v>0.2405</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1696,51 +1696,51 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>一惡人谷一</t>
+          <t>毛家村</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.7246</v>
+        <v>0.1429</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>毛家村</t>
+          <t>一惡人谷一</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
         <v>69</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.1449</v>
+        <v>0.7246</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.1791</v>
+        <v>0.1765</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>1</v>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>14</v>
@@ -1821,51 +1821,51 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>Döraè่mön</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
         <v>60</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Döraè่mön</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.2807</v>
+        <v>0.2759</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>5</v>
@@ -2371,23 +2371,23 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>cobraXverse</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>0.1786</v>
+        <v>0.2759</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>海洋之心</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -2409,38 +2409,38 @@
         <v>0.1786</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>cobraXverse</t>
+          <t>海洋之心</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
         <v>28</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>0.2857</v>
+        <v>0.1786</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -2796,7 +2796,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>のら猫</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -2809,10 +2809,10 @@
         <v>0.1333</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
@@ -2821,23 +2821,23 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>のら猫</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C90" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>0.1429</v>
+        <v>0.1333</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>0</v>
@@ -2846,23 +2846,23 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>TipsyTavern</t>
+          <t>ーArch</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
         <v>14</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>0.2143</v>
+        <v>0.6429</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>0</v>
@@ -2871,23 +2871,23 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>ーArch</t>
+          <t>TipsyTavern</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>0.6923</v>
+        <v>0.2143</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>0</v>
@@ -2971,23 +2971,23 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>一DEFlANCE</t>
+          <t>オアシスステップ</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
         <v>12</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>0</v>
@@ -2996,23 +2996,23 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>オアシスステップ</t>
+          <t>一DEFlANCE</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>12</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0</v>
@@ -3721,20 +3721,20 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>MystSA</t>
+          <t>SERENITY</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>10</v>
@@ -3746,23 +3746,23 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>China紅</t>
+          <t>MystSA</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>SERENITY</t>
+          <t>China紅</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -3784,10 +3784,10 @@
         <v>0</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0</v>
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>46</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>5</v>
@@ -5396,13 +5396,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -5618,43 +5618,43 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Orzeca</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Orzeca</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>27</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -5786,82 +5786,82 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>2</v>
@@ -5870,12 +5870,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -5885,7 +5885,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -6101,103 +6101,103 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>7</v>
@@ -6479,33 +6479,33 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>東京熱株式會社</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>雪狼族</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>沙漠黑鷹</t>
+          <t>東京熱株式會社</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>雪狼族</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
@@ -6515,130 +6515,130 @@
         <v>2</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Bagaиเ่</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>C0BRA</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Bagaиเ่</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>C0BRA</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D67" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D67" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="E67" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>FLORISTS</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
           <t>シェイド</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>5</v>
@@ -6647,61 +6647,61 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -6722,10 +6722,10 @@
         <v>18</v>
       </c>
       <c r="D73" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -6752,22 +6752,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -6778,38 +6778,38 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -6820,17 +6820,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -7214,7 +7214,7 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -7226,154 +7226,154 @@
         <v>15</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>星隕</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>星隕</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>RaиkSS</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
         <v>15</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>5</v>
@@ -7387,65 +7387,65 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>LeLien</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>LeLien</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -7457,217 +7457,217 @@
         <v>14</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>AlmaVivaJP</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>TRAITORs</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Myst</t>
+          <t>AlmaVivaJP</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>PONYTAIL</t>
+          <t>TRAITORs</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>ーリベリオンー</t>
+          <t>Myst</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>PONYTAIL</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>ーリベリオンー</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Elemento</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>3</v>
@@ -7676,54 +7676,54 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
@@ -7733,55 +7733,55 @@
         <v>4</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>當惡魔遇到殺手貓</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>微笑Party</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -7796,76 +7796,76 @@
         <v>0</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>微笑Party</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>當惡魔遇到殺手貓</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -7880,81 +7880,81 @@
         <v>2</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Elemento</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
@@ -7964,7 +7964,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -8159,138 +8159,138 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>氣噗噗讓玻璃心碎一地</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>氣噗噗讓玻璃心碎一地</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D145" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E145" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>オアシステップ</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>オアシステップ</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
@@ -8306,12 +8306,12 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Maverickz</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
@@ -8321,70 +8321,70 @@
         <v>2</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Maverickz</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>rabbits</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>rabbits</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ひよこりあ</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
@@ -8405,18 +8405,18 @@
         <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
@@ -8426,123 +8426,123 @@
         <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>天機</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>心晴</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>天機</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>心晴</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>TheUniverse</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Anino</t>
+          <t>TheUniverse</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>ouтcasт</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>・殺戮・</t>
+          <t>Anino</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>ouтcasт</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
@@ -8552,60 +8552,60 @@
         <v>6</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
+          <t>・殺戮・</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
           <t>柿一門</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>PokemonGo</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>一Arch</t>
+          <t>沙漠黑鷹</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>PokemonGo</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>ー麒麟ー</t>
+          <t>一Arch</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
@@ -8615,70 +8615,70 @@
         <v>4</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -9083,28 +9083,28 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>一SUN一</t>
+          <t>RaиkSS</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>雲淡風輕o</t>
+          <t>・殺戮・</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>美孚冰室</t>
+          <t>一SUN一</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -9125,19 +9125,19 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>FLORISTS</t>
+          <t>美孚冰室</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>雲淡風輕o</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E188" s="5" t="n">
         <v>0</v>
@@ -9146,19 +9146,19 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>FLORISTS</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>厶pocalypse</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>0</v>
@@ -9167,37 +9167,37 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>シェイド</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>黄昏のえりしおん</t>
+          <t>厶pocalypse</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>ー麒麟ー</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D191" s="5" t="n">
         <v>0</v>
@@ -9209,82 +9209,82 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>シェイド</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>黒の太陽</t>
+          <t>黄昏のえりしおん</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>EIemento</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>ZirconiA</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Revenant</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Иouver</t>
+          <t>黒の太陽</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>MÏRÃGË</t>
+          <t>EIemento</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>RëBîrth</t>
+          <t>ZirconiA</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E195" s="5" t="n">
         <v>1</v>
@@ -9293,33 +9293,33 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>Revenant</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>ーEspoirー</t>
+          <t>Иouver</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>MÏRÃGË</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>RëBîrth</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
@@ -9329,81 +9329,81 @@
         <v>0</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>Pandora</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>義勇</t>
+          <t>ーEspoirー</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>xAEGISx</t>
+          <t>月下の集い</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>柿一門</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>ひよこりあ</t>
+          <t>Pandora</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>義勇</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>月下の集い</t>
+          <t>xAEGISx</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>桜吹雪</t>
+          <t>柿一門</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
@@ -10915,13 +10915,13 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.951</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="52">
@@ -12240,7 +12240,7 @@
         <v>176</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0789</v>
+        <v>0.0786</v>
       </c>
     </row>
     <row r="3">
@@ -12256,7 +12256,7 @@
         <v>460</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.2062</v>
+        <v>0.2055</v>
       </c>
     </row>
     <row r="4">
@@ -12269,10 +12269,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4227</v>
+        <v>0.4231</v>
       </c>
     </row>
     <row r="5">
@@ -12285,10 +12285,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0789</v>
+        <v>0.0791</v>
       </c>
     </row>
     <row r="6">
@@ -12301,10 +12301,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2134</v>
+        <v>0.2136</v>
       </c>
     </row>
   </sheetData>
@@ -12318,7 +12318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Orzeca、ーリベリオンー、一SUN一</t>
+          <t>Elemento、ーリベリオンー、厶pocalypse</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Orzeca:1勝, 一SUN一:1勝</t>
+          <t>厶pocalypse:1勝, ーリベリオンー:1勝</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>微笑Party、柿一門、美孚冰室</t>
+          <t>Orzeca、ーリベリオンー、一SUN一</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -15071,7 +15071,7 @@
 